--- a/inputs/ELDORADO/os/OS_SUREG_SP_eldorado/OS_RA005_SUREG_SP_lote1537.xlsx
+++ b/inputs/ELDORADO/os/OS_SUREG_SP_eldorado/OS_RA005_SUREG_SP_lote1537.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPasta_de_trabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\viviane.ferrari\Documents\Projetos\GeochemAnalytical\inputs\boletins_raw\geosol\Eldorado\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\viviane.ferrari\Documents\Projetos\GeochemAnalytical\inputs\eldorado\os\OS_SUREG_SP_eldorado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{810228C3-DCE9-4BE5-ACEE-1F417E565CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98876E2B-5BF4-4EFA-882C-9707476EF431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="-10910" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DadosGerais" sheetId="8" r:id="rId1"/>
@@ -2691,138 +2691,6 @@
     <t>x</t>
   </si>
   <si>
-    <t>4077-RB-S-003</t>
-  </si>
-  <si>
-    <t>4077-RB-S-004</t>
-  </si>
-  <si>
-    <t>4077-RB-S-004A</t>
-  </si>
-  <si>
-    <t>4077-RB-S-010</t>
-  </si>
-  <si>
-    <t>4077-RB-S-040</t>
-  </si>
-  <si>
-    <t>4077-RB-S-046</t>
-  </si>
-  <si>
-    <t>4077-RB-S-048</t>
-  </si>
-  <si>
-    <t>4077-RB-S-049</t>
-  </si>
-  <si>
-    <t>4077-RB-S-053</t>
-  </si>
-  <si>
-    <t>4077-RB-S-053A</t>
-  </si>
-  <si>
-    <t>4077-RB-S-059</t>
-  </si>
-  <si>
-    <t>4077-RB-S-076</t>
-  </si>
-  <si>
-    <t>4077-RB-S-081</t>
-  </si>
-  <si>
-    <t>4077-RB-S-089</t>
-  </si>
-  <si>
-    <t>4077-RB-S-100</t>
-  </si>
-  <si>
-    <t>4077-RB-S-113</t>
-  </si>
-  <si>
-    <t>4077-RB-S-115</t>
-  </si>
-  <si>
-    <t>4077-RB-S-118</t>
-  </si>
-  <si>
-    <t>4077-RB-S-132</t>
-  </si>
-  <si>
-    <t>4077-RB-S-149</t>
-  </si>
-  <si>
-    <t>4077-RB-S-150</t>
-  </si>
-  <si>
-    <t>4077-RB-S-156</t>
-  </si>
-  <si>
-    <t>4077-RB-S-158</t>
-  </si>
-  <si>
-    <t>4077-RB-S-160</t>
-  </si>
-  <si>
-    <t>4077-RB-S-160A</t>
-  </si>
-  <si>
-    <t>4077-RB-S-161</t>
-  </si>
-  <si>
-    <t>4077-RB-S-163</t>
-  </si>
-  <si>
-    <t>4077-RB-S-164</t>
-  </si>
-  <si>
-    <t>4077-RB-S-165</t>
-  </si>
-  <si>
-    <t>4077-RB-S-165A</t>
-  </si>
-  <si>
-    <t>4077-RB-S-167</t>
-  </si>
-  <si>
-    <t>4077-RB-S-169</t>
-  </si>
-  <si>
-    <t>4077-RB-S-171</t>
-  </si>
-  <si>
-    <t>4077-RB-S-174</t>
-  </si>
-  <si>
-    <t>4077-RB-S-177</t>
-  </si>
-  <si>
-    <t>4077-RB-S-180</t>
-  </si>
-  <si>
-    <t>4077-RB-S-182</t>
-  </si>
-  <si>
-    <t>4077-RB-S-189</t>
-  </si>
-  <si>
-    <t>4077-RB-S-190</t>
-  </si>
-  <si>
-    <t>4077-RB-S-197</t>
-  </si>
-  <si>
-    <t>4077-RB-S-198</t>
-  </si>
-  <si>
-    <t>4077-RB-S-217</t>
-  </si>
-  <si>
-    <t>4077-RB-S-229</t>
-  </si>
-  <si>
-    <t>4077-RB-S-230</t>
-  </si>
-  <si>
     <t>1537/SP</t>
   </si>
   <si>
@@ -2958,24 +2826,6 @@
     <t>IBX226</t>
   </si>
   <si>
-    <t>4077-RB-S-232</t>
-  </si>
-  <si>
-    <t>4077-RB-S-233</t>
-  </si>
-  <si>
-    <t>4077-RB-S-238</t>
-  </si>
-  <si>
-    <t>4077-RB-S-242</t>
-  </si>
-  <si>
-    <t>4077-RB-S-246</t>
-  </si>
-  <si>
-    <t>4077-RB-S-247</t>
-  </si>
-  <si>
     <t>IBX227</t>
   </si>
   <si>
@@ -2992,6 +2842,156 @@
   </si>
   <si>
     <t>IBX232</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0003</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0004</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0004A</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0010</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0040</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0046</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0048</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0049</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0053</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0053A</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0059</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0076</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0081</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0089</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0100</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0113</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0115</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0118</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0132</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0149</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0150</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0156</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0158</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0160</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0160A</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0161</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0163</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0164</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0165</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0165A</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0167</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0169</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0171</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0174</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0177</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0180</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0182</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0189</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0190</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0197</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0198</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0217</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0229</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0230</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0232</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0233</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0238</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0242</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0246</t>
+  </si>
+  <si>
+    <t>4077-RB-S-0247</t>
   </si>
 </sst>
 </file>
@@ -4490,53 +4490,291 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="55" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="29" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4612,392 +4850,114 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="55" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="36" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="5" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="5" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="5" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="5" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="5" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="5" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="5" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="5" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -5065,31 +5025,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="43" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="44" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="45" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="5" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="5" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="24" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="165" fontId="24" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7095,11 +7095,11 @@
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
-      <c r="I2" s="142" t="s">
+      <c r="I2" s="252" t="s">
         <v>67</v>
       </c>
-      <c r="J2" s="143"/>
-      <c r="K2" s="144"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="254"/>
       <c r="L2" s="17"/>
     </row>
     <row r="3" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7111,11 +7111,11 @@
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
-      <c r="I3" s="145" t="s">
+      <c r="I3" s="255" t="s">
         <v>653</v>
       </c>
-      <c r="J3" s="146"/>
-      <c r="K3" s="147"/>
+      <c r="J3" s="256"/>
+      <c r="K3" s="257"/>
       <c r="L3" s="17"/>
     </row>
     <row r="4" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7127,11 +7127,11 @@
       <c r="F4" s="15"/>
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
-      <c r="I4" s="145" t="s">
+      <c r="I4" s="255" t="s">
         <v>654</v>
       </c>
-      <c r="J4" s="146"/>
-      <c r="K4" s="147"/>
+      <c r="J4" s="256"/>
+      <c r="K4" s="257"/>
       <c r="L4" s="17"/>
     </row>
     <row r="5" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7143,11 +7143,11 @@
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
       <c r="H5" s="15"/>
-      <c r="I5" s="148" t="s">
+      <c r="I5" s="258" t="s">
         <v>655</v>
       </c>
-      <c r="J5" s="149"/>
-      <c r="K5" s="150"/>
+      <c r="J5" s="259"/>
+      <c r="K5" s="260"/>
       <c r="L5" s="17"/>
     </row>
     <row r="6" spans="1:18" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7159,176 +7159,176 @@
       <c r="F6" s="16"/>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
-      <c r="I6" s="151" t="s">
+      <c r="I6" s="261" t="s">
         <v>656</v>
       </c>
-      <c r="J6" s="152"/>
-      <c r="K6" s="153"/>
+      <c r="J6" s="262"/>
+      <c r="K6" s="263"/>
       <c r="L6" s="17"/>
     </row>
     <row r="7" spans="1:18" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="20"/>
-      <c r="B7" s="138" t="s">
+      <c r="B7" s="248" t="s">
         <v>781</v>
       </c>
-      <c r="C7" s="139"/>
-      <c r="D7" s="139"/>
-      <c r="E7" s="139"/>
-      <c r="F7" s="139"/>
-      <c r="G7" s="139"/>
-      <c r="H7" s="139"/>
-      <c r="I7" s="140"/>
-      <c r="J7" s="140"/>
-      <c r="K7" s="141"/>
+      <c r="C7" s="249"/>
+      <c r="D7" s="249"/>
+      <c r="E7" s="249"/>
+      <c r="F7" s="249"/>
+      <c r="G7" s="249"/>
+      <c r="H7" s="249"/>
+      <c r="I7" s="250"/>
+      <c r="J7" s="250"/>
+      <c r="K7" s="251"/>
       <c r="L7" s="21"/>
     </row>
     <row r="8" spans="1:18" s="2" customFormat="1" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20"/>
-      <c r="B8" s="156" t="s">
+      <c r="B8" s="226" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="157"/>
-      <c r="D8" s="157"/>
-      <c r="E8" s="157"/>
-      <c r="F8" s="157"/>
-      <c r="G8" s="157"/>
-      <c r="H8" s="157"/>
-      <c r="I8" s="157"/>
-      <c r="J8" s="157"/>
-      <c r="K8" s="158"/>
+      <c r="C8" s="227"/>
+      <c r="D8" s="227"/>
+      <c r="E8" s="227"/>
+      <c r="F8" s="227"/>
+      <c r="G8" s="227"/>
+      <c r="H8" s="227"/>
+      <c r="I8" s="227"/>
+      <c r="J8" s="227"/>
+      <c r="K8" s="228"/>
       <c r="L8" s="21"/>
     </row>
     <row r="9" spans="1:18" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="22"/>
-      <c r="B9" s="159" t="s">
+      <c r="B9" s="229" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="160"/>
-      <c r="D9" s="160"/>
-      <c r="E9" s="160"/>
-      <c r="F9" s="160"/>
-      <c r="G9" s="160"/>
-      <c r="H9" s="160"/>
-      <c r="I9" s="160"/>
-      <c r="J9" s="160"/>
-      <c r="K9" s="161"/>
+      <c r="C9" s="230"/>
+      <c r="D9" s="230"/>
+      <c r="E9" s="230"/>
+      <c r="F9" s="230"/>
+      <c r="G9" s="230"/>
+      <c r="H9" s="230"/>
+      <c r="I9" s="230"/>
+      <c r="J9" s="230"/>
+      <c r="K9" s="231"/>
       <c r="L9" s="21"/>
       <c r="R9" s="115"/>
     </row>
     <row r="10" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="22"/>
-      <c r="B10" s="162" t="s">
+      <c r="B10" s="232" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="163"/>
-      <c r="D10" s="163"/>
-      <c r="E10" s="163"/>
-      <c r="F10" s="163"/>
-      <c r="G10" s="163"/>
-      <c r="H10" s="163"/>
-      <c r="I10" s="163"/>
-      <c r="J10" s="163"/>
-      <c r="K10" s="164"/>
+      <c r="C10" s="233"/>
+      <c r="D10" s="233"/>
+      <c r="E10" s="233"/>
+      <c r="F10" s="233"/>
+      <c r="G10" s="233"/>
+      <c r="H10" s="233"/>
+      <c r="I10" s="233"/>
+      <c r="J10" s="233"/>
+      <c r="K10" s="234"/>
       <c r="L10" s="21"/>
     </row>
     <row r="11" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22"/>
-      <c r="B11" s="162" t="s">
+      <c r="B11" s="232" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="163"/>
-      <c r="D11" s="163"/>
-      <c r="E11" s="163"/>
-      <c r="F11" s="163"/>
-      <c r="G11" s="163"/>
-      <c r="H11" s="163"/>
-      <c r="I11" s="163"/>
-      <c r="J11" s="163"/>
-      <c r="K11" s="164"/>
+      <c r="C11" s="233"/>
+      <c r="D11" s="233"/>
+      <c r="E11" s="233"/>
+      <c r="F11" s="233"/>
+      <c r="G11" s="233"/>
+      <c r="H11" s="233"/>
+      <c r="I11" s="233"/>
+      <c r="J11" s="233"/>
+      <c r="K11" s="234"/>
       <c r="L11" s="21"/>
     </row>
     <row r="12" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="22"/>
-      <c r="B12" s="162" t="s">
+      <c r="B12" s="232" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="163"/>
-      <c r="D12" s="163"/>
-      <c r="E12" s="163"/>
-      <c r="F12" s="163"/>
-      <c r="G12" s="163"/>
-      <c r="H12" s="163"/>
-      <c r="I12" s="163"/>
-      <c r="J12" s="163"/>
-      <c r="K12" s="164"/>
+      <c r="C12" s="233"/>
+      <c r="D12" s="233"/>
+      <c r="E12" s="233"/>
+      <c r="F12" s="233"/>
+      <c r="G12" s="233"/>
+      <c r="H12" s="233"/>
+      <c r="I12" s="233"/>
+      <c r="J12" s="233"/>
+      <c r="K12" s="234"/>
       <c r="L12" s="21"/>
     </row>
     <row r="13" spans="1:18" s="2" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="22"/>
-      <c r="B13" s="165" t="s">
+      <c r="B13" s="235" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="166"/>
-      <c r="D13" s="166"/>
-      <c r="E13" s="166"/>
-      <c r="F13" s="166"/>
-      <c r="G13" s="166"/>
-      <c r="H13" s="166"/>
-      <c r="I13" s="166"/>
-      <c r="J13" s="166"/>
-      <c r="K13" s="167"/>
+      <c r="C13" s="236"/>
+      <c r="D13" s="236"/>
+      <c r="E13" s="236"/>
+      <c r="F13" s="236"/>
+      <c r="G13" s="236"/>
+      <c r="H13" s="236"/>
+      <c r="I13" s="236"/>
+      <c r="J13" s="236"/>
+      <c r="K13" s="237"/>
       <c r="L13" s="21"/>
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18"/>
-      <c r="B14" s="168" t="s">
+      <c r="B14" s="238" t="s">
         <v>68</v>
       </c>
-      <c r="C14" s="169"/>
-      <c r="D14" s="169"/>
-      <c r="E14" s="169"/>
-      <c r="F14" s="169"/>
-      <c r="G14" s="169"/>
-      <c r="H14" s="169"/>
-      <c r="I14" s="169"/>
-      <c r="J14" s="169"/>
-      <c r="K14" s="170"/>
+      <c r="C14" s="239"/>
+      <c r="D14" s="239"/>
+      <c r="E14" s="239"/>
+      <c r="F14" s="239"/>
+      <c r="G14" s="239"/>
+      <c r="H14" s="239"/>
+      <c r="I14" s="239"/>
+      <c r="J14" s="239"/>
+      <c r="K14" s="240"/>
       <c r="L14" s="17"/>
     </row>
     <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15"/>
-      <c r="B15" s="171" t="s">
+      <c r="B15" s="241" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="172"/>
-      <c r="D15" s="172"/>
-      <c r="E15" s="173"/>
-      <c r="F15" s="174" t="s">
+      <c r="C15" s="242"/>
+      <c r="D15" s="242"/>
+      <c r="E15" s="243"/>
+      <c r="F15" s="244" t="s">
         <v>435</v>
       </c>
-      <c r="G15" s="174"/>
-      <c r="H15" s="174"/>
-      <c r="I15" s="174"/>
-      <c r="J15" s="174"/>
-      <c r="K15" s="175"/>
+      <c r="G15" s="244"/>
+      <c r="H15" s="244"/>
+      <c r="I15" s="244"/>
+      <c r="J15" s="244"/>
+      <c r="K15" s="245"/>
       <c r="L15" s="17"/>
     </row>
     <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15"/>
       <c r="B16" s="23"/>
       <c r="C16" s="15"/>
-      <c r="D16" s="176" t="s">
+      <c r="D16" s="246" t="s">
         <v>546</v>
       </c>
-      <c r="E16" s="177"/>
-      <c r="F16" s="174" t="s">
+      <c r="E16" s="247"/>
+      <c r="F16" s="244" t="s">
         <v>695</v>
       </c>
-      <c r="G16" s="174"/>
-      <c r="H16" s="174"/>
-      <c r="I16" s="174"/>
-      <c r="J16" s="174"/>
-      <c r="K16" s="175"/>
+      <c r="G16" s="244"/>
+      <c r="H16" s="244"/>
+      <c r="I16" s="244"/>
+      <c r="J16" s="244"/>
+      <c r="K16" s="245"/>
       <c r="L16" s="17"/>
     </row>
     <row r="17" spans="1:256" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7339,15 +7339,15 @@
       <c r="E17" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="154" t="str">
+      <c r="F17" s="224" t="str">
         <f>VLOOKUP($F$16,Controle!R3:W16,3,FALSE)</f>
         <v>Rua Costa, 55   Bairro Cerqueira César</v>
       </c>
-      <c r="G17" s="154"/>
-      <c r="H17" s="154"/>
-      <c r="I17" s="154"/>
-      <c r="J17" s="154"/>
-      <c r="K17" s="155"/>
+      <c r="G17" s="224"/>
+      <c r="H17" s="224"/>
+      <c r="I17" s="224"/>
+      <c r="J17" s="224"/>
+      <c r="K17" s="225"/>
       <c r="L17" s="17"/>
     </row>
     <row r="18" spans="1:256" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7358,20 +7358,20 @@
       <c r="E18" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="F18" s="178" t="str">
+      <c r="F18" s="205" t="str">
         <f>VLOOKUP($F$16,Controle!R3:W16,4,FALSE)</f>
         <v>01304-010</v>
       </c>
-      <c r="G18" s="179"/>
-      <c r="H18" s="180" t="s">
+      <c r="G18" s="207"/>
+      <c r="H18" s="216" t="s">
         <v>6</v>
       </c>
-      <c r="I18" s="180"/>
-      <c r="J18" s="181" t="str">
+      <c r="I18" s="216"/>
+      <c r="J18" s="217" t="str">
         <f>VLOOKUP($F$16,Controle!R3:W16,6,FALSE)</f>
         <v>SÃO PAULO / SP</v>
       </c>
-      <c r="K18" s="182"/>
+      <c r="K18" s="218"/>
       <c r="L18" s="17"/>
     </row>
     <row r="19" spans="1:256" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7382,54 +7382,54 @@
       <c r="E19" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="183" t="str">
+      <c r="F19" s="210" t="str">
         <f>VLOOKUP($F$16,Controle!R3:W16,5,FALSE)</f>
         <v>11-3775 5101</v>
       </c>
-      <c r="G19" s="184"/>
-      <c r="H19" s="185" t="s">
+      <c r="G19" s="219"/>
+      <c r="H19" s="220" t="s">
         <v>5</v>
       </c>
-      <c r="I19" s="186"/>
-      <c r="J19" s="187" t="str">
+      <c r="I19" s="221"/>
+      <c r="J19" s="222" t="str">
         <f>VLOOKUP($F$15,Controle!R20:U54,2,FALSE)</f>
         <v>viviane.ferrari@sgb.gov.br</v>
       </c>
-      <c r="K19" s="188"/>
+      <c r="K19" s="223"/>
       <c r="L19" s="17"/>
     </row>
     <row r="20" spans="1:256" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="18"/>
-      <c r="B20" s="194" t="s">
+      <c r="B20" s="191" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="195"/>
-      <c r="D20" s="195"/>
-      <c r="E20" s="195"/>
-      <c r="F20" s="195"/>
-      <c r="G20" s="195"/>
-      <c r="H20" s="195"/>
-      <c r="I20" s="195"/>
-      <c r="J20" s="195"/>
-      <c r="K20" s="196"/>
+      <c r="C20" s="192"/>
+      <c r="D20" s="192"/>
+      <c r="E20" s="192"/>
+      <c r="F20" s="192"/>
+      <c r="G20" s="192"/>
+      <c r="H20" s="192"/>
+      <c r="I20" s="192"/>
+      <c r="J20" s="192"/>
+      <c r="K20" s="193"/>
       <c r="L20" s="17"/>
     </row>
     <row r="21" spans="1:256" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18"/>
       <c r="B21" s="23"/>
       <c r="C21" s="15"/>
-      <c r="D21" s="197" t="s">
+      <c r="D21" s="194" t="s">
         <v>0</v>
       </c>
-      <c r="E21" s="197"/>
-      <c r="F21" s="198" t="s">
+      <c r="E21" s="194"/>
+      <c r="F21" s="195" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="199"/>
-      <c r="H21" s="199"/>
-      <c r="I21" s="199"/>
-      <c r="J21" s="199"/>
-      <c r="K21" s="200"/>
+      <c r="G21" s="196"/>
+      <c r="H21" s="196"/>
+      <c r="I21" s="196"/>
+      <c r="J21" s="196"/>
+      <c r="K21" s="197"/>
       <c r="L21" s="17"/>
     </row>
     <row r="22" spans="1:256" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7440,14 +7440,14 @@
       <c r="E22" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="F22" s="201" t="s">
+      <c r="F22" s="198" t="s">
         <v>699</v>
       </c>
-      <c r="G22" s="202"/>
-      <c r="H22" s="202"/>
-      <c r="I22" s="202"/>
-      <c r="J22" s="202"/>
-      <c r="K22" s="203"/>
+      <c r="G22" s="199"/>
+      <c r="H22" s="199"/>
+      <c r="I22" s="199"/>
+      <c r="J22" s="199"/>
+      <c r="K22" s="200"/>
       <c r="L22" s="17"/>
     </row>
     <row r="23" spans="1:256" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7458,15 +7458,15 @@
       <c r="E23" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="F23" s="204" t="s">
+      <c r="F23" s="201" t="s">
         <v>706</v>
       </c>
-      <c r="G23" s="205"/>
-      <c r="H23" s="206"/>
-      <c r="I23" s="207" t="s">
+      <c r="G23" s="202"/>
+      <c r="H23" s="203"/>
+      <c r="I23" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="J23" s="207"/>
+      <c r="J23" s="204"/>
       <c r="K23" s="108" t="s">
         <v>707</v>
       </c>
@@ -7480,15 +7480,15 @@
       <c r="E24" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="178" t="s">
+      <c r="F24" s="205" t="s">
         <v>444</v>
       </c>
-      <c r="G24" s="208"/>
-      <c r="H24" s="179"/>
-      <c r="I24" s="209" t="s">
+      <c r="G24" s="206"/>
+      <c r="H24" s="207"/>
+      <c r="I24" s="208" t="s">
         <v>7</v>
       </c>
-      <c r="J24" s="210"/>
+      <c r="J24" s="209"/>
       <c r="K24" s="108" t="s">
         <v>544</v>
       </c>
@@ -7502,7 +7502,7 @@
       <c r="E25" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="F25" s="183" t="s">
+      <c r="F25" s="210" t="s">
         <v>545</v>
       </c>
       <c r="G25" s="211"/>
@@ -7519,18 +7519,18 @@
     </row>
     <row r="26" spans="1:256" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18"/>
-      <c r="B26" s="215" t="s">
+      <c r="B26" s="153" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="216"/>
-      <c r="D26" s="216"/>
-      <c r="E26" s="217"/>
-      <c r="F26" s="217"/>
-      <c r="G26" s="217"/>
-      <c r="H26" s="217"/>
-      <c r="I26" s="217"/>
-      <c r="J26" s="217"/>
-      <c r="K26" s="218"/>
+      <c r="C26" s="215"/>
+      <c r="D26" s="215"/>
+      <c r="E26" s="154"/>
+      <c r="F26" s="154"/>
+      <c r="G26" s="154"/>
+      <c r="H26" s="154"/>
+      <c r="I26" s="154"/>
+      <c r="J26" s="154"/>
+      <c r="K26" s="155"/>
       <c r="L26" s="17"/>
     </row>
     <row r="27" spans="1:256" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7538,10 +7538,10 @@
       <c r="B27" s="52" t="s">
         <v>525</v>
       </c>
-      <c r="C27" s="189" t="s">
+      <c r="C27" s="186" t="s">
         <v>239</v>
       </c>
-      <c r="D27" s="190"/>
+      <c r="D27" s="187"/>
       <c r="E27" s="43" t="s">
         <v>700</v>
       </c>
@@ -7550,11 +7550,11 @@
       <c r="H27" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="I27" s="191" t="s">
+      <c r="I27" s="188" t="s">
         <v>784</v>
       </c>
-      <c r="J27" s="192"/>
-      <c r="K27" s="193"/>
+      <c r="J27" s="189"/>
+      <c r="K27" s="190"/>
       <c r="L27" s="17"/>
     </row>
     <row r="28" spans="1:256" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7562,19 +7562,19 @@
       <c r="B28" s="53" t="s">
         <v>526</v>
       </c>
-      <c r="C28" s="222" t="s">
+      <c r="C28" s="159" t="s">
         <v>436</v>
       </c>
-      <c r="D28" s="223"/>
-      <c r="E28" s="224"/>
-      <c r="F28" s="224"/>
-      <c r="G28" s="225"/>
+      <c r="D28" s="160"/>
+      <c r="E28" s="161"/>
+      <c r="F28" s="161"/>
+      <c r="G28" s="162"/>
       <c r="H28" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="I28" s="226"/>
-      <c r="J28" s="227"/>
-      <c r="K28" s="228"/>
+      <c r="I28" s="163"/>
+      <c r="J28" s="164"/>
+      <c r="K28" s="165"/>
       <c r="L28" s="17"/>
     </row>
     <row r="29" spans="1:256" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7582,19 +7582,19 @@
       <c r="B29" s="52" t="s">
         <v>527</v>
       </c>
-      <c r="C29" s="222" t="s">
+      <c r="C29" s="159" t="s">
         <v>240</v>
       </c>
-      <c r="D29" s="223"/>
-      <c r="E29" s="227"/>
-      <c r="F29" s="227"/>
-      <c r="G29" s="229"/>
+      <c r="D29" s="160"/>
+      <c r="E29" s="164"/>
+      <c r="F29" s="164"/>
+      <c r="G29" s="166"/>
       <c r="H29" s="57" t="s">
         <v>241</v>
       </c>
-      <c r="I29" s="230"/>
-      <c r="J29" s="231"/>
-      <c r="K29" s="232"/>
+      <c r="I29" s="167"/>
+      <c r="J29" s="168"/>
+      <c r="K29" s="169"/>
       <c r="L29" s="17"/>
     </row>
     <row r="30" spans="1:256" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7602,123 +7602,123 @@
       <c r="B30" s="54" t="s">
         <v>528</v>
       </c>
-      <c r="C30" s="233" t="s">
+      <c r="C30" s="170" t="s">
         <v>243</v>
       </c>
-      <c r="D30" s="234"/>
-      <c r="E30" s="235" t="s">
+      <c r="D30" s="171"/>
+      <c r="E30" s="172" t="s">
         <v>797</v>
       </c>
-      <c r="F30" s="235"/>
-      <c r="G30" s="236"/>
+      <c r="F30" s="172"/>
+      <c r="G30" s="173"/>
       <c r="H30" s="58" t="s">
         <v>242</v>
       </c>
-      <c r="I30" s="235"/>
-      <c r="J30" s="235"/>
-      <c r="K30" s="237"/>
+      <c r="I30" s="172"/>
+      <c r="J30" s="172"/>
+      <c r="K30" s="174"/>
       <c r="L30" s="17"/>
     </row>
     <row r="31" spans="1:256" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="18"/>
-      <c r="B31" s="219" t="s">
+      <c r="B31" s="156" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="238"/>
-      <c r="D31" s="238"/>
-      <c r="E31" s="220"/>
-      <c r="F31" s="220"/>
-      <c r="G31" s="220"/>
-      <c r="H31" s="220"/>
-      <c r="I31" s="220"/>
-      <c r="J31" s="220"/>
-      <c r="K31" s="239"/>
+      <c r="C31" s="175"/>
+      <c r="D31" s="175"/>
+      <c r="E31" s="157"/>
+      <c r="F31" s="157"/>
+      <c r="G31" s="157"/>
+      <c r="H31" s="157"/>
+      <c r="I31" s="157"/>
+      <c r="J31" s="157"/>
+      <c r="K31" s="176"/>
       <c r="L31" s="17"/>
     </row>
     <row r="32" spans="1:256" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="18"/>
-      <c r="B32" s="240" t="s">
+      <c r="B32" s="177" t="s">
         <v>787</v>
       </c>
-      <c r="C32" s="241"/>
-      <c r="D32" s="241"/>
-      <c r="E32" s="241"/>
-      <c r="F32" s="241"/>
-      <c r="G32" s="241"/>
-      <c r="H32" s="241"/>
-      <c r="I32" s="241"/>
-      <c r="J32" s="241"/>
-      <c r="K32" s="242"/>
+      <c r="C32" s="178"/>
+      <c r="D32" s="178"/>
+      <c r="E32" s="178"/>
+      <c r="F32" s="178"/>
+      <c r="G32" s="178"/>
+      <c r="H32" s="178"/>
+      <c r="I32" s="178"/>
+      <c r="J32" s="178"/>
+      <c r="K32" s="179"/>
       <c r="L32" s="17"/>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="18"/>
-      <c r="B33" s="243"/>
-      <c r="C33" s="244"/>
-      <c r="D33" s="244"/>
-      <c r="E33" s="244"/>
-      <c r="F33" s="244"/>
-      <c r="G33" s="244"/>
-      <c r="H33" s="244"/>
-      <c r="I33" s="244"/>
-      <c r="J33" s="244"/>
-      <c r="K33" s="245"/>
+      <c r="B33" s="180"/>
+      <c r="C33" s="181"/>
+      <c r="D33" s="181"/>
+      <c r="E33" s="181"/>
+      <c r="F33" s="181"/>
+      <c r="G33" s="181"/>
+      <c r="H33" s="181"/>
+      <c r="I33" s="181"/>
+      <c r="J33" s="181"/>
+      <c r="K33" s="182"/>
       <c r="L33" s="17"/>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="18"/>
-      <c r="B34" s="243"/>
-      <c r="C34" s="244"/>
-      <c r="D34" s="244"/>
-      <c r="E34" s="244"/>
-      <c r="F34" s="244"/>
-      <c r="G34" s="244"/>
-      <c r="H34" s="244"/>
-      <c r="I34" s="244"/>
-      <c r="J34" s="244"/>
-      <c r="K34" s="245"/>
+      <c r="B34" s="180"/>
+      <c r="C34" s="181"/>
+      <c r="D34" s="181"/>
+      <c r="E34" s="181"/>
+      <c r="F34" s="181"/>
+      <c r="G34" s="181"/>
+      <c r="H34" s="181"/>
+      <c r="I34" s="181"/>
+      <c r="J34" s="181"/>
+      <c r="K34" s="182"/>
       <c r="L34" s="17"/>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="18"/>
-      <c r="B35" s="243"/>
-      <c r="C35" s="244"/>
-      <c r="D35" s="244"/>
-      <c r="E35" s="244"/>
-      <c r="F35" s="244"/>
-      <c r="G35" s="244"/>
-      <c r="H35" s="244"/>
-      <c r="I35" s="244"/>
-      <c r="J35" s="244"/>
-      <c r="K35" s="245"/>
+      <c r="B35" s="180"/>
+      <c r="C35" s="181"/>
+      <c r="D35" s="181"/>
+      <c r="E35" s="181"/>
+      <c r="F35" s="181"/>
+      <c r="G35" s="181"/>
+      <c r="H35" s="181"/>
+      <c r="I35" s="181"/>
+      <c r="J35" s="181"/>
+      <c r="K35" s="182"/>
       <c r="L35" s="17"/>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="18"/>
-      <c r="B36" s="243"/>
-      <c r="C36" s="244"/>
-      <c r="D36" s="244"/>
-      <c r="E36" s="244"/>
-      <c r="F36" s="244"/>
-      <c r="G36" s="244"/>
-      <c r="H36" s="244"/>
-      <c r="I36" s="244"/>
-      <c r="J36" s="244"/>
-      <c r="K36" s="245"/>
+      <c r="B36" s="180"/>
+      <c r="C36" s="181"/>
+      <c r="D36" s="181"/>
+      <c r="E36" s="181"/>
+      <c r="F36" s="181"/>
+      <c r="G36" s="181"/>
+      <c r="H36" s="181"/>
+      <c r="I36" s="181"/>
+      <c r="J36" s="181"/>
+      <c r="K36" s="182"/>
       <c r="L36" s="17"/>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="18"/>
-      <c r="B37" s="246"/>
-      <c r="C37" s="247"/>
-      <c r="D37" s="247"/>
-      <c r="E37" s="247"/>
-      <c r="F37" s="247"/>
-      <c r="G37" s="247"/>
-      <c r="H37" s="247"/>
-      <c r="I37" s="247"/>
-      <c r="J37" s="247"/>
-      <c r="K37" s="248"/>
+      <c r="B37" s="183"/>
+      <c r="C37" s="184"/>
+      <c r="D37" s="184"/>
+      <c r="E37" s="184"/>
+      <c r="F37" s="184"/>
+      <c r="G37" s="184"/>
+      <c r="H37" s="184"/>
+      <c r="I37" s="184"/>
+      <c r="J37" s="184"/>
+      <c r="K37" s="185"/>
       <c r="L37" s="17"/>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7738,36 +7738,36 @@
     <row r="39" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="15"/>
       <c r="B39" s="15"/>
-      <c r="C39" s="215" t="s">
+      <c r="C39" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="D39" s="217"/>
-      <c r="E39" s="217"/>
-      <c r="F39" s="217"/>
-      <c r="G39" s="218"/>
+      <c r="D39" s="154"/>
+      <c r="E39" s="154"/>
+      <c r="F39" s="154"/>
+      <c r="G39" s="155"/>
       <c r="H39" s="18"/>
-      <c r="I39" s="219" t="s">
+      <c r="I39" s="156" t="s">
         <v>75</v>
       </c>
-      <c r="J39" s="220"/>
-      <c r="K39" s="221"/>
+      <c r="J39" s="157"/>
+      <c r="K39" s="158"/>
       <c r="L39" s="17"/>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="15"/>
       <c r="B40" s="15"/>
-      <c r="C40" s="249" t="s">
+      <c r="C40" s="138" t="s">
         <v>19</v>
       </c>
-      <c r="D40" s="250"/>
-      <c r="E40" s="250"/>
-      <c r="F40" s="250"/>
-      <c r="G40" s="251"/>
+      <c r="D40" s="139"/>
+      <c r="E40" s="139"/>
+      <c r="F40" s="139"/>
+      <c r="G40" s="140"/>
       <c r="H40" s="18"/>
-      <c r="I40" s="252" t="s">
+      <c r="I40" s="149" t="s">
         <v>23</v>
       </c>
-      <c r="J40" s="253"/>
+      <c r="J40" s="151"/>
       <c r="K40" s="49">
         <f>DadosAmostras!L110</f>
         <v>50</v>
@@ -7777,20 +7777,20 @@
     <row r="41" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="15"/>
       <c r="B41" s="15"/>
-      <c r="C41" s="249" t="s">
+      <c r="C41" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="251"/>
+      <c r="D41" s="140"/>
       <c r="E41" s="27"/>
       <c r="F41" s="28" t="s">
         <v>15</v>
       </c>
       <c r="G41" s="27"/>
       <c r="H41" s="15"/>
-      <c r="I41" s="252" t="s">
+      <c r="I41" s="149" t="s">
         <v>581</v>
       </c>
-      <c r="J41" s="254"/>
+      <c r="J41" s="152"/>
       <c r="K41" s="134" t="str">
         <f>IFERROR(VLOOKUP(K42,Controle!E2:F131,2,FALSE),"")</f>
         <v>Geologia e Potencial Mineral do Sudeste do Paraná</v>
@@ -7800,20 +7800,20 @@
     <row r="42" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="15"/>
       <c r="B42" s="15"/>
-      <c r="C42" s="249" t="s">
+      <c r="C42" s="138" t="s">
         <v>11</v>
       </c>
-      <c r="D42" s="251"/>
+      <c r="D42" s="140"/>
       <c r="E42" s="15"/>
       <c r="F42" s="29" t="s">
         <v>16</v>
       </c>
       <c r="G42" s="27"/>
       <c r="H42" s="15"/>
-      <c r="I42" s="252" t="s">
+      <c r="I42" s="149" t="s">
         <v>57</v>
       </c>
-      <c r="J42" s="253"/>
+      <c r="J42" s="151"/>
       <c r="K42" s="50" t="s">
         <v>803</v>
       </c>
@@ -7822,36 +7822,36 @@
     <row r="43" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="15"/>
       <c r="B43" s="15"/>
-      <c r="C43" s="249" t="s">
+      <c r="C43" s="138" t="s">
         <v>17</v>
       </c>
-      <c r="D43" s="250"/>
-      <c r="E43" s="250"/>
-      <c r="F43" s="250"/>
-      <c r="G43" s="251"/>
+      <c r="D43" s="139"/>
+      <c r="E43" s="139"/>
+      <c r="F43" s="139"/>
+      <c r="G43" s="140"/>
       <c r="H43" s="15"/>
-      <c r="I43" s="252" t="s">
+      <c r="I43" s="149" t="s">
         <v>58</v>
       </c>
-      <c r="J43" s="255"/>
+      <c r="J43" s="150"/>
       <c r="K43" s="46"/>
       <c r="L43" s="42"/>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="15"/>
       <c r="B44" s="15"/>
-      <c r="C44" s="249" t="s">
+      <c r="C44" s="138" t="s">
         <v>12</v>
       </c>
-      <c r="D44" s="250"/>
-      <c r="E44" s="250"/>
-      <c r="F44" s="250"/>
-      <c r="G44" s="251"/>
+      <c r="D44" s="139"/>
+      <c r="E44" s="139"/>
+      <c r="F44" s="139"/>
+      <c r="G44" s="140"/>
       <c r="H44" s="15"/>
-      <c r="I44" s="252" t="s">
+      <c r="I44" s="149" t="s">
         <v>59</v>
       </c>
-      <c r="J44" s="253"/>
+      <c r="J44" s="151"/>
       <c r="K44" s="59" t="s">
         <v>616</v>
       </c>
@@ -7860,71 +7860,71 @@
     <row r="45" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="15"/>
       <c r="B45" s="15"/>
-      <c r="C45" s="249" t="s">
+      <c r="C45" s="138" t="s">
         <v>13</v>
       </c>
-      <c r="D45" s="250"/>
-      <c r="E45" s="250"/>
-      <c r="F45" s="250"/>
-      <c r="G45" s="251"/>
+      <c r="D45" s="139"/>
+      <c r="E45" s="139"/>
+      <c r="F45" s="139"/>
+      <c r="G45" s="140"/>
       <c r="H45" s="15"/>
-      <c r="I45" s="252" t="s">
+      <c r="I45" s="149" t="s">
         <v>244</v>
       </c>
-      <c r="J45" s="253"/>
+      <c r="J45" s="151"/>
       <c r="K45" s="47"/>
       <c r="L45" s="17"/>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="15"/>
       <c r="B46" s="15"/>
-      <c r="C46" s="249" t="s">
+      <c r="C46" s="138" t="s">
         <v>14</v>
       </c>
-      <c r="D46" s="250"/>
-      <c r="E46" s="250"/>
-      <c r="F46" s="250"/>
-      <c r="G46" s="251"/>
+      <c r="D46" s="139"/>
+      <c r="E46" s="139"/>
+      <c r="F46" s="139"/>
+      <c r="G46" s="140"/>
       <c r="H46" s="15"/>
-      <c r="I46" s="256" t="s">
+      <c r="I46" s="141" t="s">
         <v>60</v>
       </c>
-      <c r="J46" s="257"/>
+      <c r="J46" s="142"/>
       <c r="K46" s="48"/>
       <c r="L46" s="17"/>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="15"/>
       <c r="B47" s="15"/>
-      <c r="C47" s="249" t="s">
+      <c r="C47" s="138" t="s">
         <v>18</v>
       </c>
-      <c r="D47" s="250"/>
-      <c r="E47" s="250"/>
-      <c r="F47" s="250"/>
-      <c r="G47" s="251"/>
+      <c r="D47" s="139"/>
+      <c r="E47" s="139"/>
+      <c r="F47" s="139"/>
+      <c r="G47" s="140"/>
       <c r="H47" s="15"/>
-      <c r="I47" s="258" t="s">
+      <c r="I47" s="143" t="s">
         <v>523</v>
       </c>
-      <c r="J47" s="259"/>
-      <c r="K47" s="262"/>
+      <c r="J47" s="144"/>
+      <c r="K47" s="147"/>
       <c r="L47" s="17"/>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="15"/>
       <c r="B48" s="15"/>
-      <c r="C48" s="249" t="s">
+      <c r="C48" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="D48" s="250"/>
-      <c r="E48" s="250"/>
-      <c r="F48" s="250"/>
-      <c r="G48" s="251"/>
+      <c r="D48" s="139"/>
+      <c r="E48" s="139"/>
+      <c r="F48" s="139"/>
+      <c r="G48" s="140"/>
       <c r="H48" s="15"/>
-      <c r="I48" s="260"/>
-      <c r="J48" s="261"/>
-      <c r="K48" s="263"/>
+      <c r="I48" s="145"/>
+      <c r="J48" s="146"/>
+      <c r="K48" s="148"/>
       <c r="L48" s="17"/>
     </row>
     <row r="49" spans="1:12" s="3" customFormat="1" ht="13.2" hidden="1" x14ac:dyDescent="0.25">
@@ -8017,24 +8017,43 @@
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0"/>
   <dataConsolidate/>
   <mergeCells count="68">
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="C47:G47"/>
-    <mergeCell ref="I47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="C43:G43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="C44:G44"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="C45:G45"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="C40:G40"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="F17:K17"/>
+    <mergeCell ref="B8:K8"/>
+    <mergeCell ref="B9:K9"/>
+    <mergeCell ref="B10:K10"/>
+    <mergeCell ref="B11:K11"/>
+    <mergeCell ref="B12:K12"/>
+    <mergeCell ref="B13:K13"/>
+    <mergeCell ref="B14:K14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="F15:K15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:K16"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="B20:K20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:K21"/>
+    <mergeCell ref="F22:K22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="B26:K26"/>
     <mergeCell ref="C39:G39"/>
     <mergeCell ref="I39:K39"/>
     <mergeCell ref="C28:D28"/>
@@ -8048,43 +8067,24 @@
     <mergeCell ref="I30:K30"/>
     <mergeCell ref="B31:K31"/>
     <mergeCell ref="B32:K37"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="B20:K20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:K21"/>
-    <mergeCell ref="F22:K22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="B26:K26"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="F17:K17"/>
-    <mergeCell ref="B8:K8"/>
-    <mergeCell ref="B9:K9"/>
-    <mergeCell ref="B10:K10"/>
-    <mergeCell ref="B11:K11"/>
-    <mergeCell ref="B12:K12"/>
-    <mergeCell ref="B13:K13"/>
-    <mergeCell ref="B14:K14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="F15:K15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:K16"/>
-    <mergeCell ref="B7:K7"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="C47:G47"/>
+    <mergeCell ref="I47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="C48:G48"/>
   </mergeCells>
   <dataValidations xWindow="44" yWindow="410" count="3">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="Não autorizado para o envio de amostras" promptTitle="Responsáveis autorizados" prompt="Responsáveis autorizados para o envio de amostras" sqref="WVI983056:WVN983056 IW15:JB15 SS15:SX15 ACO15:ACT15 AMK15:AMP15 AWG15:AWL15 BGC15:BGH15 BPY15:BQD15 BZU15:BZZ15 CJQ15:CJV15 CTM15:CTR15 DDI15:DDN15 DNE15:DNJ15 DXA15:DXF15 EGW15:EHB15 EQS15:EQX15 FAO15:FAT15 FKK15:FKP15 FUG15:FUL15 GEC15:GEH15 GNY15:GOD15 GXU15:GXZ15 HHQ15:HHV15 HRM15:HRR15 IBI15:IBN15 ILE15:ILJ15 IVA15:IVF15 JEW15:JFB15 JOS15:JOX15 JYO15:JYT15 KIK15:KIP15 KSG15:KSL15 LCC15:LCH15 LLY15:LMD15 LVU15:LVZ15 MFQ15:MFV15 MPM15:MPR15 MZI15:MZN15 NJE15:NJJ15 NTA15:NTF15 OCW15:ODB15 OMS15:OMX15 OWO15:OWT15 PGK15:PGP15 PQG15:PQL15 QAC15:QAH15 QJY15:QKD15 QTU15:QTZ15 RDQ15:RDV15 RNM15:RNR15 RXI15:RXN15 SHE15:SHJ15 SRA15:SRF15 TAW15:TBB15 TKS15:TKX15 TUO15:TUT15 UEK15:UEP15 UOG15:UOL15 UYC15:UYH15 VHY15:VID15 VRU15:VRZ15 WBQ15:WBV15 WLM15:WLR15 WVI15:WVN15 F65552:K65552 IW65552:JB65552 SS65552:SX65552 ACO65552:ACT65552 AMK65552:AMP65552 AWG65552:AWL65552 BGC65552:BGH65552 BPY65552:BQD65552 BZU65552:BZZ65552 CJQ65552:CJV65552 CTM65552:CTR65552 DDI65552:DDN65552 DNE65552:DNJ65552 DXA65552:DXF65552 EGW65552:EHB65552 EQS65552:EQX65552 FAO65552:FAT65552 FKK65552:FKP65552 FUG65552:FUL65552 GEC65552:GEH65552 GNY65552:GOD65552 GXU65552:GXZ65552 HHQ65552:HHV65552 HRM65552:HRR65552 IBI65552:IBN65552 ILE65552:ILJ65552 IVA65552:IVF65552 JEW65552:JFB65552 JOS65552:JOX65552 JYO65552:JYT65552 KIK65552:KIP65552 KSG65552:KSL65552 LCC65552:LCH65552 LLY65552:LMD65552 LVU65552:LVZ65552 MFQ65552:MFV65552 MPM65552:MPR65552 MZI65552:MZN65552 NJE65552:NJJ65552 NTA65552:NTF65552 OCW65552:ODB65552 OMS65552:OMX65552 OWO65552:OWT65552 PGK65552:PGP65552 PQG65552:PQL65552 QAC65552:QAH65552 QJY65552:QKD65552 QTU65552:QTZ65552 RDQ65552:RDV65552 RNM65552:RNR65552 RXI65552:RXN65552 SHE65552:SHJ65552 SRA65552:SRF65552 TAW65552:TBB65552 TKS65552:TKX65552 TUO65552:TUT65552 UEK65552:UEP65552 UOG65552:UOL65552 UYC65552:UYH65552 VHY65552:VID65552 VRU65552:VRZ65552 WBQ65552:WBV65552 WLM65552:WLR65552 WVI65552:WVN65552 F131088:K131088 IW131088:JB131088 SS131088:SX131088 ACO131088:ACT131088 AMK131088:AMP131088 AWG131088:AWL131088 BGC131088:BGH131088 BPY131088:BQD131088 BZU131088:BZZ131088 CJQ131088:CJV131088 CTM131088:CTR131088 DDI131088:DDN131088 DNE131088:DNJ131088 DXA131088:DXF131088 EGW131088:EHB131088 EQS131088:EQX131088 FAO131088:FAT131088 FKK131088:FKP131088 FUG131088:FUL131088 GEC131088:GEH131088 GNY131088:GOD131088 GXU131088:GXZ131088 HHQ131088:HHV131088 HRM131088:HRR131088 IBI131088:IBN131088 ILE131088:ILJ131088 IVA131088:IVF131088 JEW131088:JFB131088 JOS131088:JOX131088 JYO131088:JYT131088 KIK131088:KIP131088 KSG131088:KSL131088 LCC131088:LCH131088 LLY131088:LMD131088 LVU131088:LVZ131088 MFQ131088:MFV131088 MPM131088:MPR131088 MZI131088:MZN131088 NJE131088:NJJ131088 NTA131088:NTF131088 OCW131088:ODB131088 OMS131088:OMX131088 OWO131088:OWT131088 PGK131088:PGP131088 PQG131088:PQL131088 QAC131088:QAH131088 QJY131088:QKD131088 QTU131088:QTZ131088 RDQ131088:RDV131088 RNM131088:RNR131088 RXI131088:RXN131088 SHE131088:SHJ131088 SRA131088:SRF131088 TAW131088:TBB131088 TKS131088:TKX131088 TUO131088:TUT131088 UEK131088:UEP131088 UOG131088:UOL131088 UYC131088:UYH131088 VHY131088:VID131088 VRU131088:VRZ131088 WBQ131088:WBV131088 WLM131088:WLR131088 WVI131088:WVN131088 F196624:K196624 IW196624:JB196624 SS196624:SX196624 ACO196624:ACT196624 AMK196624:AMP196624 AWG196624:AWL196624 BGC196624:BGH196624 BPY196624:BQD196624 BZU196624:BZZ196624 CJQ196624:CJV196624 CTM196624:CTR196624 DDI196624:DDN196624 DNE196624:DNJ196624 DXA196624:DXF196624 EGW196624:EHB196624 EQS196624:EQX196624 FAO196624:FAT196624 FKK196624:FKP196624 FUG196624:FUL196624 GEC196624:GEH196624 GNY196624:GOD196624 GXU196624:GXZ196624 HHQ196624:HHV196624 HRM196624:HRR196624 IBI196624:IBN196624 ILE196624:ILJ196624 IVA196624:IVF196624 JEW196624:JFB196624 JOS196624:JOX196624 JYO196624:JYT196624 KIK196624:KIP196624 KSG196624:KSL196624 LCC196624:LCH196624 LLY196624:LMD196624 LVU196624:LVZ196624 MFQ196624:MFV196624 MPM196624:MPR196624 MZI196624:MZN196624 NJE196624:NJJ196624 NTA196624:NTF196624 OCW196624:ODB196624 OMS196624:OMX196624 OWO196624:OWT196624 PGK196624:PGP196624 PQG196624:PQL196624 QAC196624:QAH196624 QJY196624:QKD196624 QTU196624:QTZ196624 RDQ196624:RDV196624 RNM196624:RNR196624 RXI196624:RXN196624 SHE196624:SHJ196624 SRA196624:SRF196624 TAW196624:TBB196624 TKS196624:TKX196624 TUO196624:TUT196624 UEK196624:UEP196624 UOG196624:UOL196624 UYC196624:UYH196624 VHY196624:VID196624 VRU196624:VRZ196624 WBQ196624:WBV196624 WLM196624:WLR196624 WVI196624:WVN196624 F262160:K262160 IW262160:JB262160 SS262160:SX262160 ACO262160:ACT262160 AMK262160:AMP262160 AWG262160:AWL262160 BGC262160:BGH262160 BPY262160:BQD262160 BZU262160:BZZ262160 CJQ262160:CJV262160 CTM262160:CTR262160 DDI262160:DDN262160 DNE262160:DNJ262160 DXA262160:DXF262160 EGW262160:EHB262160 EQS262160:EQX262160 FAO262160:FAT262160 FKK262160:FKP262160 FUG262160:FUL262160 GEC262160:GEH262160 GNY262160:GOD262160 GXU262160:GXZ262160 HHQ262160:HHV262160 HRM262160:HRR262160 IBI262160:IBN262160 ILE262160:ILJ262160 IVA262160:IVF262160 JEW262160:JFB262160 JOS262160:JOX262160 JYO262160:JYT262160 KIK262160:KIP262160 KSG262160:KSL262160 LCC262160:LCH262160 LLY262160:LMD262160 LVU262160:LVZ262160 MFQ262160:MFV262160 MPM262160:MPR262160 MZI262160:MZN262160 NJE262160:NJJ262160 NTA262160:NTF262160 OCW262160:ODB262160 OMS262160:OMX262160 OWO262160:OWT262160 PGK262160:PGP262160 PQG262160:PQL262160 QAC262160:QAH262160 QJY262160:QKD262160 QTU262160:QTZ262160 RDQ262160:RDV262160 RNM262160:RNR262160 RXI262160:RXN262160 SHE262160:SHJ262160 SRA262160:SRF262160 TAW262160:TBB262160 TKS262160:TKX262160 TUO262160:TUT262160 UEK262160:UEP262160 UOG262160:UOL262160 UYC262160:UYH262160 VHY262160:VID262160 VRU262160:VRZ262160 WBQ262160:WBV262160 WLM262160:WLR262160 WVI262160:WVN262160 F327696:K327696 IW327696:JB327696 SS327696:SX327696 ACO327696:ACT327696 AMK327696:AMP327696 AWG327696:AWL327696 BGC327696:BGH327696 BPY327696:BQD327696 BZU327696:BZZ327696 CJQ327696:CJV327696 CTM327696:CTR327696 DDI327696:DDN327696 DNE327696:DNJ327696 DXA327696:DXF327696 EGW327696:EHB327696 EQS327696:EQX327696 FAO327696:FAT327696 FKK327696:FKP327696 FUG327696:FUL327696 GEC327696:GEH327696 GNY327696:GOD327696 GXU327696:GXZ327696 HHQ327696:HHV327696 HRM327696:HRR327696 IBI327696:IBN327696 ILE327696:ILJ327696 IVA327696:IVF327696 JEW327696:JFB327696 JOS327696:JOX327696 JYO327696:JYT327696 KIK327696:KIP327696 KSG327696:KSL327696 LCC327696:LCH327696 LLY327696:LMD327696 LVU327696:LVZ327696 MFQ327696:MFV327696 MPM327696:MPR327696 MZI327696:MZN327696 NJE327696:NJJ327696 NTA327696:NTF327696 OCW327696:ODB327696 OMS327696:OMX327696 OWO327696:OWT327696 PGK327696:PGP327696 PQG327696:PQL327696 QAC327696:QAH327696 QJY327696:QKD327696 QTU327696:QTZ327696 RDQ327696:RDV327696 RNM327696:RNR327696 RXI327696:RXN327696 SHE327696:SHJ327696 SRA327696:SRF327696 TAW327696:TBB327696 TKS327696:TKX327696 TUO327696:TUT327696 UEK327696:UEP327696 UOG327696:UOL327696 UYC327696:UYH327696 VHY327696:VID327696 VRU327696:VRZ327696 WBQ327696:WBV327696 WLM327696:WLR327696 WVI327696:WVN327696 F393232:K393232 IW393232:JB393232 SS393232:SX393232 ACO393232:ACT393232 AMK393232:AMP393232 AWG393232:AWL393232 BGC393232:BGH393232 BPY393232:BQD393232 BZU393232:BZZ393232 CJQ393232:CJV393232 CTM393232:CTR393232 DDI393232:DDN393232 DNE393232:DNJ393232 DXA393232:DXF393232 EGW393232:EHB393232 EQS393232:EQX393232 FAO393232:FAT393232 FKK393232:FKP393232 FUG393232:FUL393232 GEC393232:GEH393232 GNY393232:GOD393232 GXU393232:GXZ393232 HHQ393232:HHV393232 HRM393232:HRR393232 IBI393232:IBN393232 ILE393232:ILJ393232 IVA393232:IVF393232 JEW393232:JFB393232 JOS393232:JOX393232 JYO393232:JYT393232 KIK393232:KIP393232 KSG393232:KSL393232 LCC393232:LCH393232 LLY393232:LMD393232 LVU393232:LVZ393232 MFQ393232:MFV393232 MPM393232:MPR393232 MZI393232:MZN393232 NJE393232:NJJ393232 NTA393232:NTF393232 OCW393232:ODB393232 OMS393232:OMX393232 OWO393232:OWT393232 PGK393232:PGP393232 PQG393232:PQL393232 QAC393232:QAH393232 QJY393232:QKD393232 QTU393232:QTZ393232 RDQ393232:RDV393232 RNM393232:RNR393232 RXI393232:RXN393232 SHE393232:SHJ393232 SRA393232:SRF393232 TAW393232:TBB393232 TKS393232:TKX393232 TUO393232:TUT393232 UEK393232:UEP393232 UOG393232:UOL393232 UYC393232:UYH393232 VHY393232:VID393232 VRU393232:VRZ393232 WBQ393232:WBV393232 WLM393232:WLR393232 WVI393232:WVN393232 F458768:K458768 IW458768:JB458768 SS458768:SX458768 ACO458768:ACT458768 AMK458768:AMP458768 AWG458768:AWL458768 BGC458768:BGH458768 BPY458768:BQD458768 BZU458768:BZZ458768 CJQ458768:CJV458768 CTM458768:CTR458768 DDI458768:DDN458768 DNE458768:DNJ458768 DXA458768:DXF458768 EGW458768:EHB458768 EQS458768:EQX458768 FAO458768:FAT458768 FKK458768:FKP458768 FUG458768:FUL458768 GEC458768:GEH458768 GNY458768:GOD458768 GXU458768:GXZ458768 HHQ458768:HHV458768 HRM458768:HRR458768 IBI458768:IBN458768 ILE458768:ILJ458768 IVA458768:IVF458768 JEW458768:JFB458768 JOS458768:JOX458768 JYO458768:JYT458768 KIK458768:KIP458768 KSG458768:KSL458768 LCC458768:LCH458768 LLY458768:LMD458768 LVU458768:LVZ458768 MFQ458768:MFV458768 MPM458768:MPR458768 MZI458768:MZN458768 NJE458768:NJJ458768 NTA458768:NTF458768 OCW458768:ODB458768 OMS458768:OMX458768 OWO458768:OWT458768 PGK458768:PGP458768 PQG458768:PQL458768 QAC458768:QAH458768 QJY458768:QKD458768 QTU458768:QTZ458768 RDQ458768:RDV458768 RNM458768:RNR458768 RXI458768:RXN458768 SHE458768:SHJ458768 SRA458768:SRF458768 TAW458768:TBB458768 TKS458768:TKX458768 TUO458768:TUT458768 UEK458768:UEP458768 UOG458768:UOL458768 UYC458768:UYH458768 VHY458768:VID458768 VRU458768:VRZ458768 WBQ458768:WBV458768 WLM458768:WLR458768 WVI458768:WVN458768 F524304:K524304 IW524304:JB524304 SS524304:SX524304 ACO524304:ACT524304 AMK524304:AMP524304 AWG524304:AWL524304 BGC524304:BGH524304 BPY524304:BQD524304 BZU524304:BZZ524304 CJQ524304:CJV524304 CTM524304:CTR524304 DDI524304:DDN524304 DNE524304:DNJ524304 DXA524304:DXF524304 EGW524304:EHB524304 EQS524304:EQX524304 FAO524304:FAT524304 FKK524304:FKP524304 FUG524304:FUL524304 GEC524304:GEH524304 GNY524304:GOD524304 GXU524304:GXZ524304 HHQ524304:HHV524304 HRM524304:HRR524304 IBI524304:IBN524304 ILE524304:ILJ524304 IVA524304:IVF524304 JEW524304:JFB524304 JOS524304:JOX524304 JYO524304:JYT524304 KIK524304:KIP524304 KSG524304:KSL524304 LCC524304:LCH524304 LLY524304:LMD524304 LVU524304:LVZ524304 MFQ524304:MFV524304 MPM524304:MPR524304 MZI524304:MZN524304 NJE524304:NJJ524304 NTA524304:NTF524304 OCW524304:ODB524304 OMS524304:OMX524304 OWO524304:OWT524304 PGK524304:PGP524304 PQG524304:PQL524304 QAC524304:QAH524304 QJY524304:QKD524304 QTU524304:QTZ524304 RDQ524304:RDV524304 RNM524304:RNR524304 RXI524304:RXN524304 SHE524304:SHJ524304 SRA524304:SRF524304 TAW524304:TBB524304 TKS524304:TKX524304 TUO524304:TUT524304 UEK524304:UEP524304 UOG524304:UOL524304 UYC524304:UYH524304 VHY524304:VID524304 VRU524304:VRZ524304 WBQ524304:WBV524304 WLM524304:WLR524304 WVI524304:WVN524304 F589840:K589840 IW589840:JB589840 SS589840:SX589840 ACO589840:ACT589840 AMK589840:AMP589840 AWG589840:AWL589840 BGC589840:BGH589840 BPY589840:BQD589840 BZU589840:BZZ589840 CJQ589840:CJV589840 CTM589840:CTR589840 DDI589840:DDN589840 DNE589840:DNJ589840 DXA589840:DXF589840 EGW589840:EHB589840 EQS589840:EQX589840 FAO589840:FAT589840 FKK589840:FKP589840 FUG589840:FUL589840 GEC589840:GEH589840 GNY589840:GOD589840 GXU589840:GXZ589840 HHQ589840:HHV589840 HRM589840:HRR589840 IBI589840:IBN589840 ILE589840:ILJ589840 IVA589840:IVF589840 JEW589840:JFB589840 JOS589840:JOX589840 JYO589840:JYT589840 KIK589840:KIP589840 KSG589840:KSL589840 LCC589840:LCH589840 LLY589840:LMD589840 LVU589840:LVZ589840 MFQ589840:MFV589840 MPM589840:MPR589840 MZI589840:MZN589840 NJE589840:NJJ589840 NTA589840:NTF589840 OCW589840:ODB589840 OMS589840:OMX589840 OWO589840:OWT589840 PGK589840:PGP589840 PQG589840:PQL589840 QAC589840:QAH589840 QJY589840:QKD589840 QTU589840:QTZ589840 RDQ589840:RDV589840 RNM589840:RNR589840 RXI589840:RXN589840 SHE589840:SHJ589840 SRA589840:SRF589840 TAW589840:TBB589840 TKS589840:TKX589840 TUO589840:TUT589840 UEK589840:UEP589840 UOG589840:UOL589840 UYC589840:UYH589840 VHY589840:VID589840 VRU589840:VRZ589840 WBQ589840:WBV589840 WLM589840:WLR589840 WVI589840:WVN589840 F655376:K655376 IW655376:JB655376 SS655376:SX655376 ACO655376:ACT655376 AMK655376:AMP655376 AWG655376:AWL655376 BGC655376:BGH655376 BPY655376:BQD655376 BZU655376:BZZ655376 CJQ655376:CJV655376 CTM655376:CTR655376 DDI655376:DDN655376 DNE655376:DNJ655376 DXA655376:DXF655376 EGW655376:EHB655376 EQS655376:EQX655376 FAO655376:FAT655376 FKK655376:FKP655376 FUG655376:FUL655376 GEC655376:GEH655376 GNY655376:GOD655376 GXU655376:GXZ655376 HHQ655376:HHV655376 HRM655376:HRR655376 IBI655376:IBN655376 ILE655376:ILJ655376 IVA655376:IVF655376 JEW655376:JFB655376 JOS655376:JOX655376 JYO655376:JYT655376 KIK655376:KIP655376 KSG655376:KSL655376 LCC655376:LCH655376 LLY655376:LMD655376 LVU655376:LVZ655376 MFQ655376:MFV655376 MPM655376:MPR655376 MZI655376:MZN655376 NJE655376:NJJ655376 NTA655376:NTF655376 OCW655376:ODB655376 OMS655376:OMX655376 OWO655376:OWT655376 PGK655376:PGP655376 PQG655376:PQL655376 QAC655376:QAH655376 QJY655376:QKD655376 QTU655376:QTZ655376 RDQ655376:RDV655376 RNM655376:RNR655376 RXI655376:RXN655376 SHE655376:SHJ655376 SRA655376:SRF655376 TAW655376:TBB655376 TKS655376:TKX655376 TUO655376:TUT655376 UEK655376:UEP655376 UOG655376:UOL655376 UYC655376:UYH655376 VHY655376:VID655376 VRU655376:VRZ655376 WBQ655376:WBV655376 WLM655376:WLR655376 WVI655376:WVN655376 F720912:K720912 IW720912:JB720912 SS720912:SX720912 ACO720912:ACT720912 AMK720912:AMP720912 AWG720912:AWL720912 BGC720912:BGH720912 BPY720912:BQD720912 BZU720912:BZZ720912 CJQ720912:CJV720912 CTM720912:CTR720912 DDI720912:DDN720912 DNE720912:DNJ720912 DXA720912:DXF720912 EGW720912:EHB720912 EQS720912:EQX720912 FAO720912:FAT720912 FKK720912:FKP720912 FUG720912:FUL720912 GEC720912:GEH720912 GNY720912:GOD720912 GXU720912:GXZ720912 HHQ720912:HHV720912 HRM720912:HRR720912 IBI720912:IBN720912 ILE720912:ILJ720912 IVA720912:IVF720912 JEW720912:JFB720912 JOS720912:JOX720912 JYO720912:JYT720912 KIK720912:KIP720912 KSG720912:KSL720912 LCC720912:LCH720912 LLY720912:LMD720912 LVU720912:LVZ720912 MFQ720912:MFV720912 MPM720912:MPR720912 MZI720912:MZN720912 NJE720912:NJJ720912 NTA720912:NTF720912 OCW720912:ODB720912 OMS720912:OMX720912 OWO720912:OWT720912 PGK720912:PGP720912 PQG720912:PQL720912 QAC720912:QAH720912 QJY720912:QKD720912 QTU720912:QTZ720912 RDQ720912:RDV720912 RNM720912:RNR720912 RXI720912:RXN720912 SHE720912:SHJ720912 SRA720912:SRF720912 TAW720912:TBB720912 TKS720912:TKX720912 TUO720912:TUT720912 UEK720912:UEP720912 UOG720912:UOL720912 UYC720912:UYH720912 VHY720912:VID720912 VRU720912:VRZ720912 WBQ720912:WBV720912 WLM720912:WLR720912 WVI720912:WVN720912 F786448:K786448 IW786448:JB786448 SS786448:SX786448 ACO786448:ACT786448 AMK786448:AMP786448 AWG786448:AWL786448 BGC786448:BGH786448 BPY786448:BQD786448 BZU786448:BZZ786448 CJQ786448:CJV786448 CTM786448:CTR786448 DDI786448:DDN786448 DNE786448:DNJ786448 DXA786448:DXF786448 EGW786448:EHB786448 EQS786448:EQX786448 FAO786448:FAT786448 FKK786448:FKP786448 FUG786448:FUL786448 GEC786448:GEH786448 GNY786448:GOD786448 GXU786448:GXZ786448 HHQ786448:HHV786448 HRM786448:HRR786448 IBI786448:IBN786448 ILE786448:ILJ786448 IVA786448:IVF786448 JEW786448:JFB786448 JOS786448:JOX786448 JYO786448:JYT786448 KIK786448:KIP786448 KSG786448:KSL786448 LCC786448:LCH786448 LLY786448:LMD786448 LVU786448:LVZ786448 MFQ786448:MFV786448 MPM786448:MPR786448 MZI786448:MZN786448 NJE786448:NJJ786448 NTA786448:NTF786448 OCW786448:ODB786448 OMS786448:OMX786448 OWO786448:OWT786448 PGK786448:PGP786448 PQG786448:PQL786448 QAC786448:QAH786448 QJY786448:QKD786448 QTU786448:QTZ786448 RDQ786448:RDV786448 RNM786448:RNR786448 RXI786448:RXN786448 SHE786448:SHJ786448 SRA786448:SRF786448 TAW786448:TBB786448 TKS786448:TKX786448 TUO786448:TUT786448 UEK786448:UEP786448 UOG786448:UOL786448 UYC786448:UYH786448 VHY786448:VID786448 VRU786448:VRZ786448 WBQ786448:WBV786448 WLM786448:WLR786448 WVI786448:WVN786448 F851984:K851984 IW851984:JB851984 SS851984:SX851984 ACO851984:ACT851984 AMK851984:AMP851984 AWG851984:AWL851984 BGC851984:BGH851984 BPY851984:BQD851984 BZU851984:BZZ851984 CJQ851984:CJV851984 CTM851984:CTR851984 DDI851984:DDN851984 DNE851984:DNJ851984 DXA851984:DXF851984 EGW851984:EHB851984 EQS851984:EQX851984 FAO851984:FAT851984 FKK851984:FKP851984 FUG851984:FUL851984 GEC851984:GEH851984 GNY851984:GOD851984 GXU851984:GXZ851984 HHQ851984:HHV851984 HRM851984:HRR851984 IBI851984:IBN851984 ILE851984:ILJ851984 IVA851984:IVF851984 JEW851984:JFB851984 JOS851984:JOX851984 JYO851984:JYT851984 KIK851984:KIP851984 KSG851984:KSL851984 LCC851984:LCH851984 LLY851984:LMD851984 LVU851984:LVZ851984 MFQ851984:MFV851984 MPM851984:MPR851984 MZI851984:MZN851984 NJE851984:NJJ851984 NTA851984:NTF851984 OCW851984:ODB851984 OMS851984:OMX851984 OWO851984:OWT851984 PGK851984:PGP851984 PQG851984:PQL851984 QAC851984:QAH851984 QJY851984:QKD851984 QTU851984:QTZ851984 RDQ851984:RDV851984 RNM851984:RNR851984 RXI851984:RXN851984 SHE851984:SHJ851984 SRA851984:SRF851984 TAW851984:TBB851984 TKS851984:TKX851984 TUO851984:TUT851984 UEK851984:UEP851984 UOG851984:UOL851984 UYC851984:UYH851984 VHY851984:VID851984 VRU851984:VRZ851984 WBQ851984:WBV851984 WLM851984:WLR851984 WVI851984:WVN851984 F917520:K917520 IW917520:JB917520 SS917520:SX917520 ACO917520:ACT917520 AMK917520:AMP917520 AWG917520:AWL917520 BGC917520:BGH917520 BPY917520:BQD917520 BZU917520:BZZ917520 CJQ917520:CJV917520 CTM917520:CTR917520 DDI917520:DDN917520 DNE917520:DNJ917520 DXA917520:DXF917520 EGW917520:EHB917520 EQS917520:EQX917520 FAO917520:FAT917520 FKK917520:FKP917520 FUG917520:FUL917520 GEC917520:GEH917520 GNY917520:GOD917520 GXU917520:GXZ917520 HHQ917520:HHV917520 HRM917520:HRR917520 IBI917520:IBN917520 ILE917520:ILJ917520 IVA917520:IVF917520 JEW917520:JFB917520 JOS917520:JOX917520 JYO917520:JYT917520 KIK917520:KIP917520 KSG917520:KSL917520 LCC917520:LCH917520 LLY917520:LMD917520 LVU917520:LVZ917520 MFQ917520:MFV917520 MPM917520:MPR917520 MZI917520:MZN917520 NJE917520:NJJ917520 NTA917520:NTF917520 OCW917520:ODB917520 OMS917520:OMX917520 OWO917520:OWT917520 PGK917520:PGP917520 PQG917520:PQL917520 QAC917520:QAH917520 QJY917520:QKD917520 QTU917520:QTZ917520 RDQ917520:RDV917520 RNM917520:RNR917520 RXI917520:RXN917520 SHE917520:SHJ917520 SRA917520:SRF917520 TAW917520:TBB917520 TKS917520:TKX917520 TUO917520:TUT917520 UEK917520:UEP917520 UOG917520:UOL917520 UYC917520:UYH917520 VHY917520:VID917520 VRU917520:VRZ917520 WBQ917520:WBV917520 WLM917520:WLR917520 WVI917520:WVN917520 F983056:K983056 IW983056:JB983056 SS983056:SX983056 ACO983056:ACT983056 AMK983056:AMP983056 AWG983056:AWL983056 BGC983056:BGH983056 BPY983056:BQD983056 BZU983056:BZZ983056 CJQ983056:CJV983056 CTM983056:CTR983056 DDI983056:DDN983056 DNE983056:DNJ983056 DXA983056:DXF983056 EGW983056:EHB983056 EQS983056:EQX983056 FAO983056:FAT983056 FKK983056:FKP983056 FUG983056:FUL983056 GEC983056:GEH983056 GNY983056:GOD983056 GXU983056:GXZ983056 HHQ983056:HHV983056 HRM983056:HRR983056 IBI983056:IBN983056 ILE983056:ILJ983056 IVA983056:IVF983056 JEW983056:JFB983056 JOS983056:JOX983056 JYO983056:JYT983056 KIK983056:KIP983056 KSG983056:KSL983056 LCC983056:LCH983056 LLY983056:LMD983056 LVU983056:LVZ983056 MFQ983056:MFV983056 MPM983056:MPR983056 MZI983056:MZN983056 NJE983056:NJJ983056 NTA983056:NTF983056 OCW983056:ODB983056 OMS983056:OMX983056 OWO983056:OWT983056 PGK983056:PGP983056 PQG983056:PQL983056 QAC983056:QAH983056 QJY983056:QKD983056 QTU983056:QTZ983056 RDQ983056:RDV983056 RNM983056:RNR983056 RXI983056:RXN983056 SHE983056:SHJ983056 SRA983056:SRF983056 TAW983056:TBB983056 TKS983056:TKX983056 TUO983056:TUT983056 UEK983056:UEP983056 UOG983056:UOL983056 UYC983056:UYH983056 VHY983056:VID983056 VRU983056:VRZ983056 WBQ983056:WBV983056 WLM983056:WLR983056" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -8179,140 +8179,140 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:80" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="267"/>
-      <c r="B1" s="267"/>
-      <c r="C1" s="267"/>
-      <c r="D1" s="267"/>
-      <c r="E1" s="267"/>
-      <c r="F1" s="267"/>
-      <c r="G1" s="267"/>
-      <c r="H1" s="267"/>
-      <c r="I1" s="267"/>
-      <c r="J1" s="267"/>
-      <c r="K1" s="267"/>
-      <c r="L1" s="267"/>
-      <c r="M1" s="267"/>
-      <c r="N1" s="267"/>
-      <c r="O1" s="267"/>
-      <c r="P1" s="267"/>
-      <c r="Q1" s="267"/>
-      <c r="R1" s="267"/>
-      <c r="S1" s="267"/>
-      <c r="T1" s="267"/>
-      <c r="U1" s="267"/>
-      <c r="V1" s="267"/>
-      <c r="W1" s="267"/>
-      <c r="X1" s="267"/>
-      <c r="Y1" s="267"/>
-      <c r="Z1" s="267"/>
-      <c r="AA1" s="267"/>
-      <c r="AB1" s="267"/>
-      <c r="AC1" s="267"/>
-      <c r="AD1" s="267"/>
-      <c r="AE1" s="267"/>
-      <c r="AF1" s="267"/>
-      <c r="AG1" s="267"/>
-      <c r="AH1" s="267"/>
-      <c r="AI1" s="267"/>
-      <c r="AJ1" s="267"/>
-      <c r="AK1" s="267"/>
-      <c r="AL1" s="267"/>
-      <c r="AM1" s="267"/>
-      <c r="AN1" s="267"/>
-      <c r="AO1" s="267"/>
-      <c r="AP1" s="267"/>
-      <c r="AQ1" s="267"/>
-      <c r="AR1" s="267"/>
-      <c r="AS1" s="267"/>
-      <c r="AT1" s="267"/>
-      <c r="AU1" s="267"/>
-      <c r="AV1" s="267"/>
-      <c r="AW1" s="267"/>
-      <c r="AX1" s="267"/>
-      <c r="AY1" s="267"/>
-      <c r="AZ1" s="267"/>
-      <c r="BA1" s="267"/>
-      <c r="BB1" s="267"/>
-      <c r="BC1" s="267"/>
-      <c r="BD1" s="267"/>
-      <c r="BE1" s="267"/>
-      <c r="BF1" s="267"/>
-      <c r="BG1" s="267"/>
-      <c r="BH1" s="267"/>
-      <c r="BI1" s="267"/>
-      <c r="BJ1" s="267"/>
-      <c r="BK1" s="267"/>
-      <c r="BL1" s="267"/>
-      <c r="BM1" s="267"/>
-      <c r="BN1" s="267"/>
-      <c r="BO1" s="267"/>
-      <c r="BP1" s="267"/>
-      <c r="BQ1" s="267"/>
-      <c r="BR1" s="267"/>
-      <c r="BS1" s="267"/>
-      <c r="BT1" s="267"/>
-      <c r="BU1" s="267"/>
-      <c r="BV1" s="267"/>
-      <c r="BW1" s="267"/>
-      <c r="BX1" s="267"/>
-      <c r="BY1" s="267"/>
-      <c r="BZ1" s="267"/>
-      <c r="CA1" s="267"/>
-      <c r="CB1" s="267"/>
+      <c r="A1" s="281"/>
+      <c r="B1" s="281"/>
+      <c r="C1" s="281"/>
+      <c r="D1" s="281"/>
+      <c r="E1" s="281"/>
+      <c r="F1" s="281"/>
+      <c r="G1" s="281"/>
+      <c r="H1" s="281"/>
+      <c r="I1" s="281"/>
+      <c r="J1" s="281"/>
+      <c r="K1" s="281"/>
+      <c r="L1" s="281"/>
+      <c r="M1" s="281"/>
+      <c r="N1" s="281"/>
+      <c r="O1" s="281"/>
+      <c r="P1" s="281"/>
+      <c r="Q1" s="281"/>
+      <c r="R1" s="281"/>
+      <c r="S1" s="281"/>
+      <c r="T1" s="281"/>
+      <c r="U1" s="281"/>
+      <c r="V1" s="281"/>
+      <c r="W1" s="281"/>
+      <c r="X1" s="281"/>
+      <c r="Y1" s="281"/>
+      <c r="Z1" s="281"/>
+      <c r="AA1" s="281"/>
+      <c r="AB1" s="281"/>
+      <c r="AC1" s="281"/>
+      <c r="AD1" s="281"/>
+      <c r="AE1" s="281"/>
+      <c r="AF1" s="281"/>
+      <c r="AG1" s="281"/>
+      <c r="AH1" s="281"/>
+      <c r="AI1" s="281"/>
+      <c r="AJ1" s="281"/>
+      <c r="AK1" s="281"/>
+      <c r="AL1" s="281"/>
+      <c r="AM1" s="281"/>
+      <c r="AN1" s="281"/>
+      <c r="AO1" s="281"/>
+      <c r="AP1" s="281"/>
+      <c r="AQ1" s="281"/>
+      <c r="AR1" s="281"/>
+      <c r="AS1" s="281"/>
+      <c r="AT1" s="281"/>
+      <c r="AU1" s="281"/>
+      <c r="AV1" s="281"/>
+      <c r="AW1" s="281"/>
+      <c r="AX1" s="281"/>
+      <c r="AY1" s="281"/>
+      <c r="AZ1" s="281"/>
+      <c r="BA1" s="281"/>
+      <c r="BB1" s="281"/>
+      <c r="BC1" s="281"/>
+      <c r="BD1" s="281"/>
+      <c r="BE1" s="281"/>
+      <c r="BF1" s="281"/>
+      <c r="BG1" s="281"/>
+      <c r="BH1" s="281"/>
+      <c r="BI1" s="281"/>
+      <c r="BJ1" s="281"/>
+      <c r="BK1" s="281"/>
+      <c r="BL1" s="281"/>
+      <c r="BM1" s="281"/>
+      <c r="BN1" s="281"/>
+      <c r="BO1" s="281"/>
+      <c r="BP1" s="281"/>
+      <c r="BQ1" s="281"/>
+      <c r="BR1" s="281"/>
+      <c r="BS1" s="281"/>
+      <c r="BT1" s="281"/>
+      <c r="BU1" s="281"/>
+      <c r="BV1" s="281"/>
+      <c r="BW1" s="281"/>
+      <c r="BX1" s="281"/>
+      <c r="BY1" s="281"/>
+      <c r="BZ1" s="281"/>
+      <c r="CA1" s="281"/>
+      <c r="CB1" s="281"/>
     </row>
     <row r="2" spans="1:80" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="268"/>
-      <c r="B2" s="269"/>
-      <c r="C2" s="270"/>
-      <c r="D2" s="270"/>
-      <c r="E2" s="270"/>
-      <c r="F2" s="270"/>
+      <c r="A2" s="308"/>
+      <c r="B2" s="309"/>
+      <c r="C2" s="310"/>
+      <c r="D2" s="310"/>
+      <c r="E2" s="310"/>
+      <c r="F2" s="310"/>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="J2" s="272"/>
-      <c r="K2" s="272"/>
-      <c r="L2" s="272"/>
-      <c r="M2" s="272"/>
-      <c r="N2" s="272"/>
-      <c r="O2" s="272"/>
-      <c r="P2" s="272"/>
-      <c r="Q2" s="272"/>
-      <c r="R2" s="272"/>
-      <c r="S2" s="272"/>
-      <c r="T2" s="272"/>
-      <c r="U2" s="272"/>
-      <c r="V2" s="272"/>
-      <c r="W2" s="272"/>
-      <c r="X2" s="272"/>
-      <c r="Y2" s="272"/>
-      <c r="Z2" s="272"/>
-      <c r="AA2" s="272"/>
-      <c r="AB2" s="272"/>
-      <c r="AC2" s="272"/>
-      <c r="AD2" s="272"/>
-      <c r="AE2" s="272"/>
-      <c r="AF2" s="272"/>
-      <c r="AG2" s="272"/>
-      <c r="AH2" s="272"/>
-      <c r="AI2" s="272"/>
-      <c r="AJ2" s="272"/>
-      <c r="AK2" s="272"/>
-      <c r="AL2" s="272"/>
-      <c r="AM2" s="272"/>
-      <c r="AN2" s="272"/>
-      <c r="AO2" s="272"/>
-      <c r="AP2" s="272"/>
-      <c r="AQ2" s="272"/>
-      <c r="AR2" s="272"/>
-      <c r="AS2" s="272"/>
-      <c r="AT2" s="272"/>
-      <c r="AU2" s="272"/>
-      <c r="AV2" s="272"/>
-      <c r="AW2" s="272"/>
-      <c r="AX2" s="272"/>
-      <c r="AY2" s="272"/>
-      <c r="AZ2" s="272"/>
+      <c r="J2" s="312"/>
+      <c r="K2" s="312"/>
+      <c r="L2" s="312"/>
+      <c r="M2" s="312"/>
+      <c r="N2" s="312"/>
+      <c r="O2" s="312"/>
+      <c r="P2" s="312"/>
+      <c r="Q2" s="312"/>
+      <c r="R2" s="312"/>
+      <c r="S2" s="312"/>
+      <c r="T2" s="312"/>
+      <c r="U2" s="312"/>
+      <c r="V2" s="312"/>
+      <c r="W2" s="312"/>
+      <c r="X2" s="312"/>
+      <c r="Y2" s="312"/>
+      <c r="Z2" s="312"/>
+      <c r="AA2" s="312"/>
+      <c r="AB2" s="312"/>
+      <c r="AC2" s="312"/>
+      <c r="AD2" s="312"/>
+      <c r="AE2" s="312"/>
+      <c r="AF2" s="312"/>
+      <c r="AG2" s="312"/>
+      <c r="AH2" s="312"/>
+      <c r="AI2" s="312"/>
+      <c r="AJ2" s="312"/>
+      <c r="AK2" s="312"/>
+      <c r="AL2" s="312"/>
+      <c r="AM2" s="312"/>
+      <c r="AN2" s="312"/>
+      <c r="AO2" s="312"/>
+      <c r="AP2" s="312"/>
+      <c r="AQ2" s="312"/>
+      <c r="AR2" s="312"/>
+      <c r="AS2" s="312"/>
+      <c r="AT2" s="312"/>
+      <c r="AU2" s="312"/>
+      <c r="AV2" s="312"/>
+      <c r="AW2" s="312"/>
+      <c r="AX2" s="312"/>
+      <c r="AY2" s="312"/>
+      <c r="AZ2" s="312"/>
       <c r="BA2" s="109"/>
       <c r="BB2" s="32"/>
       <c r="BC2" s="32"/>
@@ -8343,58 +8343,58 @@
       <c r="CB2" s="107"/>
     </row>
     <row r="3" spans="1:80" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="268"/>
-      <c r="B3" s="271"/>
-      <c r="C3" s="268"/>
-      <c r="D3" s="268"/>
-      <c r="E3" s="268"/>
-      <c r="F3" s="268"/>
+      <c r="A3" s="308"/>
+      <c r="B3" s="311"/>
+      <c r="C3" s="308"/>
+      <c r="D3" s="308"/>
+      <c r="E3" s="308"/>
+      <c r="F3" s="308"/>
       <c r="G3" s="17"/>
       <c r="H3" s="17"/>
       <c r="I3" s="17"/>
-      <c r="J3" s="273"/>
-      <c r="K3" s="273"/>
-      <c r="L3" s="273"/>
-      <c r="M3" s="273"/>
-      <c r="N3" s="273"/>
-      <c r="O3" s="273"/>
-      <c r="P3" s="273"/>
-      <c r="Q3" s="273"/>
-      <c r="R3" s="273"/>
-      <c r="S3" s="273"/>
-      <c r="T3" s="273"/>
-      <c r="U3" s="273"/>
-      <c r="V3" s="273"/>
-      <c r="W3" s="273"/>
-      <c r="X3" s="273"/>
-      <c r="Y3" s="273"/>
-      <c r="Z3" s="273"/>
-      <c r="AA3" s="273"/>
-      <c r="AB3" s="273"/>
-      <c r="AC3" s="273"/>
-      <c r="AD3" s="273"/>
-      <c r="AE3" s="273"/>
-      <c r="AF3" s="273"/>
-      <c r="AG3" s="273"/>
-      <c r="AH3" s="273"/>
-      <c r="AI3" s="273"/>
-      <c r="AJ3" s="273"/>
-      <c r="AK3" s="273"/>
-      <c r="AL3" s="273"/>
-      <c r="AM3" s="273"/>
-      <c r="AN3" s="273"/>
-      <c r="AO3" s="273"/>
-      <c r="AP3" s="273"/>
-      <c r="AQ3" s="273"/>
-      <c r="AR3" s="273"/>
-      <c r="AS3" s="273"/>
-      <c r="AT3" s="273"/>
-      <c r="AU3" s="273"/>
-      <c r="AV3" s="273"/>
-      <c r="AW3" s="273"/>
-      <c r="AX3" s="273"/>
-      <c r="AY3" s="273"/>
-      <c r="AZ3" s="273"/>
+      <c r="J3" s="268"/>
+      <c r="K3" s="268"/>
+      <c r="L3" s="268"/>
+      <c r="M3" s="268"/>
+      <c r="N3" s="268"/>
+      <c r="O3" s="268"/>
+      <c r="P3" s="268"/>
+      <c r="Q3" s="268"/>
+      <c r="R3" s="268"/>
+      <c r="S3" s="268"/>
+      <c r="T3" s="268"/>
+      <c r="U3" s="268"/>
+      <c r="V3" s="268"/>
+      <c r="W3" s="268"/>
+      <c r="X3" s="268"/>
+      <c r="Y3" s="268"/>
+      <c r="Z3" s="268"/>
+      <c r="AA3" s="268"/>
+      <c r="AB3" s="268"/>
+      <c r="AC3" s="268"/>
+      <c r="AD3" s="268"/>
+      <c r="AE3" s="268"/>
+      <c r="AF3" s="268"/>
+      <c r="AG3" s="268"/>
+      <c r="AH3" s="268"/>
+      <c r="AI3" s="268"/>
+      <c r="AJ3" s="268"/>
+      <c r="AK3" s="268"/>
+      <c r="AL3" s="268"/>
+      <c r="AM3" s="268"/>
+      <c r="AN3" s="268"/>
+      <c r="AO3" s="268"/>
+      <c r="AP3" s="268"/>
+      <c r="AQ3" s="268"/>
+      <c r="AR3" s="268"/>
+      <c r="AS3" s="268"/>
+      <c r="AT3" s="268"/>
+      <c r="AU3" s="268"/>
+      <c r="AV3" s="268"/>
+      <c r="AW3" s="268"/>
+      <c r="AX3" s="268"/>
+      <c r="AY3" s="268"/>
+      <c r="AZ3" s="268"/>
       <c r="BA3" s="110"/>
       <c r="BB3" s="17"/>
       <c r="BC3" s="17"/>
@@ -8425,58 +8425,58 @@
       <c r="CB3" s="107"/>
     </row>
     <row r="4" spans="1:80" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="268"/>
-      <c r="B4" s="271"/>
-      <c r="C4" s="268"/>
-      <c r="D4" s="268"/>
-      <c r="E4" s="268"/>
-      <c r="F4" s="268"/>
+      <c r="A4" s="308"/>
+      <c r="B4" s="311"/>
+      <c r="C4" s="308"/>
+      <c r="D4" s="308"/>
+      <c r="E4" s="308"/>
+      <c r="F4" s="308"/>
       <c r="G4" s="17"/>
       <c r="H4" s="17"/>
       <c r="I4" s="17"/>
-      <c r="J4" s="274"/>
-      <c r="K4" s="274"/>
-      <c r="L4" s="274"/>
-      <c r="M4" s="274"/>
-      <c r="N4" s="274"/>
-      <c r="O4" s="274"/>
-      <c r="P4" s="274"/>
-      <c r="Q4" s="274"/>
-      <c r="R4" s="274"/>
-      <c r="S4" s="274"/>
-      <c r="T4" s="274"/>
-      <c r="U4" s="274"/>
-      <c r="V4" s="274"/>
-      <c r="W4" s="274"/>
-      <c r="X4" s="274"/>
-      <c r="Y4" s="274"/>
-      <c r="Z4" s="274"/>
-      <c r="AA4" s="274"/>
-      <c r="AB4" s="274"/>
-      <c r="AC4" s="274"/>
-      <c r="AD4" s="274"/>
-      <c r="AE4" s="274"/>
-      <c r="AF4" s="274"/>
-      <c r="AG4" s="274"/>
-      <c r="AH4" s="274"/>
-      <c r="AI4" s="274"/>
-      <c r="AJ4" s="274"/>
-      <c r="AK4" s="274"/>
-      <c r="AL4" s="274"/>
-      <c r="AM4" s="274"/>
-      <c r="AN4" s="274"/>
-      <c r="AO4" s="274"/>
-      <c r="AP4" s="274"/>
-      <c r="AQ4" s="274"/>
-      <c r="AR4" s="274"/>
-      <c r="AS4" s="274"/>
-      <c r="AT4" s="274"/>
-      <c r="AU4" s="274"/>
-      <c r="AV4" s="274"/>
-      <c r="AW4" s="274"/>
-      <c r="AX4" s="274"/>
-      <c r="AY4" s="274"/>
-      <c r="AZ4" s="274"/>
+      <c r="J4" s="313"/>
+      <c r="K4" s="313"/>
+      <c r="L4" s="313"/>
+      <c r="M4" s="313"/>
+      <c r="N4" s="313"/>
+      <c r="O4" s="313"/>
+      <c r="P4" s="313"/>
+      <c r="Q4" s="313"/>
+      <c r="R4" s="313"/>
+      <c r="S4" s="313"/>
+      <c r="T4" s="313"/>
+      <c r="U4" s="313"/>
+      <c r="V4" s="313"/>
+      <c r="W4" s="313"/>
+      <c r="X4" s="313"/>
+      <c r="Y4" s="313"/>
+      <c r="Z4" s="313"/>
+      <c r="AA4" s="313"/>
+      <c r="AB4" s="313"/>
+      <c r="AC4" s="313"/>
+      <c r="AD4" s="313"/>
+      <c r="AE4" s="313"/>
+      <c r="AF4" s="313"/>
+      <c r="AG4" s="313"/>
+      <c r="AH4" s="313"/>
+      <c r="AI4" s="313"/>
+      <c r="AJ4" s="313"/>
+      <c r="AK4" s="313"/>
+      <c r="AL4" s="313"/>
+      <c r="AM4" s="313"/>
+      <c r="AN4" s="313"/>
+      <c r="AO4" s="313"/>
+      <c r="AP4" s="313"/>
+      <c r="AQ4" s="313"/>
+      <c r="AR4" s="313"/>
+      <c r="AS4" s="313"/>
+      <c r="AT4" s="313"/>
+      <c r="AU4" s="313"/>
+      <c r="AV4" s="313"/>
+      <c r="AW4" s="313"/>
+      <c r="AX4" s="313"/>
+      <c r="AY4" s="313"/>
+      <c r="AZ4" s="313"/>
       <c r="BA4" s="111"/>
       <c r="BB4" s="17"/>
       <c r="BC4" s="17"/>
@@ -8507,58 +8507,58 @@
       <c r="CB4" s="107"/>
     </row>
     <row r="5" spans="1:80" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="268"/>
-      <c r="B5" s="271"/>
-      <c r="C5" s="268"/>
-      <c r="D5" s="268"/>
-      <c r="E5" s="268"/>
-      <c r="F5" s="268"/>
+      <c r="A5" s="308"/>
+      <c r="B5" s="311"/>
+      <c r="C5" s="308"/>
+      <c r="D5" s="308"/>
+      <c r="E5" s="308"/>
+      <c r="F5" s="308"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17"/>
       <c r="I5" s="17"/>
-      <c r="J5" s="275"/>
-      <c r="K5" s="275"/>
-      <c r="L5" s="275"/>
-      <c r="M5" s="275"/>
-      <c r="N5" s="275"/>
-      <c r="O5" s="275"/>
-      <c r="P5" s="275"/>
-      <c r="Q5" s="275"/>
-      <c r="R5" s="275"/>
-      <c r="S5" s="275"/>
-      <c r="T5" s="275"/>
-      <c r="U5" s="275"/>
-      <c r="V5" s="275"/>
-      <c r="W5" s="275"/>
-      <c r="X5" s="275"/>
-      <c r="Y5" s="275"/>
-      <c r="Z5" s="275"/>
-      <c r="AA5" s="275"/>
-      <c r="AB5" s="275"/>
-      <c r="AC5" s="275"/>
-      <c r="AD5" s="275"/>
-      <c r="AE5" s="275"/>
-      <c r="AF5" s="275"/>
-      <c r="AG5" s="275"/>
-      <c r="AH5" s="275"/>
-      <c r="AI5" s="275"/>
-      <c r="AJ5" s="275"/>
-      <c r="AK5" s="275"/>
-      <c r="AL5" s="275"/>
-      <c r="AM5" s="275"/>
-      <c r="AN5" s="275"/>
-      <c r="AO5" s="275"/>
-      <c r="AP5" s="275"/>
-      <c r="AQ5" s="275"/>
-      <c r="AR5" s="275"/>
-      <c r="AS5" s="275"/>
-      <c r="AT5" s="275"/>
-      <c r="AU5" s="275"/>
-      <c r="AV5" s="275"/>
-      <c r="AW5" s="275"/>
-      <c r="AX5" s="275"/>
-      <c r="AY5" s="275"/>
-      <c r="AZ5" s="275"/>
+      <c r="J5" s="269"/>
+      <c r="K5" s="269"/>
+      <c r="L5" s="269"/>
+      <c r="M5" s="269"/>
+      <c r="N5" s="269"/>
+      <c r="O5" s="269"/>
+      <c r="P5" s="269"/>
+      <c r="Q5" s="269"/>
+      <c r="R5" s="269"/>
+      <c r="S5" s="269"/>
+      <c r="T5" s="269"/>
+      <c r="U5" s="269"/>
+      <c r="V5" s="269"/>
+      <c r="W5" s="269"/>
+      <c r="X5" s="269"/>
+      <c r="Y5" s="269"/>
+      <c r="Z5" s="269"/>
+      <c r="AA5" s="269"/>
+      <c r="AB5" s="269"/>
+      <c r="AC5" s="269"/>
+      <c r="AD5" s="269"/>
+      <c r="AE5" s="269"/>
+      <c r="AF5" s="269"/>
+      <c r="AG5" s="269"/>
+      <c r="AH5" s="269"/>
+      <c r="AI5" s="269"/>
+      <c r="AJ5" s="269"/>
+      <c r="AK5" s="269"/>
+      <c r="AL5" s="269"/>
+      <c r="AM5" s="269"/>
+      <c r="AN5" s="269"/>
+      <c r="AO5" s="269"/>
+      <c r="AP5" s="269"/>
+      <c r="AQ5" s="269"/>
+      <c r="AR5" s="269"/>
+      <c r="AS5" s="269"/>
+      <c r="AT5" s="269"/>
+      <c r="AU5" s="269"/>
+      <c r="AV5" s="269"/>
+      <c r="AW5" s="269"/>
+      <c r="AX5" s="269"/>
+      <c r="AY5" s="269"/>
+      <c r="AZ5" s="269"/>
       <c r="BA5" s="112"/>
       <c r="BB5" s="17"/>
       <c r="BC5" s="17"/>
@@ -8589,58 +8589,58 @@
       <c r="CB5" s="107"/>
     </row>
     <row r="6" spans="1:80" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="268"/>
-      <c r="B6" s="271"/>
-      <c r="C6" s="268"/>
-      <c r="D6" s="268"/>
-      <c r="E6" s="268"/>
-      <c r="F6" s="268"/>
+      <c r="A6" s="308"/>
+      <c r="B6" s="311"/>
+      <c r="C6" s="308"/>
+      <c r="D6" s="308"/>
+      <c r="E6" s="308"/>
+      <c r="F6" s="308"/>
       <c r="G6" s="37"/>
       <c r="H6" s="37"/>
       <c r="I6" s="37"/>
-      <c r="J6" s="276"/>
-      <c r="K6" s="276"/>
-      <c r="L6" s="276"/>
-      <c r="M6" s="276"/>
-      <c r="N6" s="276"/>
-      <c r="O6" s="276"/>
-      <c r="P6" s="276"/>
-      <c r="Q6" s="276"/>
-      <c r="R6" s="276"/>
-      <c r="S6" s="276"/>
-      <c r="T6" s="276"/>
-      <c r="U6" s="276"/>
-      <c r="V6" s="276"/>
-      <c r="W6" s="276"/>
-      <c r="X6" s="276"/>
-      <c r="Y6" s="276"/>
-      <c r="Z6" s="276"/>
-      <c r="AA6" s="276"/>
-      <c r="AB6" s="276"/>
-      <c r="AC6" s="276"/>
-      <c r="AD6" s="276"/>
-      <c r="AE6" s="276"/>
-      <c r="AF6" s="276"/>
-      <c r="AG6" s="276"/>
-      <c r="AH6" s="276"/>
-      <c r="AI6" s="276"/>
-      <c r="AJ6" s="276"/>
-      <c r="AK6" s="276"/>
-      <c r="AL6" s="276"/>
-      <c r="AM6" s="276"/>
-      <c r="AN6" s="276"/>
-      <c r="AO6" s="276"/>
-      <c r="AP6" s="276"/>
-      <c r="AQ6" s="276"/>
-      <c r="AR6" s="276"/>
-      <c r="AS6" s="276"/>
-      <c r="AT6" s="276"/>
-      <c r="AU6" s="276"/>
-      <c r="AV6" s="276"/>
-      <c r="AW6" s="276"/>
-      <c r="AX6" s="276"/>
-      <c r="AY6" s="276"/>
-      <c r="AZ6" s="276"/>
+      <c r="J6" s="282"/>
+      <c r="K6" s="282"/>
+      <c r="L6" s="282"/>
+      <c r="M6" s="282"/>
+      <c r="N6" s="282"/>
+      <c r="O6" s="282"/>
+      <c r="P6" s="282"/>
+      <c r="Q6" s="282"/>
+      <c r="R6" s="282"/>
+      <c r="S6" s="282"/>
+      <c r="T6" s="282"/>
+      <c r="U6" s="282"/>
+      <c r="V6" s="282"/>
+      <c r="W6" s="282"/>
+      <c r="X6" s="282"/>
+      <c r="Y6" s="282"/>
+      <c r="Z6" s="282"/>
+      <c r="AA6" s="282"/>
+      <c r="AB6" s="282"/>
+      <c r="AC6" s="282"/>
+      <c r="AD6" s="282"/>
+      <c r="AE6" s="282"/>
+      <c r="AF6" s="282"/>
+      <c r="AG6" s="282"/>
+      <c r="AH6" s="282"/>
+      <c r="AI6" s="282"/>
+      <c r="AJ6" s="282"/>
+      <c r="AK6" s="282"/>
+      <c r="AL6" s="282"/>
+      <c r="AM6" s="282"/>
+      <c r="AN6" s="282"/>
+      <c r="AO6" s="282"/>
+      <c r="AP6" s="282"/>
+      <c r="AQ6" s="282"/>
+      <c r="AR6" s="282"/>
+      <c r="AS6" s="282"/>
+      <c r="AT6" s="282"/>
+      <c r="AU6" s="282"/>
+      <c r="AV6" s="282"/>
+      <c r="AW6" s="282"/>
+      <c r="AX6" s="282"/>
+      <c r="AY6" s="282"/>
+      <c r="AZ6" s="282"/>
       <c r="BA6" s="113"/>
       <c r="BB6" s="37"/>
       <c r="BC6" s="37"/>
@@ -8671,209 +8671,209 @@
       <c r="CB6" s="107"/>
     </row>
     <row r="7" spans="1:80" s="2" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="268"/>
-      <c r="B7" s="277"/>
-      <c r="C7" s="278" t="s">
+      <c r="A7" s="308"/>
+      <c r="B7" s="314"/>
+      <c r="C7" s="315" t="s">
         <v>652</v>
       </c>
-      <c r="D7" s="279"/>
-      <c r="E7" s="279"/>
-      <c r="F7" s="279"/>
-      <c r="G7" s="279"/>
-      <c r="H7" s="279"/>
-      <c r="I7" s="279"/>
-      <c r="J7" s="279"/>
-      <c r="K7" s="279"/>
-      <c r="L7" s="279"/>
-      <c r="M7" s="279"/>
-      <c r="N7" s="279"/>
-      <c r="O7" s="279"/>
-      <c r="P7" s="279"/>
-      <c r="Q7" s="279"/>
-      <c r="R7" s="279"/>
-      <c r="S7" s="279"/>
-      <c r="T7" s="279"/>
-      <c r="U7" s="279"/>
-      <c r="V7" s="279"/>
-      <c r="W7" s="279"/>
-      <c r="X7" s="279"/>
-      <c r="Y7" s="279"/>
-      <c r="Z7" s="279"/>
-      <c r="AA7" s="279"/>
-      <c r="AB7" s="279"/>
-      <c r="AC7" s="279"/>
-      <c r="AD7" s="279"/>
-      <c r="AE7" s="279"/>
-      <c r="AF7" s="279"/>
-      <c r="AG7" s="279"/>
-      <c r="AH7" s="279"/>
-      <c r="AI7" s="279"/>
-      <c r="AJ7" s="279"/>
-      <c r="AK7" s="279"/>
-      <c r="AL7" s="279"/>
-      <c r="AM7" s="279"/>
-      <c r="AN7" s="279"/>
-      <c r="AO7" s="279"/>
-      <c r="AP7" s="279"/>
-      <c r="AQ7" s="279"/>
-      <c r="AR7" s="279"/>
-      <c r="AS7" s="279"/>
-      <c r="AT7" s="279"/>
-      <c r="AU7" s="279"/>
-      <c r="AV7" s="279"/>
-      <c r="AW7" s="279"/>
-      <c r="AX7" s="279"/>
-      <c r="AY7" s="279"/>
-      <c r="AZ7" s="279"/>
-      <c r="BA7" s="279"/>
-      <c r="BB7" s="279"/>
-      <c r="BC7" s="279"/>
-      <c r="BD7" s="279"/>
-      <c r="BE7" s="279"/>
-      <c r="BF7" s="279"/>
-      <c r="BG7" s="279"/>
-      <c r="BH7" s="279"/>
-      <c r="BI7" s="279"/>
-      <c r="BJ7" s="279"/>
-      <c r="BK7" s="279"/>
-      <c r="BL7" s="279"/>
-      <c r="BM7" s="279"/>
-      <c r="BN7" s="279"/>
-      <c r="BO7" s="279"/>
-      <c r="BP7" s="279"/>
-      <c r="BQ7" s="279"/>
-      <c r="BR7" s="279"/>
-      <c r="BS7" s="279"/>
-      <c r="BT7" s="279"/>
-      <c r="BU7" s="279"/>
-      <c r="BV7" s="279"/>
-      <c r="BW7" s="279"/>
-      <c r="BX7" s="279"/>
-      <c r="BY7" s="279"/>
-      <c r="BZ7" s="279"/>
-      <c r="CA7" s="280"/>
+      <c r="D7" s="316"/>
+      <c r="E7" s="316"/>
+      <c r="F7" s="316"/>
+      <c r="G7" s="316"/>
+      <c r="H7" s="316"/>
+      <c r="I7" s="316"/>
+      <c r="J7" s="316"/>
+      <c r="K7" s="316"/>
+      <c r="L7" s="316"/>
+      <c r="M7" s="316"/>
+      <c r="N7" s="316"/>
+      <c r="O7" s="316"/>
+      <c r="P7" s="316"/>
+      <c r="Q7" s="316"/>
+      <c r="R7" s="316"/>
+      <c r="S7" s="316"/>
+      <c r="T7" s="316"/>
+      <c r="U7" s="316"/>
+      <c r="V7" s="316"/>
+      <c r="W7" s="316"/>
+      <c r="X7" s="316"/>
+      <c r="Y7" s="316"/>
+      <c r="Z7" s="316"/>
+      <c r="AA7" s="316"/>
+      <c r="AB7" s="316"/>
+      <c r="AC7" s="316"/>
+      <c r="AD7" s="316"/>
+      <c r="AE7" s="316"/>
+      <c r="AF7" s="316"/>
+      <c r="AG7" s="316"/>
+      <c r="AH7" s="316"/>
+      <c r="AI7" s="316"/>
+      <c r="AJ7" s="316"/>
+      <c r="AK7" s="316"/>
+      <c r="AL7" s="316"/>
+      <c r="AM7" s="316"/>
+      <c r="AN7" s="316"/>
+      <c r="AO7" s="316"/>
+      <c r="AP7" s="316"/>
+      <c r="AQ7" s="316"/>
+      <c r="AR7" s="316"/>
+      <c r="AS7" s="316"/>
+      <c r="AT7" s="316"/>
+      <c r="AU7" s="316"/>
+      <c r="AV7" s="316"/>
+      <c r="AW7" s="316"/>
+      <c r="AX7" s="316"/>
+      <c r="AY7" s="316"/>
+      <c r="AZ7" s="316"/>
+      <c r="BA7" s="316"/>
+      <c r="BB7" s="316"/>
+      <c r="BC7" s="316"/>
+      <c r="BD7" s="316"/>
+      <c r="BE7" s="316"/>
+      <c r="BF7" s="316"/>
+      <c r="BG7" s="316"/>
+      <c r="BH7" s="316"/>
+      <c r="BI7" s="316"/>
+      <c r="BJ7" s="316"/>
+      <c r="BK7" s="316"/>
+      <c r="BL7" s="316"/>
+      <c r="BM7" s="316"/>
+      <c r="BN7" s="316"/>
+      <c r="BO7" s="316"/>
+      <c r="BP7" s="316"/>
+      <c r="BQ7" s="316"/>
+      <c r="BR7" s="316"/>
+      <c r="BS7" s="316"/>
+      <c r="BT7" s="316"/>
+      <c r="BU7" s="316"/>
+      <c r="BV7" s="316"/>
+      <c r="BW7" s="316"/>
+      <c r="BX7" s="316"/>
+      <c r="BY7" s="316"/>
+      <c r="BZ7" s="316"/>
+      <c r="CA7" s="317"/>
       <c r="CB7" s="107"/>
     </row>
     <row r="8" spans="1:80" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="268"/>
-      <c r="B8" s="277"/>
-      <c r="C8" s="281" t="s">
+      <c r="A8" s="308"/>
+      <c r="B8" s="314"/>
+      <c r="C8" s="318" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="282"/>
-      <c r="E8" s="287" t="s">
+      <c r="D8" s="319"/>
+      <c r="E8" s="324" t="s">
         <v>77</v>
       </c>
-      <c r="F8" s="287" t="s">
+      <c r="F8" s="324" t="s">
         <v>536</v>
       </c>
-      <c r="G8" s="287" t="s">
+      <c r="G8" s="324" t="s">
         <v>524</v>
       </c>
-      <c r="H8" s="290" t="s">
+      <c r="H8" s="270" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="290" t="s">
+      <c r="I8" s="270" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="290" t="s">
+      <c r="J8" s="270" t="s">
         <v>534</v>
       </c>
-      <c r="K8" s="322" t="s">
+      <c r="K8" s="273" t="s">
         <v>535</v>
       </c>
-      <c r="L8" s="324" t="s">
+      <c r="L8" s="275" t="s">
         <v>437</v>
       </c>
-      <c r="M8" s="325"/>
-      <c r="N8" s="325"/>
-      <c r="O8" s="325"/>
-      <c r="P8" s="325"/>
-      <c r="Q8" s="325"/>
-      <c r="R8" s="325"/>
-      <c r="S8" s="325"/>
-      <c r="T8" s="325"/>
-      <c r="U8" s="325"/>
-      <c r="V8" s="326"/>
-      <c r="W8" s="325" t="s">
+      <c r="M8" s="276"/>
+      <c r="N8" s="276"/>
+      <c r="O8" s="276"/>
+      <c r="P8" s="276"/>
+      <c r="Q8" s="276"/>
+      <c r="R8" s="276"/>
+      <c r="S8" s="276"/>
+      <c r="T8" s="276"/>
+      <c r="U8" s="276"/>
+      <c r="V8" s="277"/>
+      <c r="W8" s="276" t="s">
         <v>497</v>
       </c>
-      <c r="X8" s="325"/>
-      <c r="Y8" s="325"/>
-      <c r="Z8" s="325"/>
-      <c r="AA8" s="325"/>
-      <c r="AB8" s="325"/>
-      <c r="AC8" s="325"/>
-      <c r="AD8" s="325"/>
-      <c r="AE8" s="325"/>
-      <c r="AF8" s="325"/>
-      <c r="AG8" s="325"/>
-      <c r="AH8" s="325"/>
-      <c r="AI8" s="325"/>
-      <c r="AJ8" s="325"/>
-      <c r="AK8" s="325"/>
-      <c r="AL8" s="325"/>
-      <c r="AM8" s="325"/>
-      <c r="AN8" s="325"/>
-      <c r="AO8" s="325"/>
-      <c r="AP8" s="325"/>
-      <c r="AQ8" s="325"/>
-      <c r="AR8" s="325"/>
-      <c r="AS8" s="325"/>
-      <c r="AT8" s="325"/>
-      <c r="AU8" s="325"/>
-      <c r="AV8" s="325"/>
-      <c r="AW8" s="325"/>
-      <c r="AX8" s="325"/>
-      <c r="AY8" s="325"/>
-      <c r="AZ8" s="325"/>
-      <c r="BA8" s="325"/>
-      <c r="BB8" s="325"/>
-      <c r="BC8" s="325"/>
-      <c r="BD8" s="325"/>
-      <c r="BE8" s="325"/>
-      <c r="BF8" s="325"/>
-      <c r="BG8" s="325"/>
-      <c r="BH8" s="325"/>
-      <c r="BI8" s="325"/>
-      <c r="BJ8" s="325"/>
-      <c r="BK8" s="325"/>
-      <c r="BL8" s="325"/>
-      <c r="BM8" s="325"/>
-      <c r="BN8" s="325"/>
-      <c r="BO8" s="325"/>
-      <c r="BP8" s="325"/>
-      <c r="BQ8" s="325"/>
-      <c r="BR8" s="325"/>
-      <c r="BS8" s="325"/>
-      <c r="BT8" s="325"/>
-      <c r="BU8" s="325"/>
-      <c r="BV8" s="325"/>
-      <c r="BW8" s="325"/>
-      <c r="BX8" s="325"/>
-      <c r="BY8" s="293" t="s">
+      <c r="X8" s="276"/>
+      <c r="Y8" s="276"/>
+      <c r="Z8" s="276"/>
+      <c r="AA8" s="276"/>
+      <c r="AB8" s="276"/>
+      <c r="AC8" s="276"/>
+      <c r="AD8" s="276"/>
+      <c r="AE8" s="276"/>
+      <c r="AF8" s="276"/>
+      <c r="AG8" s="276"/>
+      <c r="AH8" s="276"/>
+      <c r="AI8" s="276"/>
+      <c r="AJ8" s="276"/>
+      <c r="AK8" s="276"/>
+      <c r="AL8" s="276"/>
+      <c r="AM8" s="276"/>
+      <c r="AN8" s="276"/>
+      <c r="AO8" s="276"/>
+      <c r="AP8" s="276"/>
+      <c r="AQ8" s="276"/>
+      <c r="AR8" s="276"/>
+      <c r="AS8" s="276"/>
+      <c r="AT8" s="276"/>
+      <c r="AU8" s="276"/>
+      <c r="AV8" s="276"/>
+      <c r="AW8" s="276"/>
+      <c r="AX8" s="276"/>
+      <c r="AY8" s="276"/>
+      <c r="AZ8" s="276"/>
+      <c r="BA8" s="276"/>
+      <c r="BB8" s="276"/>
+      <c r="BC8" s="276"/>
+      <c r="BD8" s="276"/>
+      <c r="BE8" s="276"/>
+      <c r="BF8" s="276"/>
+      <c r="BG8" s="276"/>
+      <c r="BH8" s="276"/>
+      <c r="BI8" s="276"/>
+      <c r="BJ8" s="276"/>
+      <c r="BK8" s="276"/>
+      <c r="BL8" s="276"/>
+      <c r="BM8" s="276"/>
+      <c r="BN8" s="276"/>
+      <c r="BO8" s="276"/>
+      <c r="BP8" s="276"/>
+      <c r="BQ8" s="276"/>
+      <c r="BR8" s="276"/>
+      <c r="BS8" s="276"/>
+      <c r="BT8" s="276"/>
+      <c r="BU8" s="276"/>
+      <c r="BV8" s="276"/>
+      <c r="BW8" s="276"/>
+      <c r="BX8" s="276"/>
+      <c r="BY8" s="278" t="s">
         <v>522</v>
       </c>
-      <c r="BZ8" s="293" t="s">
+      <c r="BZ8" s="278" t="s">
         <v>743</v>
       </c>
-      <c r="CA8" s="264" t="s">
+      <c r="CA8" s="305" t="s">
         <v>238</v>
       </c>
       <c r="CB8" s="107"/>
     </row>
     <row r="9" spans="1:80" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="268"/>
-      <c r="B9" s="277"/>
-      <c r="C9" s="283"/>
-      <c r="D9" s="284"/>
-      <c r="E9" s="288"/>
-      <c r="F9" s="288"/>
-      <c r="G9" s="288"/>
-      <c r="H9" s="291"/>
-      <c r="I9" s="291"/>
-      <c r="J9" s="291"/>
-      <c r="K9" s="323"/>
+      <c r="A9" s="308"/>
+      <c r="B9" s="314"/>
+      <c r="C9" s="320"/>
+      <c r="D9" s="321"/>
+      <c r="E9" s="325"/>
+      <c r="F9" s="325"/>
+      <c r="G9" s="325"/>
+      <c r="H9" s="271"/>
+      <c r="I9" s="271"/>
+      <c r="J9" s="271"/>
+      <c r="K9" s="274"/>
       <c r="L9" s="90">
         <v>1</v>
       </c>
@@ -9069,23 +9069,23 @@
       <c r="BX9" s="90">
         <v>65</v>
       </c>
-      <c r="BY9" s="294"/>
-      <c r="BZ9" s="294"/>
-      <c r="CA9" s="265"/>
+      <c r="BY9" s="279"/>
+      <c r="BZ9" s="279"/>
+      <c r="CA9" s="306"/>
       <c r="CB9" s="107"/>
     </row>
     <row r="10" spans="1:80" ht="88.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="268"/>
-      <c r="B10" s="277"/>
-      <c r="C10" s="285"/>
-      <c r="D10" s="286"/>
-      <c r="E10" s="288"/>
-      <c r="F10" s="288"/>
-      <c r="G10" s="288"/>
-      <c r="H10" s="291"/>
-      <c r="I10" s="291"/>
-      <c r="J10" s="291"/>
-      <c r="K10" s="323"/>
+      <c r="A10" s="308"/>
+      <c r="B10" s="314"/>
+      <c r="C10" s="322"/>
+      <c r="D10" s="323"/>
+      <c r="E10" s="325"/>
+      <c r="F10" s="325"/>
+      <c r="G10" s="325"/>
+      <c r="H10" s="271"/>
+      <c r="I10" s="271"/>
+      <c r="J10" s="271"/>
+      <c r="K10" s="274"/>
       <c r="L10" s="71">
         <v>35.450000000000003</v>
       </c>
@@ -9281,27 +9281,27 @@
       <c r="BX10" s="73">
         <v>66.34</v>
       </c>
-      <c r="BY10" s="294"/>
-      <c r="BZ10" s="294"/>
-      <c r="CA10" s="265"/>
+      <c r="BY10" s="279"/>
+      <c r="BZ10" s="279"/>
+      <c r="CA10" s="306"/>
       <c r="CB10" s="107"/>
     </row>
-    <row r="11" spans="1:80" ht="189" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="268"/>
-      <c r="B11" s="277"/>
+    <row r="11" spans="1:80" ht="189.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="308"/>
+      <c r="B11" s="314"/>
       <c r="C11" s="74" t="s">
         <v>26</v>
       </c>
       <c r="D11" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="289"/>
-      <c r="F11" s="289"/>
-      <c r="G11" s="289"/>
-      <c r="H11" s="292"/>
-      <c r="I11" s="291"/>
-      <c r="J11" s="292"/>
-      <c r="K11" s="323"/>
+      <c r="E11" s="326"/>
+      <c r="F11" s="326"/>
+      <c r="G11" s="326"/>
+      <c r="H11" s="272"/>
+      <c r="I11" s="271"/>
+      <c r="J11" s="272"/>
+      <c r="K11" s="274"/>
       <c r="L11" s="131" t="s">
         <v>510</v>
       </c>
@@ -9497,13 +9497,13 @@
       <c r="BX11" s="70" t="s">
         <v>596</v>
       </c>
-      <c r="BY11" s="295"/>
-      <c r="BZ11" s="295"/>
-      <c r="CA11" s="266"/>
+      <c r="BY11" s="280"/>
+      <c r="BZ11" s="280"/>
+      <c r="CA11" s="307"/>
       <c r="CB11" s="107"/>
     </row>
     <row r="12" spans="1:80" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="268"/>
+      <c r="A12" s="308"/>
       <c r="B12" s="80"/>
       <c r="C12" s="81"/>
       <c r="D12" s="82"/>
@@ -9513,7 +9513,7 @@
       <c r="H12" s="84"/>
       <c r="I12" s="85"/>
       <c r="J12" s="86"/>
-      <c r="K12" s="323"/>
+      <c r="K12" s="274"/>
       <c r="L12" s="61">
         <v>0</v>
       </c>
@@ -9693,7 +9693,7 @@
       <c r="CB12" s="107"/>
     </row>
     <row r="13" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="268"/>
+      <c r="A13" s="308"/>
       <c r="B13" s="120">
         <v>1</v>
       </c>
@@ -9704,14 +9704,14 @@
         <v>-24.991141420000002</v>
       </c>
       <c r="E13" s="69" t="s">
-        <v>805</v>
+        <v>856</v>
       </c>
       <c r="F13" s="65"/>
       <c r="G13" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H13" s="69" t="s">
-        <v>850</v>
+        <v>806</v>
       </c>
       <c r="I13" s="64" t="s">
         <v>560</v>
@@ -9800,7 +9800,7 @@
       <c r="BV13" s="4"/>
       <c r="BW13" s="4"/>
       <c r="BX13" s="4"/>
-      <c r="BY13" s="319"/>
+      <c r="BY13" s="264"/>
       <c r="BZ13" s="122">
         <f t="shared" ref="BZ13:BZ56" si="1">SUMIF($L13:$BX13, "x", $L$12:$BX$12)</f>
         <v>150</v>
@@ -9809,7 +9809,7 @@
       <c r="CB13" s="107"/>
     </row>
     <row r="14" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="268"/>
+      <c r="A14" s="308"/>
       <c r="B14" s="120">
         <v>2</v>
       </c>
@@ -9820,14 +9820,14 @@
         <v>-24.989249229999999</v>
       </c>
       <c r="E14" s="69" t="s">
-        <v>806</v>
+        <v>857</v>
       </c>
       <c r="F14" s="65"/>
       <c r="G14" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H14" s="69" t="s">
-        <v>851</v>
+        <v>807</v>
       </c>
       <c r="I14" s="64" t="s">
         <v>560</v>
@@ -9916,7 +9916,7 @@
       <c r="BV14" s="4"/>
       <c r="BW14" s="4"/>
       <c r="BX14" s="4"/>
-      <c r="BY14" s="296"/>
+      <c r="BY14" s="265"/>
       <c r="BZ14" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -9925,7 +9925,7 @@
       <c r="CB14" s="107"/>
     </row>
     <row r="15" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="268"/>
+      <c r="A15" s="308"/>
       <c r="B15" s="120">
         <v>3</v>
       </c>
@@ -9936,14 +9936,14 @@
         <v>-24.989249229999999</v>
       </c>
       <c r="E15" s="69" t="s">
-        <v>807</v>
+        <v>858</v>
       </c>
       <c r="F15" s="65"/>
       <c r="G15" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H15" s="69" t="s">
-        <v>852</v>
+        <v>808</v>
       </c>
       <c r="I15" s="64" t="s">
         <v>560</v>
@@ -10032,7 +10032,7 @@
       <c r="BV15" s="4"/>
       <c r="BW15" s="4"/>
       <c r="BX15" s="4"/>
-      <c r="BY15" s="296"/>
+      <c r="BY15" s="265"/>
       <c r="BZ15" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -10041,7 +10041,7 @@
       <c r="CB15" s="107"/>
     </row>
     <row r="16" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="268"/>
+      <c r="A16" s="308"/>
       <c r="B16" s="120">
         <v>4</v>
       </c>
@@ -10052,14 +10052,14 @@
         <v>-24.980295649999999</v>
       </c>
       <c r="E16" s="69" t="s">
-        <v>808</v>
+        <v>859</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H16" s="69" t="s">
-        <v>853</v>
+        <v>809</v>
       </c>
       <c r="I16" s="64" t="s">
         <v>560</v>
@@ -10148,7 +10148,7 @@
       <c r="BV16" s="4"/>
       <c r="BW16" s="4"/>
       <c r="BX16" s="4"/>
-      <c r="BY16" s="296"/>
+      <c r="BY16" s="265"/>
       <c r="BZ16" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -10157,7 +10157,7 @@
       <c r="CB16" s="107"/>
     </row>
     <row r="17" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="268"/>
+      <c r="A17" s="308"/>
       <c r="B17" s="120">
         <v>5</v>
       </c>
@@ -10168,14 +10168,14 @@
         <v>-24.919689219999999</v>
       </c>
       <c r="E17" s="69" t="s">
-        <v>809</v>
+        <v>860</v>
       </c>
       <c r="F17" s="65"/>
       <c r="G17" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H17" s="69" t="s">
-        <v>854</v>
+        <v>810</v>
       </c>
       <c r="I17" s="64" t="s">
         <v>560</v>
@@ -10264,7 +10264,7 @@
       <c r="BV17" s="4"/>
       <c r="BW17" s="4"/>
       <c r="BX17" s="4"/>
-      <c r="BY17" s="296"/>
+      <c r="BY17" s="265"/>
       <c r="BZ17" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -10273,7 +10273,7 @@
       <c r="CB17" s="107"/>
     </row>
     <row r="18" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="268"/>
+      <c r="A18" s="308"/>
       <c r="B18" s="120">
         <v>6</v>
       </c>
@@ -10284,14 +10284,14 @@
         <v>-24.910317450000001</v>
       </c>
       <c r="E18" s="69" t="s">
-        <v>810</v>
+        <v>861</v>
       </c>
       <c r="F18" s="65"/>
       <c r="G18" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H18" s="69" t="s">
-        <v>855</v>
+        <v>811</v>
       </c>
       <c r="I18" s="64" t="s">
         <v>560</v>
@@ -10380,7 +10380,7 @@
       <c r="BV18" s="4"/>
       <c r="BW18" s="4"/>
       <c r="BX18" s="4"/>
-      <c r="BY18" s="296"/>
+      <c r="BY18" s="265"/>
       <c r="BZ18" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -10389,7 +10389,7 @@
       <c r="CB18" s="107"/>
     </row>
     <row r="19" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="268"/>
+      <c r="A19" s="308"/>
       <c r="B19" s="120">
         <v>7</v>
       </c>
@@ -10400,14 +10400,14 @@
         <v>-24.91638038</v>
       </c>
       <c r="E19" s="69" t="s">
-        <v>811</v>
+        <v>862</v>
       </c>
       <c r="F19" s="65"/>
       <c r="G19" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H19" s="69" t="s">
-        <v>856</v>
+        <v>812</v>
       </c>
       <c r="I19" s="64" t="s">
         <v>560</v>
@@ -10496,7 +10496,7 @@
       <c r="BV19" s="4"/>
       <c r="BW19" s="4"/>
       <c r="BX19" s="4"/>
-      <c r="BY19" s="296"/>
+      <c r="BY19" s="265"/>
       <c r="BZ19" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -10505,7 +10505,7 @@
       <c r="CB19" s="107"/>
     </row>
     <row r="20" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="268"/>
+      <c r="A20" s="308"/>
       <c r="B20" s="120">
         <v>8</v>
       </c>
@@ -10516,14 +10516,14 @@
         <v>-24.906146289999999</v>
       </c>
       <c r="E20" s="69" t="s">
-        <v>812</v>
+        <v>863</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H20" s="69" t="s">
-        <v>857</v>
+        <v>813</v>
       </c>
       <c r="I20" s="64" t="s">
         <v>560</v>
@@ -10612,7 +10612,7 @@
       <c r="BV20" s="4"/>
       <c r="BW20" s="4"/>
       <c r="BX20" s="4"/>
-      <c r="BY20" s="296"/>
+      <c r="BY20" s="265"/>
       <c r="BZ20" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -10621,7 +10621,7 @@
       <c r="CB20" s="107"/>
     </row>
     <row r="21" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="268"/>
+      <c r="A21" s="308"/>
       <c r="B21" s="120">
         <v>9</v>
       </c>
@@ -10632,14 +10632,14 @@
         <v>-24.902915920000002</v>
       </c>
       <c r="E21" s="69" t="s">
-        <v>813</v>
+        <v>864</v>
       </c>
       <c r="F21" s="65"/>
       <c r="G21" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H21" s="69" t="s">
-        <v>858</v>
+        <v>814</v>
       </c>
       <c r="I21" s="64" t="s">
         <v>560</v>
@@ -10728,7 +10728,7 @@
       <c r="BV21" s="4"/>
       <c r="BW21" s="4"/>
       <c r="BX21" s="4"/>
-      <c r="BY21" s="296"/>
+      <c r="BY21" s="265"/>
       <c r="BZ21" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -10737,7 +10737,7 @@
       <c r="CB21" s="107"/>
     </row>
     <row r="22" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="268"/>
+      <c r="A22" s="308"/>
       <c r="B22" s="120">
         <v>10</v>
       </c>
@@ -10748,14 +10748,14 @@
         <v>-24.902915920000002</v>
       </c>
       <c r="E22" s="69" t="s">
-        <v>814</v>
+        <v>865</v>
       </c>
       <c r="F22" s="65"/>
       <c r="G22" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H22" s="69" t="s">
-        <v>859</v>
+        <v>815</v>
       </c>
       <c r="I22" s="64" t="s">
         <v>560</v>
@@ -10844,7 +10844,7 @@
       <c r="BV22" s="4"/>
       <c r="BW22" s="4"/>
       <c r="BX22" s="4"/>
-      <c r="BY22" s="296"/>
+      <c r="BY22" s="265"/>
       <c r="BZ22" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -10853,7 +10853,7 @@
       <c r="CB22" s="107"/>
     </row>
     <row r="23" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="268"/>
+      <c r="A23" s="308"/>
       <c r="B23" s="120">
         <v>11</v>
       </c>
@@ -10864,14 +10864,14 @@
         <v>-24.893052699999998</v>
       </c>
       <c r="E23" s="69" t="s">
-        <v>815</v>
+        <v>866</v>
       </c>
       <c r="F23" s="65"/>
       <c r="G23" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H23" s="69" t="s">
-        <v>860</v>
+        <v>816</v>
       </c>
       <c r="I23" s="64" t="s">
         <v>560</v>
@@ -10960,7 +10960,7 @@
       <c r="BV23" s="4"/>
       <c r="BW23" s="4"/>
       <c r="BX23" s="4"/>
-      <c r="BY23" s="296"/>
+      <c r="BY23" s="265"/>
       <c r="BZ23" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -10969,7 +10969,7 @@
       <c r="CB23" s="107"/>
     </row>
     <row r="24" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="268"/>
+      <c r="A24" s="308"/>
       <c r="B24" s="120">
         <v>12</v>
       </c>
@@ -10980,14 +10980,14 @@
         <v>-24.859047289999999</v>
       </c>
       <c r="E24" s="69" t="s">
-        <v>816</v>
+        <v>867</v>
       </c>
       <c r="F24" s="65"/>
       <c r="G24" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H24" s="69" t="s">
-        <v>861</v>
+        <v>817</v>
       </c>
       <c r="I24" s="64" t="s">
         <v>560</v>
@@ -11076,7 +11076,7 @@
       <c r="BV24" s="4"/>
       <c r="BW24" s="4"/>
       <c r="BX24" s="4"/>
-      <c r="BY24" s="296"/>
+      <c r="BY24" s="265"/>
       <c r="BZ24" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -11085,7 +11085,7 @@
       <c r="CB24" s="107"/>
     </row>
     <row r="25" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="268"/>
+      <c r="A25" s="308"/>
       <c r="B25" s="120">
         <v>13</v>
       </c>
@@ -11096,14 +11096,14 @@
         <v>-24.847029429999999</v>
       </c>
       <c r="E25" s="69" t="s">
-        <v>817</v>
+        <v>868</v>
       </c>
       <c r="F25" s="65"/>
       <c r="G25" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H25" s="69" t="s">
-        <v>862</v>
+        <v>818</v>
       </c>
       <c r="I25" s="64" t="s">
         <v>560</v>
@@ -11192,7 +11192,7 @@
       <c r="BV25" s="4"/>
       <c r="BW25" s="4"/>
       <c r="BX25" s="4"/>
-      <c r="BY25" s="296"/>
+      <c r="BY25" s="265"/>
       <c r="BZ25" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -11201,7 +11201,7 @@
       <c r="CB25" s="107"/>
     </row>
     <row r="26" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="268"/>
+      <c r="A26" s="308"/>
       <c r="B26" s="120">
         <v>14</v>
       </c>
@@ -11212,14 +11212,14 @@
         <v>-24.829678860000001</v>
       </c>
       <c r="E26" s="69" t="s">
-        <v>818</v>
+        <v>869</v>
       </c>
       <c r="F26" s="65"/>
       <c r="G26" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H26" s="69" t="s">
-        <v>863</v>
+        <v>819</v>
       </c>
       <c r="I26" s="64" t="s">
         <v>560</v>
@@ -11308,7 +11308,7 @@
       <c r="BV26" s="4"/>
       <c r="BW26" s="4"/>
       <c r="BX26" s="4"/>
-      <c r="BY26" s="296"/>
+      <c r="BY26" s="265"/>
       <c r="BZ26" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -11317,7 +11317,7 @@
       <c r="CB26" s="107"/>
     </row>
     <row r="27" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="268"/>
+      <c r="A27" s="308"/>
       <c r="B27" s="120">
         <v>15</v>
       </c>
@@ -11328,14 +11328,14 @@
         <v>-24.807529809999998</v>
       </c>
       <c r="E27" s="69" t="s">
-        <v>819</v>
+        <v>870</v>
       </c>
       <c r="F27" s="65"/>
       <c r="G27" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H27" s="69" t="s">
-        <v>864</v>
+        <v>820</v>
       </c>
       <c r="I27" s="64" t="s">
         <v>560</v>
@@ -11424,7 +11424,7 @@
       <c r="BV27" s="4"/>
       <c r="BW27" s="4"/>
       <c r="BX27" s="4"/>
-      <c r="BY27" s="296"/>
+      <c r="BY27" s="265"/>
       <c r="BZ27" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -11433,7 +11433,7 @@
       <c r="CB27" s="107"/>
     </row>
     <row r="28" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="268"/>
+      <c r="A28" s="308"/>
       <c r="B28" s="120">
         <v>16</v>
       </c>
@@ -11444,14 +11444,14 @@
         <v>-24.779475059999999</v>
       </c>
       <c r="E28" s="69" t="s">
-        <v>820</v>
+        <v>871</v>
       </c>
       <c r="F28" s="65"/>
       <c r="G28" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H28" s="69" t="s">
-        <v>865</v>
+        <v>821</v>
       </c>
       <c r="I28" s="64" t="s">
         <v>560</v>
@@ -11540,7 +11540,7 @@
       <c r="BV28" s="4"/>
       <c r="BW28" s="4"/>
       <c r="BX28" s="4"/>
-      <c r="BY28" s="296"/>
+      <c r="BY28" s="265"/>
       <c r="BZ28" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -11549,7 +11549,7 @@
       <c r="CB28" s="107"/>
     </row>
     <row r="29" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="268"/>
+      <c r="A29" s="308"/>
       <c r="B29" s="120">
         <v>17</v>
       </c>
@@ -11560,14 +11560,14 @@
         <v>-24.768206240000001</v>
       </c>
       <c r="E29" s="69" t="s">
-        <v>821</v>
+        <v>872</v>
       </c>
       <c r="F29" s="65"/>
       <c r="G29" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H29" s="69" t="s">
-        <v>866</v>
+        <v>822</v>
       </c>
       <c r="I29" s="64" t="s">
         <v>560</v>
@@ -11656,7 +11656,7 @@
       <c r="BV29" s="4"/>
       <c r="BW29" s="4"/>
       <c r="BX29" s="4"/>
-      <c r="BY29" s="296"/>
+      <c r="BY29" s="265"/>
       <c r="BZ29" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -11665,7 +11665,7 @@
       <c r="CB29" s="107"/>
     </row>
     <row r="30" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="268"/>
+      <c r="A30" s="308"/>
       <c r="B30" s="120">
         <v>18</v>
       </c>
@@ -11676,14 +11676,14 @@
         <v>-24.756586049999999</v>
       </c>
       <c r="E30" s="69" t="s">
-        <v>822</v>
+        <v>873</v>
       </c>
       <c r="F30" s="65"/>
       <c r="G30" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H30" s="69" t="s">
-        <v>867</v>
+        <v>823</v>
       </c>
       <c r="I30" s="64" t="s">
         <v>560</v>
@@ -11772,7 +11772,7 @@
       <c r="BV30" s="4"/>
       <c r="BW30" s="4"/>
       <c r="BX30" s="4"/>
-      <c r="BY30" s="296"/>
+      <c r="BY30" s="265"/>
       <c r="BZ30" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -11781,7 +11781,7 @@
       <c r="CB30" s="107"/>
     </row>
     <row r="31" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="268"/>
+      <c r="A31" s="308"/>
       <c r="B31" s="120">
         <v>19</v>
       </c>
@@ -11792,14 +11792,14 @@
         <v>-24.741586699999999</v>
       </c>
       <c r="E31" s="69" t="s">
-        <v>823</v>
+        <v>874</v>
       </c>
       <c r="F31" s="65"/>
       <c r="G31" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H31" s="69" t="s">
-        <v>868</v>
+        <v>824</v>
       </c>
       <c r="I31" s="64" t="s">
         <v>560</v>
@@ -11888,7 +11888,7 @@
       <c r="BV31" s="4"/>
       <c r="BW31" s="4"/>
       <c r="BX31" s="4"/>
-      <c r="BY31" s="296"/>
+      <c r="BY31" s="265"/>
       <c r="BZ31" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -11897,7 +11897,7 @@
       <c r="CB31" s="107"/>
     </row>
     <row r="32" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="268"/>
+      <c r="A32" s="308"/>
       <c r="B32" s="120">
         <v>20</v>
       </c>
@@ -11908,14 +11908,14 @@
         <v>-24.720987969999999</v>
       </c>
       <c r="E32" s="69" t="s">
-        <v>824</v>
+        <v>875</v>
       </c>
       <c r="F32" s="65"/>
       <c r="G32" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H32" s="69" t="s">
-        <v>869</v>
+        <v>825</v>
       </c>
       <c r="I32" s="64" t="s">
         <v>560</v>
@@ -12004,7 +12004,7 @@
       <c r="BV32" s="4"/>
       <c r="BW32" s="4"/>
       <c r="BX32" s="4"/>
-      <c r="BY32" s="296"/>
+      <c r="BY32" s="265"/>
       <c r="BZ32" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -12013,7 +12013,7 @@
       <c r="CB32" s="107"/>
     </row>
     <row r="33" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="268"/>
+      <c r="A33" s="308"/>
       <c r="B33" s="120">
         <v>21</v>
       </c>
@@ -12024,14 +12024,14 @@
         <v>-24.718220930000001</v>
       </c>
       <c r="E33" s="69" t="s">
-        <v>825</v>
+        <v>876</v>
       </c>
       <c r="F33" s="65"/>
       <c r="G33" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H33" s="69" t="s">
-        <v>870</v>
+        <v>826</v>
       </c>
       <c r="I33" s="64" t="s">
         <v>560</v>
@@ -12120,7 +12120,7 @@
       <c r="BV33" s="4"/>
       <c r="BW33" s="4"/>
       <c r="BX33" s="4"/>
-      <c r="BY33" s="296"/>
+      <c r="BY33" s="265"/>
       <c r="BZ33" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -12129,7 +12129,7 @@
       <c r="CB33" s="107"/>
     </row>
     <row r="34" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="268"/>
+      <c r="A34" s="308"/>
       <c r="B34" s="120">
         <v>22</v>
       </c>
@@ -12140,14 +12140,14 @@
         <v>-24.70942522</v>
       </c>
       <c r="E34" s="69" t="s">
-        <v>826</v>
+        <v>877</v>
       </c>
       <c r="F34" s="65"/>
       <c r="G34" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H34" s="69" t="s">
-        <v>871</v>
+        <v>827</v>
       </c>
       <c r="I34" s="64" t="s">
         <v>560</v>
@@ -12236,7 +12236,7 @@
       <c r="BV34" s="4"/>
       <c r="BW34" s="4"/>
       <c r="BX34" s="4"/>
-      <c r="BY34" s="296"/>
+      <c r="BY34" s="265"/>
       <c r="BZ34" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -12245,7 +12245,7 @@
       <c r="CB34" s="107"/>
     </row>
     <row r="35" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="268"/>
+      <c r="A35" s="308"/>
       <c r="B35" s="120">
         <v>23</v>
       </c>
@@ -12256,14 +12256,14 @@
         <v>-24.697864330000002</v>
       </c>
       <c r="E35" s="69" t="s">
-        <v>827</v>
+        <v>878</v>
       </c>
       <c r="F35" s="65"/>
       <c r="G35" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H35" s="69" t="s">
-        <v>872</v>
+        <v>828</v>
       </c>
       <c r="I35" s="64" t="s">
         <v>560</v>
@@ -12352,7 +12352,7 @@
       <c r="BV35" s="4"/>
       <c r="BW35" s="4"/>
       <c r="BX35" s="4"/>
-      <c r="BY35" s="296"/>
+      <c r="BY35" s="265"/>
       <c r="BZ35" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -12361,7 +12361,7 @@
       <c r="CB35" s="107"/>
     </row>
     <row r="36" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="268"/>
+      <c r="A36" s="308"/>
       <c r="B36" s="120">
         <v>24</v>
       </c>
@@ -12372,14 +12372,14 @@
         <v>-24.693880799999999</v>
       </c>
       <c r="E36" s="69" t="s">
-        <v>828</v>
+        <v>879</v>
       </c>
       <c r="F36" s="65"/>
       <c r="G36" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H36" s="69" t="s">
-        <v>873</v>
+        <v>829</v>
       </c>
       <c r="I36" s="64" t="s">
         <v>560</v>
@@ -12468,7 +12468,7 @@
       <c r="BV36" s="4"/>
       <c r="BW36" s="4"/>
       <c r="BX36" s="4"/>
-      <c r="BY36" s="296"/>
+      <c r="BY36" s="265"/>
       <c r="BZ36" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -12477,7 +12477,7 @@
       <c r="CB36" s="107"/>
     </row>
     <row r="37" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="268"/>
+      <c r="A37" s="308"/>
       <c r="B37" s="120">
         <v>25</v>
       </c>
@@ -12488,14 +12488,14 @@
         <v>-24.693880799999999</v>
       </c>
       <c r="E37" s="69" t="s">
-        <v>829</v>
+        <v>880</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H37" s="69" t="s">
-        <v>874</v>
+        <v>830</v>
       </c>
       <c r="I37" s="64" t="s">
         <v>560</v>
@@ -12584,7 +12584,7 @@
       <c r="BV37" s="4"/>
       <c r="BW37" s="4"/>
       <c r="BX37" s="4"/>
-      <c r="BY37" s="296"/>
+      <c r="BY37" s="265"/>
       <c r="BZ37" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -12593,7 +12593,7 @@
       <c r="CB37" s="107"/>
     </row>
     <row r="38" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="268"/>
+      <c r="A38" s="308"/>
       <c r="B38" s="120">
         <v>26</v>
       </c>
@@ -12604,14 +12604,14 @@
         <v>-24.691585509999999</v>
       </c>
       <c r="E38" s="69" t="s">
-        <v>830</v>
+        <v>881</v>
       </c>
       <c r="F38" s="65"/>
       <c r="G38" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H38" s="69" t="s">
-        <v>875</v>
+        <v>831</v>
       </c>
       <c r="I38" s="64" t="s">
         <v>560</v>
@@ -12700,7 +12700,7 @@
       <c r="BV38" s="4"/>
       <c r="BW38" s="4"/>
       <c r="BX38" s="4"/>
-      <c r="BY38" s="296"/>
+      <c r="BY38" s="265"/>
       <c r="BZ38" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -12709,7 +12709,7 @@
       <c r="CB38" s="107"/>
     </row>
     <row r="39" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="268"/>
+      <c r="A39" s="308"/>
       <c r="B39" s="120">
         <v>27</v>
       </c>
@@ -12720,14 +12720,14 @@
         <v>-24.684366619999999</v>
       </c>
       <c r="E39" s="69" t="s">
-        <v>831</v>
+        <v>882</v>
       </c>
       <c r="F39" s="65"/>
       <c r="G39" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H39" s="69" t="s">
-        <v>876</v>
+        <v>832</v>
       </c>
       <c r="I39" s="64" t="s">
         <v>560</v>
@@ -12816,7 +12816,7 @@
       <c r="BV39" s="4"/>
       <c r="BW39" s="4"/>
       <c r="BX39" s="4"/>
-      <c r="BY39" s="296"/>
+      <c r="BY39" s="265"/>
       <c r="BZ39" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -12825,7 +12825,7 @@
       <c r="CB39" s="107"/>
     </row>
     <row r="40" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="268"/>
+      <c r="A40" s="308"/>
       <c r="B40" s="120">
         <v>28</v>
       </c>
@@ -12836,14 +12836,14 @@
         <v>-24.685839900000001</v>
       </c>
       <c r="E40" s="69" t="s">
-        <v>832</v>
+        <v>883</v>
       </c>
       <c r="F40" s="65"/>
       <c r="G40" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H40" s="69" t="s">
-        <v>877</v>
+        <v>833</v>
       </c>
       <c r="I40" s="64" t="s">
         <v>560</v>
@@ -12932,7 +12932,7 @@
       <c r="BV40" s="4"/>
       <c r="BW40" s="4"/>
       <c r="BX40" s="4"/>
-      <c r="BY40" s="296"/>
+      <c r="BY40" s="265"/>
       <c r="BZ40" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -12941,7 +12941,7 @@
       <c r="CB40" s="107"/>
     </row>
     <row r="41" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="268"/>
+      <c r="A41" s="308"/>
       <c r="B41" s="120">
         <v>29</v>
       </c>
@@ -12952,14 +12952,14 @@
         <v>-24.684785900000001</v>
       </c>
       <c r="E41" s="69" t="s">
-        <v>833</v>
+        <v>884</v>
       </c>
       <c r="F41" s="65"/>
       <c r="G41" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H41" s="69" t="s">
-        <v>878</v>
+        <v>834</v>
       </c>
       <c r="I41" s="64" t="s">
         <v>560</v>
@@ -13048,7 +13048,7 @@
       <c r="BV41" s="4"/>
       <c r="BW41" s="4"/>
       <c r="BX41" s="4"/>
-      <c r="BY41" s="296"/>
+      <c r="BY41" s="265"/>
       <c r="BZ41" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -13057,7 +13057,7 @@
       <c r="CB41" s="107"/>
     </row>
     <row r="42" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="268"/>
+      <c r="A42" s="308"/>
       <c r="B42" s="120">
         <v>30</v>
       </c>
@@ -13068,14 +13068,14 @@
         <v>-24.684785900000001</v>
       </c>
       <c r="E42" s="69" t="s">
-        <v>834</v>
+        <v>885</v>
       </c>
       <c r="F42" s="65"/>
       <c r="G42" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H42" s="69" t="s">
-        <v>879</v>
+        <v>835</v>
       </c>
       <c r="I42" s="64" t="s">
         <v>560</v>
@@ -13164,7 +13164,7 @@
       <c r="BV42" s="4"/>
       <c r="BW42" s="4"/>
       <c r="BX42" s="4"/>
-      <c r="BY42" s="296"/>
+      <c r="BY42" s="265"/>
       <c r="BZ42" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -13173,7 +13173,7 @@
       <c r="CB42" s="107"/>
     </row>
     <row r="43" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="268"/>
+      <c r="A43" s="308"/>
       <c r="B43" s="120">
         <v>31</v>
       </c>
@@ -13184,14 +13184,14 @@
         <v>-24.684196060000001</v>
       </c>
       <c r="E43" s="69" t="s">
-        <v>835</v>
+        <v>886</v>
       </c>
       <c r="F43" s="65"/>
       <c r="G43" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H43" s="69" t="s">
-        <v>880</v>
+        <v>836</v>
       </c>
       <c r="I43" s="64" t="s">
         <v>560</v>
@@ -13280,7 +13280,7 @@
       <c r="BV43" s="4"/>
       <c r="BW43" s="4"/>
       <c r="BX43" s="4"/>
-      <c r="BY43" s="296"/>
+      <c r="BY43" s="265"/>
       <c r="BZ43" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -13289,7 +13289,7 @@
       <c r="CB43" s="107"/>
     </row>
     <row r="44" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="268"/>
+      <c r="A44" s="308"/>
       <c r="B44" s="120">
         <v>32</v>
       </c>
@@ -13300,14 +13300,14 @@
         <v>-24.666214360000001</v>
       </c>
       <c r="E44" s="69" t="s">
-        <v>836</v>
+        <v>887</v>
       </c>
       <c r="F44" s="65"/>
       <c r="G44" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H44" s="69" t="s">
-        <v>881</v>
+        <v>837</v>
       </c>
       <c r="I44" s="64" t="s">
         <v>560</v>
@@ -13396,7 +13396,7 @@
       <c r="BV44" s="4"/>
       <c r="BW44" s="4"/>
       <c r="BX44" s="4"/>
-      <c r="BY44" s="296"/>
+      <c r="BY44" s="265"/>
       <c r="BZ44" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -13405,7 +13405,7 @@
       <c r="CB44" s="107"/>
     </row>
     <row r="45" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="268"/>
+      <c r="A45" s="308"/>
       <c r="B45" s="120">
         <v>33</v>
       </c>
@@ -13416,14 +13416,14 @@
         <v>-24.660029699999999</v>
       </c>
       <c r="E45" s="69" t="s">
-        <v>837</v>
+        <v>888</v>
       </c>
       <c r="F45" s="65"/>
       <c r="G45" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H45" s="69" t="s">
-        <v>882</v>
+        <v>838</v>
       </c>
       <c r="I45" s="64" t="s">
         <v>560</v>
@@ -13512,7 +13512,7 @@
       <c r="BV45" s="4"/>
       <c r="BW45" s="4"/>
       <c r="BX45" s="4"/>
-      <c r="BY45" s="296"/>
+      <c r="BY45" s="265"/>
       <c r="BZ45" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -13521,7 +13521,7 @@
       <c r="CB45" s="107"/>
     </row>
     <row r="46" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="268"/>
+      <c r="A46" s="308"/>
       <c r="B46" s="120">
         <v>34</v>
       </c>
@@ -13532,14 +13532,14 @@
         <v>-24.659087639999999</v>
       </c>
       <c r="E46" s="69" t="s">
-        <v>838</v>
+        <v>889</v>
       </c>
       <c r="F46" s="65"/>
       <c r="G46" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H46" s="69" t="s">
-        <v>883</v>
+        <v>839</v>
       </c>
       <c r="I46" s="64" t="s">
         <v>560</v>
@@ -13628,7 +13628,7 @@
       <c r="BV46" s="4"/>
       <c r="BW46" s="4"/>
       <c r="BX46" s="4"/>
-      <c r="BY46" s="296"/>
+      <c r="BY46" s="265"/>
       <c r="BZ46" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -13637,7 +13637,7 @@
       <c r="CB46" s="107"/>
     </row>
     <row r="47" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="268"/>
+      <c r="A47" s="308"/>
       <c r="B47" s="120">
         <v>35</v>
       </c>
@@ -13648,14 +13648,14 @@
         <v>-24.66255035</v>
       </c>
       <c r="E47" s="69" t="s">
-        <v>839</v>
+        <v>890</v>
       </c>
       <c r="F47" s="65"/>
       <c r="G47" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H47" s="69" t="s">
-        <v>884</v>
+        <v>840</v>
       </c>
       <c r="I47" s="64" t="s">
         <v>560</v>
@@ -13744,7 +13744,7 @@
       <c r="BV47" s="4"/>
       <c r="BW47" s="4"/>
       <c r="BX47" s="4"/>
-      <c r="BY47" s="296"/>
+      <c r="BY47" s="265"/>
       <c r="BZ47" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -13753,7 +13753,7 @@
       <c r="CB47" s="107"/>
     </row>
     <row r="48" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="268"/>
+      <c r="A48" s="308"/>
       <c r="B48" s="120">
         <v>36</v>
       </c>
@@ -13764,14 +13764,14 @@
         <v>-24.67002707</v>
       </c>
       <c r="E48" s="69" t="s">
-        <v>840</v>
+        <v>891</v>
       </c>
       <c r="F48" s="65"/>
       <c r="G48" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H48" s="69" t="s">
-        <v>885</v>
+        <v>841</v>
       </c>
       <c r="I48" s="64" t="s">
         <v>560</v>
@@ -13860,7 +13860,7 @@
       <c r="BV48" s="4"/>
       <c r="BW48" s="4"/>
       <c r="BX48" s="4"/>
-      <c r="BY48" s="296"/>
+      <c r="BY48" s="265"/>
       <c r="BZ48" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -13869,7 +13869,7 @@
       <c r="CB48" s="107"/>
     </row>
     <row r="49" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="268"/>
+      <c r="A49" s="308"/>
       <c r="B49" s="120">
         <v>37</v>
       </c>
@@ -13880,14 +13880,14 @@
         <v>-24.648686250000001</v>
       </c>
       <c r="E49" s="69" t="s">
-        <v>841</v>
+        <v>892</v>
       </c>
       <c r="F49" s="65"/>
       <c r="G49" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H49" s="69" t="s">
-        <v>886</v>
+        <v>842</v>
       </c>
       <c r="I49" s="64" t="s">
         <v>560</v>
@@ -13976,7 +13976,7 @@
       <c r="BV49" s="4"/>
       <c r="BW49" s="4"/>
       <c r="BX49" s="4"/>
-      <c r="BY49" s="296"/>
+      <c r="BY49" s="265"/>
       <c r="BZ49" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -13985,7 +13985,7 @@
       <c r="CB49" s="107"/>
     </row>
     <row r="50" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="268"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="120">
         <v>38</v>
       </c>
@@ -13996,14 +13996,14 @@
         <v>-24.63116398</v>
       </c>
       <c r="E50" s="69" t="s">
-        <v>842</v>
+        <v>893</v>
       </c>
       <c r="F50" s="65"/>
       <c r="G50" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H50" s="69" t="s">
-        <v>887</v>
+        <v>843</v>
       </c>
       <c r="I50" s="64" t="s">
         <v>560</v>
@@ -14092,7 +14092,7 @@
       <c r="BV50" s="4"/>
       <c r="BW50" s="4"/>
       <c r="BX50" s="4"/>
-      <c r="BY50" s="296"/>
+      <c r="BY50" s="265"/>
       <c r="BZ50" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -14101,7 +14101,7 @@
       <c r="CB50" s="107"/>
     </row>
     <row r="51" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="268"/>
+      <c r="A51" s="308"/>
       <c r="B51" s="120">
         <v>39</v>
       </c>
@@ -14112,14 +14112,14 @@
         <v>-24.632860130000001</v>
       </c>
       <c r="E51" s="69" t="s">
-        <v>843</v>
+        <v>894</v>
       </c>
       <c r="F51" s="65"/>
       <c r="G51" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H51" s="69" t="s">
-        <v>888</v>
+        <v>844</v>
       </c>
       <c r="I51" s="64" t="s">
         <v>560</v>
@@ -14208,7 +14208,7 @@
       <c r="BV51" s="4"/>
       <c r="BW51" s="4"/>
       <c r="BX51" s="4"/>
-      <c r="BY51" s="296"/>
+      <c r="BY51" s="265"/>
       <c r="BZ51" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -14217,7 +14217,7 @@
       <c r="CB51" s="107"/>
     </row>
     <row r="52" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="268"/>
+      <c r="A52" s="308"/>
       <c r="B52" s="120">
         <v>40</v>
       </c>
@@ -14228,14 +14228,14 @@
         <v>-24.616549339999999</v>
       </c>
       <c r="E52" s="69" t="s">
-        <v>844</v>
+        <v>895</v>
       </c>
       <c r="F52" s="65"/>
       <c r="G52" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H52" s="69" t="s">
-        <v>889</v>
+        <v>845</v>
       </c>
       <c r="I52" s="64" t="s">
         <v>560</v>
@@ -14324,7 +14324,7 @@
       <c r="BV52" s="4"/>
       <c r="BW52" s="4"/>
       <c r="BX52" s="4"/>
-      <c r="BY52" s="296"/>
+      <c r="BY52" s="265"/>
       <c r="BZ52" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -14333,7 +14333,7 @@
       <c r="CB52" s="107"/>
     </row>
     <row r="53" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="268"/>
+      <c r="A53" s="308"/>
       <c r="B53" s="120">
         <v>41</v>
       </c>
@@ -14344,14 +14344,14 @@
         <v>-24.615831379999999</v>
       </c>
       <c r="E53" s="69" t="s">
-        <v>845</v>
+        <v>896</v>
       </c>
       <c r="F53" s="65"/>
       <c r="G53" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H53" s="69" t="s">
-        <v>890</v>
+        <v>846</v>
       </c>
       <c r="I53" s="64" t="s">
         <v>560</v>
@@ -14440,7 +14440,7 @@
       <c r="BV53" s="4"/>
       <c r="BW53" s="4"/>
       <c r="BX53" s="4"/>
-      <c r="BY53" s="296"/>
+      <c r="BY53" s="265"/>
       <c r="BZ53" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -14449,7 +14449,7 @@
       <c r="CB53" s="107"/>
     </row>
     <row r="54" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="268"/>
+      <c r="A54" s="308"/>
       <c r="B54" s="120">
         <v>42</v>
       </c>
@@ -14460,14 +14460,14 @@
         <v>-24.56820304</v>
       </c>
       <c r="E54" s="69" t="s">
-        <v>846</v>
+        <v>897</v>
       </c>
       <c r="F54" s="65"/>
       <c r="G54" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H54" s="69" t="s">
-        <v>891</v>
+        <v>847</v>
       </c>
       <c r="I54" s="64" t="s">
         <v>560</v>
@@ -14556,7 +14556,7 @@
       <c r="BV54" s="4"/>
       <c r="BW54" s="4"/>
       <c r="BX54" s="4"/>
-      <c r="BY54" s="296"/>
+      <c r="BY54" s="265"/>
       <c r="BZ54" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -14565,7 +14565,7 @@
       <c r="CB54" s="107"/>
     </row>
     <row r="55" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="268"/>
+      <c r="A55" s="308"/>
       <c r="B55" s="120">
         <v>43</v>
       </c>
@@ -14576,14 +14576,14 @@
         <v>-24.548045290000001</v>
       </c>
       <c r="E55" s="69" t="s">
-        <v>847</v>
+        <v>898</v>
       </c>
       <c r="F55" s="65"/>
       <c r="G55" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H55" s="69" t="s">
-        <v>892</v>
+        <v>848</v>
       </c>
       <c r="I55" s="64" t="s">
         <v>560</v>
@@ -14672,7 +14672,7 @@
       <c r="BV55" s="4"/>
       <c r="BW55" s="4"/>
       <c r="BX55" s="4"/>
-      <c r="BY55" s="296"/>
+      <c r="BY55" s="265"/>
       <c r="BZ55" s="123">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -14681,7 +14681,7 @@
       <c r="CB55" s="107"/>
     </row>
     <row r="56" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="268"/>
+      <c r="A56" s="308"/>
       <c r="B56" s="120">
         <v>44</v>
       </c>
@@ -14692,14 +14692,14 @@
         <v>-24.547319890000001</v>
       </c>
       <c r="E56" s="69" t="s">
-        <v>848</v>
+        <v>899</v>
       </c>
       <c r="F56" s="65"/>
       <c r="G56" s="63" t="s">
+        <v>805</v>
+      </c>
+      <c r="H56" s="69" t="s">
         <v>849</v>
-      </c>
-      <c r="H56" s="69" t="s">
-        <v>893</v>
       </c>
       <c r="I56" s="64" t="s">
         <v>560</v>
@@ -14788,7 +14788,7 @@
       <c r="BV56" s="4"/>
       <c r="BW56" s="4"/>
       <c r="BX56" s="4"/>
-      <c r="BY56" s="320"/>
+      <c r="BY56" s="266"/>
       <c r="BZ56" s="124">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -14797,12 +14797,12 @@
       <c r="CB56" s="107"/>
     </row>
     <row r="57" spans="1:80" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="268"/>
-      <c r="B57" s="314"/>
-      <c r="C57" s="315"/>
-      <c r="D57" s="315"/>
-      <c r="E57" s="315"/>
-      <c r="F57" s="315"/>
+      <c r="A57" s="308"/>
+      <c r="B57" s="300"/>
+      <c r="C57" s="301"/>
+      <c r="D57" s="301"/>
+      <c r="E57" s="301"/>
+      <c r="F57" s="301"/>
       <c r="G57" s="32"/>
       <c r="H57" s="32"/>
       <c r="I57" s="32"/>
@@ -14879,58 +14879,58 @@
       <c r="CB57" s="107"/>
     </row>
     <row r="58" spans="1:80" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="268"/>
-      <c r="B58" s="316"/>
-      <c r="C58" s="267"/>
-      <c r="D58" s="267"/>
-      <c r="E58" s="267"/>
-      <c r="F58" s="267"/>
+      <c r="A58" s="308"/>
+      <c r="B58" s="302"/>
+      <c r="C58" s="281"/>
+      <c r="D58" s="281"/>
+      <c r="E58" s="281"/>
+      <c r="F58" s="281"/>
       <c r="G58" s="17"/>
       <c r="H58" s="17"/>
       <c r="I58" s="17"/>
-      <c r="J58" s="321"/>
-      <c r="K58" s="321"/>
-      <c r="L58" s="321"/>
-      <c r="M58" s="321"/>
-      <c r="N58" s="321"/>
-      <c r="O58" s="321"/>
-      <c r="P58" s="321"/>
-      <c r="Q58" s="321"/>
-      <c r="R58" s="321"/>
-      <c r="S58" s="321"/>
-      <c r="T58" s="321"/>
-      <c r="U58" s="321"/>
-      <c r="V58" s="321"/>
-      <c r="W58" s="321"/>
-      <c r="X58" s="321"/>
-      <c r="Y58" s="321"/>
-      <c r="Z58" s="321"/>
-      <c r="AA58" s="321"/>
-      <c r="AB58" s="321"/>
-      <c r="AC58" s="321"/>
-      <c r="AD58" s="321"/>
-      <c r="AE58" s="321"/>
-      <c r="AF58" s="321"/>
-      <c r="AG58" s="321"/>
-      <c r="AH58" s="321"/>
-      <c r="AI58" s="321"/>
-      <c r="AJ58" s="321"/>
-      <c r="AK58" s="321"/>
-      <c r="AL58" s="321"/>
-      <c r="AM58" s="321"/>
-      <c r="AN58" s="321"/>
-      <c r="AO58" s="321"/>
-      <c r="AP58" s="321"/>
-      <c r="AQ58" s="321"/>
-      <c r="AR58" s="321"/>
-      <c r="AS58" s="321"/>
-      <c r="AT58" s="321"/>
-      <c r="AU58" s="321"/>
-      <c r="AV58" s="321"/>
-      <c r="AW58" s="321"/>
-      <c r="AX58" s="321"/>
-      <c r="AY58" s="321"/>
-      <c r="AZ58" s="321"/>
+      <c r="J58" s="267"/>
+      <c r="K58" s="267"/>
+      <c r="L58" s="267"/>
+      <c r="M58" s="267"/>
+      <c r="N58" s="267"/>
+      <c r="O58" s="267"/>
+      <c r="P58" s="267"/>
+      <c r="Q58" s="267"/>
+      <c r="R58" s="267"/>
+      <c r="S58" s="267"/>
+      <c r="T58" s="267"/>
+      <c r="U58" s="267"/>
+      <c r="V58" s="267"/>
+      <c r="W58" s="267"/>
+      <c r="X58" s="267"/>
+      <c r="Y58" s="267"/>
+      <c r="Z58" s="267"/>
+      <c r="AA58" s="267"/>
+      <c r="AB58" s="267"/>
+      <c r="AC58" s="267"/>
+      <c r="AD58" s="267"/>
+      <c r="AE58" s="267"/>
+      <c r="AF58" s="267"/>
+      <c r="AG58" s="267"/>
+      <c r="AH58" s="267"/>
+      <c r="AI58" s="267"/>
+      <c r="AJ58" s="267"/>
+      <c r="AK58" s="267"/>
+      <c r="AL58" s="267"/>
+      <c r="AM58" s="267"/>
+      <c r="AN58" s="267"/>
+      <c r="AO58" s="267"/>
+      <c r="AP58" s="267"/>
+      <c r="AQ58" s="267"/>
+      <c r="AR58" s="267"/>
+      <c r="AS58" s="267"/>
+      <c r="AT58" s="267"/>
+      <c r="AU58" s="267"/>
+      <c r="AV58" s="267"/>
+      <c r="AW58" s="267"/>
+      <c r="AX58" s="267"/>
+      <c r="AY58" s="267"/>
+      <c r="AZ58" s="267"/>
       <c r="BA58" s="114"/>
       <c r="BB58" s="17"/>
       <c r="BC58" s="17"/>
@@ -14961,58 +14961,58 @@
       <c r="CB58" s="107"/>
     </row>
     <row r="59" spans="1:80" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="268"/>
-      <c r="B59" s="316"/>
-      <c r="C59" s="267"/>
-      <c r="D59" s="267"/>
-      <c r="E59" s="267"/>
-      <c r="F59" s="267"/>
+      <c r="A59" s="308"/>
+      <c r="B59" s="302"/>
+      <c r="C59" s="281"/>
+      <c r="D59" s="281"/>
+      <c r="E59" s="281"/>
+      <c r="F59" s="281"/>
       <c r="G59" s="17"/>
       <c r="H59" s="17"/>
       <c r="I59" s="17"/>
-      <c r="J59" s="273"/>
-      <c r="K59" s="273"/>
-      <c r="L59" s="273"/>
-      <c r="M59" s="273"/>
-      <c r="N59" s="273"/>
-      <c r="O59" s="273"/>
-      <c r="P59" s="273"/>
-      <c r="Q59" s="273"/>
-      <c r="R59" s="273"/>
-      <c r="S59" s="273"/>
-      <c r="T59" s="273"/>
-      <c r="U59" s="273"/>
-      <c r="V59" s="273"/>
-      <c r="W59" s="273"/>
-      <c r="X59" s="273"/>
-      <c r="Y59" s="273"/>
-      <c r="Z59" s="273"/>
-      <c r="AA59" s="273"/>
-      <c r="AB59" s="273"/>
-      <c r="AC59" s="273"/>
-      <c r="AD59" s="273"/>
-      <c r="AE59" s="273"/>
-      <c r="AF59" s="273"/>
-      <c r="AG59" s="273"/>
-      <c r="AH59" s="273"/>
-      <c r="AI59" s="273"/>
-      <c r="AJ59" s="273"/>
-      <c r="AK59" s="273"/>
-      <c r="AL59" s="273"/>
-      <c r="AM59" s="273"/>
-      <c r="AN59" s="273"/>
-      <c r="AO59" s="273"/>
-      <c r="AP59" s="273"/>
-      <c r="AQ59" s="273"/>
-      <c r="AR59" s="273"/>
-      <c r="AS59" s="273"/>
-      <c r="AT59" s="273"/>
-      <c r="AU59" s="273"/>
-      <c r="AV59" s="273"/>
-      <c r="AW59" s="273"/>
-      <c r="AX59" s="273"/>
-      <c r="AY59" s="273"/>
-      <c r="AZ59" s="273"/>
+      <c r="J59" s="268"/>
+      <c r="K59" s="268"/>
+      <c r="L59" s="268"/>
+      <c r="M59" s="268"/>
+      <c r="N59" s="268"/>
+      <c r="O59" s="268"/>
+      <c r="P59" s="268"/>
+      <c r="Q59" s="268"/>
+      <c r="R59" s="268"/>
+      <c r="S59" s="268"/>
+      <c r="T59" s="268"/>
+      <c r="U59" s="268"/>
+      <c r="V59" s="268"/>
+      <c r="W59" s="268"/>
+      <c r="X59" s="268"/>
+      <c r="Y59" s="268"/>
+      <c r="Z59" s="268"/>
+      <c r="AA59" s="268"/>
+      <c r="AB59" s="268"/>
+      <c r="AC59" s="268"/>
+      <c r="AD59" s="268"/>
+      <c r="AE59" s="268"/>
+      <c r="AF59" s="268"/>
+      <c r="AG59" s="268"/>
+      <c r="AH59" s="268"/>
+      <c r="AI59" s="268"/>
+      <c r="AJ59" s="268"/>
+      <c r="AK59" s="268"/>
+      <c r="AL59" s="268"/>
+      <c r="AM59" s="268"/>
+      <c r="AN59" s="268"/>
+      <c r="AO59" s="268"/>
+      <c r="AP59" s="268"/>
+      <c r="AQ59" s="268"/>
+      <c r="AR59" s="268"/>
+      <c r="AS59" s="268"/>
+      <c r="AT59" s="268"/>
+      <c r="AU59" s="268"/>
+      <c r="AV59" s="268"/>
+      <c r="AW59" s="268"/>
+      <c r="AX59" s="268"/>
+      <c r="AY59" s="268"/>
+      <c r="AZ59" s="268"/>
       <c r="BA59" s="110"/>
       <c r="BB59" s="17"/>
       <c r="BC59" s="17"/>
@@ -15043,58 +15043,58 @@
       <c r="CB59" s="107"/>
     </row>
     <row r="60" spans="1:80" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="268"/>
-      <c r="B60" s="316"/>
-      <c r="C60" s="267"/>
-      <c r="D60" s="267"/>
-      <c r="E60" s="267"/>
-      <c r="F60" s="267"/>
+      <c r="A60" s="308"/>
+      <c r="B60" s="302"/>
+      <c r="C60" s="281"/>
+      <c r="D60" s="281"/>
+      <c r="E60" s="281"/>
+      <c r="F60" s="281"/>
       <c r="G60" s="17"/>
       <c r="H60" s="17"/>
       <c r="I60" s="17"/>
-      <c r="J60" s="275"/>
-      <c r="K60" s="275"/>
-      <c r="L60" s="275"/>
-      <c r="M60" s="275"/>
-      <c r="N60" s="275"/>
-      <c r="O60" s="275"/>
-      <c r="P60" s="275"/>
-      <c r="Q60" s="275"/>
-      <c r="R60" s="275"/>
-      <c r="S60" s="275"/>
-      <c r="T60" s="275"/>
-      <c r="U60" s="275"/>
-      <c r="V60" s="275"/>
-      <c r="W60" s="275"/>
-      <c r="X60" s="275"/>
-      <c r="Y60" s="275"/>
-      <c r="Z60" s="275"/>
-      <c r="AA60" s="275"/>
-      <c r="AB60" s="275"/>
-      <c r="AC60" s="275"/>
-      <c r="AD60" s="275"/>
-      <c r="AE60" s="275"/>
-      <c r="AF60" s="275"/>
-      <c r="AG60" s="275"/>
-      <c r="AH60" s="275"/>
-      <c r="AI60" s="275"/>
-      <c r="AJ60" s="275"/>
-      <c r="AK60" s="275"/>
-      <c r="AL60" s="275"/>
-      <c r="AM60" s="275"/>
-      <c r="AN60" s="275"/>
-      <c r="AO60" s="275"/>
-      <c r="AP60" s="275"/>
-      <c r="AQ60" s="275"/>
-      <c r="AR60" s="275"/>
-      <c r="AS60" s="275"/>
-      <c r="AT60" s="275"/>
-      <c r="AU60" s="275"/>
-      <c r="AV60" s="275"/>
-      <c r="AW60" s="275"/>
-      <c r="AX60" s="275"/>
-      <c r="AY60" s="275"/>
-      <c r="AZ60" s="275"/>
+      <c r="J60" s="269"/>
+      <c r="K60" s="269"/>
+      <c r="L60" s="269"/>
+      <c r="M60" s="269"/>
+      <c r="N60" s="269"/>
+      <c r="O60" s="269"/>
+      <c r="P60" s="269"/>
+      <c r="Q60" s="269"/>
+      <c r="R60" s="269"/>
+      <c r="S60" s="269"/>
+      <c r="T60" s="269"/>
+      <c r="U60" s="269"/>
+      <c r="V60" s="269"/>
+      <c r="W60" s="269"/>
+      <c r="X60" s="269"/>
+      <c r="Y60" s="269"/>
+      <c r="Z60" s="269"/>
+      <c r="AA60" s="269"/>
+      <c r="AB60" s="269"/>
+      <c r="AC60" s="269"/>
+      <c r="AD60" s="269"/>
+      <c r="AE60" s="269"/>
+      <c r="AF60" s="269"/>
+      <c r="AG60" s="269"/>
+      <c r="AH60" s="269"/>
+      <c r="AI60" s="269"/>
+      <c r="AJ60" s="269"/>
+      <c r="AK60" s="269"/>
+      <c r="AL60" s="269"/>
+      <c r="AM60" s="269"/>
+      <c r="AN60" s="269"/>
+      <c r="AO60" s="269"/>
+      <c r="AP60" s="269"/>
+      <c r="AQ60" s="269"/>
+      <c r="AR60" s="269"/>
+      <c r="AS60" s="269"/>
+      <c r="AT60" s="269"/>
+      <c r="AU60" s="269"/>
+      <c r="AV60" s="269"/>
+      <c r="AW60" s="269"/>
+      <c r="AX60" s="269"/>
+      <c r="AY60" s="269"/>
+      <c r="AZ60" s="269"/>
       <c r="BA60" s="111"/>
       <c r="BB60" s="17"/>
       <c r="BC60" s="17"/>
@@ -15125,58 +15125,58 @@
       <c r="CB60" s="107"/>
     </row>
     <row r="61" spans="1:80" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="268"/>
-      <c r="B61" s="316"/>
-      <c r="C61" s="267"/>
-      <c r="D61" s="267"/>
-      <c r="E61" s="267"/>
-      <c r="F61" s="267"/>
+      <c r="A61" s="308"/>
+      <c r="B61" s="302"/>
+      <c r="C61" s="281"/>
+      <c r="D61" s="281"/>
+      <c r="E61" s="281"/>
+      <c r="F61" s="281"/>
       <c r="G61" s="17"/>
       <c r="H61" s="17"/>
       <c r="I61" s="17"/>
-      <c r="J61" s="275"/>
-      <c r="K61" s="275"/>
-      <c r="L61" s="275"/>
-      <c r="M61" s="275"/>
-      <c r="N61" s="275"/>
-      <c r="O61" s="275"/>
-      <c r="P61" s="275"/>
-      <c r="Q61" s="275"/>
-      <c r="R61" s="275"/>
-      <c r="S61" s="275"/>
-      <c r="T61" s="275"/>
-      <c r="U61" s="275"/>
-      <c r="V61" s="275"/>
-      <c r="W61" s="275"/>
-      <c r="X61" s="275"/>
-      <c r="Y61" s="275"/>
-      <c r="Z61" s="275"/>
-      <c r="AA61" s="275"/>
-      <c r="AB61" s="275"/>
-      <c r="AC61" s="275"/>
-      <c r="AD61" s="275"/>
-      <c r="AE61" s="275"/>
-      <c r="AF61" s="275"/>
-      <c r="AG61" s="275"/>
-      <c r="AH61" s="275"/>
-      <c r="AI61" s="275"/>
-      <c r="AJ61" s="275"/>
-      <c r="AK61" s="275"/>
-      <c r="AL61" s="275"/>
-      <c r="AM61" s="275"/>
-      <c r="AN61" s="275"/>
-      <c r="AO61" s="275"/>
-      <c r="AP61" s="275"/>
-      <c r="AQ61" s="275"/>
-      <c r="AR61" s="275"/>
-      <c r="AS61" s="275"/>
-      <c r="AT61" s="275"/>
-      <c r="AU61" s="275"/>
-      <c r="AV61" s="275"/>
-      <c r="AW61" s="275"/>
-      <c r="AX61" s="275"/>
-      <c r="AY61" s="275"/>
-      <c r="AZ61" s="275"/>
+      <c r="J61" s="269"/>
+      <c r="K61" s="269"/>
+      <c r="L61" s="269"/>
+      <c r="M61" s="269"/>
+      <c r="N61" s="269"/>
+      <c r="O61" s="269"/>
+      <c r="P61" s="269"/>
+      <c r="Q61" s="269"/>
+      <c r="R61" s="269"/>
+      <c r="S61" s="269"/>
+      <c r="T61" s="269"/>
+      <c r="U61" s="269"/>
+      <c r="V61" s="269"/>
+      <c r="W61" s="269"/>
+      <c r="X61" s="269"/>
+      <c r="Y61" s="269"/>
+      <c r="Z61" s="269"/>
+      <c r="AA61" s="269"/>
+      <c r="AB61" s="269"/>
+      <c r="AC61" s="269"/>
+      <c r="AD61" s="269"/>
+      <c r="AE61" s="269"/>
+      <c r="AF61" s="269"/>
+      <c r="AG61" s="269"/>
+      <c r="AH61" s="269"/>
+      <c r="AI61" s="269"/>
+      <c r="AJ61" s="269"/>
+      <c r="AK61" s="269"/>
+      <c r="AL61" s="269"/>
+      <c r="AM61" s="269"/>
+      <c r="AN61" s="269"/>
+      <c r="AO61" s="269"/>
+      <c r="AP61" s="269"/>
+      <c r="AQ61" s="269"/>
+      <c r="AR61" s="269"/>
+      <c r="AS61" s="269"/>
+      <c r="AT61" s="269"/>
+      <c r="AU61" s="269"/>
+      <c r="AV61" s="269"/>
+      <c r="AW61" s="269"/>
+      <c r="AX61" s="269"/>
+      <c r="AY61" s="269"/>
+      <c r="AZ61" s="269"/>
       <c r="BA61" s="112"/>
       <c r="BB61" s="17"/>
       <c r="BC61" s="17"/>
@@ -15207,58 +15207,58 @@
       <c r="CB61" s="107"/>
     </row>
     <row r="62" spans="1:80" ht="35.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="268"/>
-      <c r="B62" s="317"/>
-      <c r="C62" s="318"/>
-      <c r="D62" s="318"/>
-      <c r="E62" s="318"/>
-      <c r="F62" s="318"/>
+      <c r="A62" s="308"/>
+      <c r="B62" s="303"/>
+      <c r="C62" s="304"/>
+      <c r="D62" s="304"/>
+      <c r="E62" s="304"/>
+      <c r="F62" s="304"/>
       <c r="G62" s="37"/>
       <c r="H62" s="37"/>
       <c r="I62" s="37"/>
-      <c r="J62" s="276"/>
-      <c r="K62" s="276"/>
-      <c r="L62" s="276"/>
-      <c r="M62" s="276"/>
-      <c r="N62" s="276"/>
-      <c r="O62" s="276"/>
-      <c r="P62" s="276"/>
-      <c r="Q62" s="276"/>
-      <c r="R62" s="276"/>
-      <c r="S62" s="276"/>
-      <c r="T62" s="276"/>
-      <c r="U62" s="276"/>
-      <c r="V62" s="276"/>
-      <c r="W62" s="276"/>
-      <c r="X62" s="276"/>
-      <c r="Y62" s="276"/>
-      <c r="Z62" s="276"/>
-      <c r="AA62" s="276"/>
-      <c r="AB62" s="276"/>
-      <c r="AC62" s="276"/>
-      <c r="AD62" s="276"/>
-      <c r="AE62" s="276"/>
-      <c r="AF62" s="276"/>
-      <c r="AG62" s="276"/>
-      <c r="AH62" s="276"/>
-      <c r="AI62" s="276"/>
-      <c r="AJ62" s="276"/>
-      <c r="AK62" s="276"/>
-      <c r="AL62" s="276"/>
-      <c r="AM62" s="276"/>
-      <c r="AN62" s="276"/>
-      <c r="AO62" s="276"/>
-      <c r="AP62" s="276"/>
-      <c r="AQ62" s="276"/>
-      <c r="AR62" s="276"/>
-      <c r="AS62" s="276"/>
-      <c r="AT62" s="276"/>
-      <c r="AU62" s="276"/>
-      <c r="AV62" s="276"/>
-      <c r="AW62" s="276"/>
-      <c r="AX62" s="276"/>
-      <c r="AY62" s="276"/>
-      <c r="AZ62" s="276"/>
+      <c r="J62" s="282"/>
+      <c r="K62" s="282"/>
+      <c r="L62" s="282"/>
+      <c r="M62" s="282"/>
+      <c r="N62" s="282"/>
+      <c r="O62" s="282"/>
+      <c r="P62" s="282"/>
+      <c r="Q62" s="282"/>
+      <c r="R62" s="282"/>
+      <c r="S62" s="282"/>
+      <c r="T62" s="282"/>
+      <c r="U62" s="282"/>
+      <c r="V62" s="282"/>
+      <c r="W62" s="282"/>
+      <c r="X62" s="282"/>
+      <c r="Y62" s="282"/>
+      <c r="Z62" s="282"/>
+      <c r="AA62" s="282"/>
+      <c r="AB62" s="282"/>
+      <c r="AC62" s="282"/>
+      <c r="AD62" s="282"/>
+      <c r="AE62" s="282"/>
+      <c r="AF62" s="282"/>
+      <c r="AG62" s="282"/>
+      <c r="AH62" s="282"/>
+      <c r="AI62" s="282"/>
+      <c r="AJ62" s="282"/>
+      <c r="AK62" s="282"/>
+      <c r="AL62" s="282"/>
+      <c r="AM62" s="282"/>
+      <c r="AN62" s="282"/>
+      <c r="AO62" s="282"/>
+      <c r="AP62" s="282"/>
+      <c r="AQ62" s="282"/>
+      <c r="AR62" s="282"/>
+      <c r="AS62" s="282"/>
+      <c r="AT62" s="282"/>
+      <c r="AU62" s="282"/>
+      <c r="AV62" s="282"/>
+      <c r="AW62" s="282"/>
+      <c r="AX62" s="282"/>
+      <c r="AY62" s="282"/>
+      <c r="AZ62" s="282"/>
       <c r="BA62" s="113"/>
       <c r="BB62" s="37"/>
       <c r="BC62" s="37"/>
@@ -15289,7 +15289,7 @@
       <c r="CB62" s="107"/>
     </row>
     <row r="63" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="268"/>
+      <c r="A63" s="308"/>
       <c r="B63" s="120">
         <v>45</v>
       </c>
@@ -15300,14 +15300,14 @@
         <v>-24.546168099999999</v>
       </c>
       <c r="E63" s="69" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="F63" s="65"/>
       <c r="G63" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H63" s="69" t="s">
-        <v>900</v>
+        <v>850</v>
       </c>
       <c r="I63" s="64" t="s">
         <v>560</v>
@@ -15396,7 +15396,7 @@
       <c r="BV63" s="4"/>
       <c r="BW63" s="4"/>
       <c r="BX63" s="4"/>
-      <c r="BY63" s="296"/>
+      <c r="BY63" s="265"/>
       <c r="BZ63" s="125">
         <f t="shared" ref="BZ63:BZ106" si="7">SUMIF($L63:$BX63, "x", $L$12:$BX$12)</f>
         <v>150</v>
@@ -15405,7 +15405,7 @@
       <c r="CB63" s="107"/>
     </row>
     <row r="64" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="268"/>
+      <c r="A64" s="308"/>
       <c r="B64" s="120">
         <v>46</v>
       </c>
@@ -15416,14 +15416,14 @@
         <v>-24.54386088</v>
       </c>
       <c r="E64" s="69" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="F64" s="65"/>
       <c r="G64" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H64" s="69" t="s">
-        <v>901</v>
+        <v>851</v>
       </c>
       <c r="I64" s="64" t="s">
         <v>560</v>
@@ -15512,7 +15512,7 @@
       <c r="BV64" s="4"/>
       <c r="BW64" s="4"/>
       <c r="BX64" s="4"/>
-      <c r="BY64" s="296"/>
+      <c r="BY64" s="265"/>
       <c r="BZ64" s="123">
         <f t="shared" si="7"/>
         <v>150</v>
@@ -15521,7 +15521,7 @@
       <c r="CB64" s="107"/>
     </row>
     <row r="65" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="268"/>
+      <c r="A65" s="308"/>
       <c r="B65" s="120">
         <v>47</v>
       </c>
@@ -15532,14 +15532,14 @@
         <v>-24.53844926</v>
       </c>
       <c r="E65" s="69" t="s">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="F65" s="65"/>
       <c r="G65" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H65" s="69" t="s">
-        <v>902</v>
+        <v>852</v>
       </c>
       <c r="I65" s="64" t="s">
         <v>560</v>
@@ -15628,7 +15628,7 @@
       <c r="BV65" s="4"/>
       <c r="BW65" s="4"/>
       <c r="BX65" s="4"/>
-      <c r="BY65" s="296"/>
+      <c r="BY65" s="265"/>
       <c r="BZ65" s="123">
         <f t="shared" si="7"/>
         <v>150</v>
@@ -15637,7 +15637,7 @@
       <c r="CB65" s="107"/>
     </row>
     <row r="66" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="268"/>
+      <c r="A66" s="308"/>
       <c r="B66" s="120">
         <v>48</v>
       </c>
@@ -15648,14 +15648,14 @@
         <v>-24.520826830000001</v>
       </c>
       <c r="E66" s="69" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="F66" s="65"/>
       <c r="G66" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H66" s="69" t="s">
-        <v>903</v>
+        <v>853</v>
       </c>
       <c r="I66" s="64" t="s">
         <v>560</v>
@@ -15744,7 +15744,7 @@
       <c r="BV66" s="4"/>
       <c r="BW66" s="4"/>
       <c r="BX66" s="4"/>
-      <c r="BY66" s="296"/>
+      <c r="BY66" s="265"/>
       <c r="BZ66" s="123">
         <f t="shared" si="7"/>
         <v>150</v>
@@ -15753,7 +15753,7 @@
       <c r="CB66" s="107"/>
     </row>
     <row r="67" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="268"/>
+      <c r="A67" s="308"/>
       <c r="B67" s="120">
         <v>49</v>
       </c>
@@ -15764,14 +15764,14 @@
         <v>-24.508967760000001</v>
       </c>
       <c r="E67" s="69" t="s">
-        <v>898</v>
+        <v>904</v>
       </c>
       <c r="F67" s="65"/>
       <c r="G67" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H67" s="69" t="s">
-        <v>904</v>
+        <v>854</v>
       </c>
       <c r="I67" s="64" t="s">
         <v>560</v>
@@ -15860,7 +15860,7 @@
       <c r="BV67" s="4"/>
       <c r="BW67" s="4"/>
       <c r="BX67" s="4"/>
-      <c r="BY67" s="296"/>
+      <c r="BY67" s="265"/>
       <c r="BZ67" s="123">
         <f t="shared" si="7"/>
         <v>150</v>
@@ -15869,7 +15869,7 @@
       <c r="CB67" s="107"/>
     </row>
     <row r="68" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="268"/>
+      <c r="A68" s="308"/>
       <c r="B68" s="120">
         <v>50</v>
       </c>
@@ -15880,14 +15880,14 @@
         <v>-24.506801800000002</v>
       </c>
       <c r="E68" s="69" t="s">
-        <v>899</v>
+        <v>905</v>
       </c>
       <c r="F68" s="65"/>
       <c r="G68" s="63" t="s">
-        <v>849</v>
+        <v>805</v>
       </c>
       <c r="H68" s="69" t="s">
-        <v>905</v>
+        <v>855</v>
       </c>
       <c r="I68" s="64" t="s">
         <v>560</v>
@@ -15976,7 +15976,7 @@
       <c r="BV68" s="4"/>
       <c r="BW68" s="4"/>
       <c r="BX68" s="4"/>
-      <c r="BY68" s="296"/>
+      <c r="BY68" s="265"/>
       <c r="BZ68" s="123">
         <f t="shared" si="7"/>
         <v>150</v>
@@ -15985,7 +15985,7 @@
       <c r="CB68" s="107"/>
     </row>
     <row r="69" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="268"/>
+      <c r="A69" s="308"/>
       <c r="B69" s="120">
         <v>51</v>
       </c>
@@ -16072,7 +16072,7 @@
       <c r="BV69" s="4"/>
       <c r="BW69" s="4"/>
       <c r="BX69" s="4"/>
-      <c r="BY69" s="296"/>
+      <c r="BY69" s="265"/>
       <c r="BZ69" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -16081,7 +16081,7 @@
       <c r="CB69" s="107"/>
     </row>
     <row r="70" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="268"/>
+      <c r="A70" s="308"/>
       <c r="B70" s="120">
         <v>52</v>
       </c>
@@ -16168,7 +16168,7 @@
       <c r="BV70" s="4"/>
       <c r="BW70" s="4"/>
       <c r="BX70" s="4"/>
-      <c r="BY70" s="296"/>
+      <c r="BY70" s="265"/>
       <c r="BZ70" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -16177,7 +16177,7 @@
       <c r="CB70" s="107"/>
     </row>
     <row r="71" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="268"/>
+      <c r="A71" s="308"/>
       <c r="B71" s="120">
         <v>53</v>
       </c>
@@ -16264,7 +16264,7 @@
       <c r="BV71" s="4"/>
       <c r="BW71" s="4"/>
       <c r="BX71" s="4"/>
-      <c r="BY71" s="296"/>
+      <c r="BY71" s="265"/>
       <c r="BZ71" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -16273,7 +16273,7 @@
       <c r="CB71" s="107"/>
     </row>
     <row r="72" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="268"/>
+      <c r="A72" s="308"/>
       <c r="B72" s="120">
         <v>54</v>
       </c>
@@ -16360,7 +16360,7 @@
       <c r="BV72" s="4"/>
       <c r="BW72" s="4"/>
       <c r="BX72" s="4"/>
-      <c r="BY72" s="296"/>
+      <c r="BY72" s="265"/>
       <c r="BZ72" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -16369,7 +16369,7 @@
       <c r="CB72" s="107"/>
     </row>
     <row r="73" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="268"/>
+      <c r="A73" s="308"/>
       <c r="B73" s="120">
         <v>55</v>
       </c>
@@ -16456,7 +16456,7 @@
       <c r="BV73" s="4"/>
       <c r="BW73" s="4"/>
       <c r="BX73" s="4"/>
-      <c r="BY73" s="296"/>
+      <c r="BY73" s="265"/>
       <c r="BZ73" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -16465,7 +16465,7 @@
       <c r="CB73" s="107"/>
     </row>
     <row r="74" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="268"/>
+      <c r="A74" s="308"/>
       <c r="B74" s="120">
         <v>56</v>
       </c>
@@ -16552,7 +16552,7 @@
       <c r="BV74" s="4"/>
       <c r="BW74" s="4"/>
       <c r="BX74" s="4"/>
-      <c r="BY74" s="296"/>
+      <c r="BY74" s="265"/>
       <c r="BZ74" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -16561,7 +16561,7 @@
       <c r="CB74" s="107"/>
     </row>
     <row r="75" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="268"/>
+      <c r="A75" s="308"/>
       <c r="B75" s="120">
         <v>57</v>
       </c>
@@ -16648,7 +16648,7 @@
       <c r="BV75" s="4"/>
       <c r="BW75" s="4"/>
       <c r="BX75" s="4"/>
-      <c r="BY75" s="296"/>
+      <c r="BY75" s="265"/>
       <c r="BZ75" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -16657,7 +16657,7 @@
       <c r="CB75" s="107"/>
     </row>
     <row r="76" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="268"/>
+      <c r="A76" s="308"/>
       <c r="B76" s="120">
         <v>58</v>
       </c>
@@ -16744,7 +16744,7 @@
       <c r="BV76" s="4"/>
       <c r="BW76" s="4"/>
       <c r="BX76" s="4"/>
-      <c r="BY76" s="296"/>
+      <c r="BY76" s="265"/>
       <c r="BZ76" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -16753,7 +16753,7 @@
       <c r="CB76" s="107"/>
     </row>
     <row r="77" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="268"/>
+      <c r="A77" s="308"/>
       <c r="B77" s="120">
         <v>59</v>
       </c>
@@ -16840,7 +16840,7 @@
       <c r="BV77" s="4"/>
       <c r="BW77" s="4"/>
       <c r="BX77" s="4"/>
-      <c r="BY77" s="296"/>
+      <c r="BY77" s="265"/>
       <c r="BZ77" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -16849,7 +16849,7 @@
       <c r="CB77" s="107"/>
     </row>
     <row r="78" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="268"/>
+      <c r="A78" s="308"/>
       <c r="B78" s="120">
         <v>60</v>
       </c>
@@ -16936,7 +16936,7 @@
       <c r="BV78" s="4"/>
       <c r="BW78" s="4"/>
       <c r="BX78" s="4"/>
-      <c r="BY78" s="296"/>
+      <c r="BY78" s="265"/>
       <c r="BZ78" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -16945,7 +16945,7 @@
       <c r="CB78" s="107"/>
     </row>
     <row r="79" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="268"/>
+      <c r="A79" s="308"/>
       <c r="B79" s="120">
         <v>61</v>
       </c>
@@ -17032,7 +17032,7 @@
       <c r="BV79" s="4"/>
       <c r="BW79" s="4"/>
       <c r="BX79" s="4"/>
-      <c r="BY79" s="296"/>
+      <c r="BY79" s="265"/>
       <c r="BZ79" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -17041,7 +17041,7 @@
       <c r="CB79" s="107"/>
     </row>
     <row r="80" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="268"/>
+      <c r="A80" s="308"/>
       <c r="B80" s="120">
         <v>62</v>
       </c>
@@ -17128,7 +17128,7 @@
       <c r="BV80" s="4"/>
       <c r="BW80" s="4"/>
       <c r="BX80" s="4"/>
-      <c r="BY80" s="296"/>
+      <c r="BY80" s="265"/>
       <c r="BZ80" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -17137,7 +17137,7 @@
       <c r="CB80" s="107"/>
     </row>
     <row r="81" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="268"/>
+      <c r="A81" s="308"/>
       <c r="B81" s="120">
         <v>63</v>
       </c>
@@ -17224,7 +17224,7 @@
       <c r="BV81" s="4"/>
       <c r="BW81" s="4"/>
       <c r="BX81" s="4"/>
-      <c r="BY81" s="296"/>
+      <c r="BY81" s="265"/>
       <c r="BZ81" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -17233,7 +17233,7 @@
       <c r="CB81" s="107"/>
     </row>
     <row r="82" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="268"/>
+      <c r="A82" s="308"/>
       <c r="B82" s="120">
         <v>64</v>
       </c>
@@ -17320,7 +17320,7 @@
       <c r="BV82" s="4"/>
       <c r="BW82" s="4"/>
       <c r="BX82" s="4"/>
-      <c r="BY82" s="296"/>
+      <c r="BY82" s="265"/>
       <c r="BZ82" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -17329,7 +17329,7 @@
       <c r="CB82" s="107"/>
     </row>
     <row r="83" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="268"/>
+      <c r="A83" s="308"/>
       <c r="B83" s="120">
         <v>65</v>
       </c>
@@ -17416,7 +17416,7 @@
       <c r="BV83" s="4"/>
       <c r="BW83" s="4"/>
       <c r="BX83" s="4"/>
-      <c r="BY83" s="296"/>
+      <c r="BY83" s="265"/>
       <c r="BZ83" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -17425,7 +17425,7 @@
       <c r="CB83" s="107"/>
     </row>
     <row r="84" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="268"/>
+      <c r="A84" s="308"/>
       <c r="B84" s="120">
         <v>66</v>
       </c>
@@ -17512,7 +17512,7 @@
       <c r="BV84" s="4"/>
       <c r="BW84" s="4"/>
       <c r="BX84" s="4"/>
-      <c r="BY84" s="296"/>
+      <c r="BY84" s="265"/>
       <c r="BZ84" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -17521,7 +17521,7 @@
       <c r="CB84" s="107"/>
     </row>
     <row r="85" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="268"/>
+      <c r="A85" s="308"/>
       <c r="B85" s="120">
         <v>67</v>
       </c>
@@ -17608,7 +17608,7 @@
       <c r="BV85" s="4"/>
       <c r="BW85" s="4"/>
       <c r="BX85" s="4"/>
-      <c r="BY85" s="296"/>
+      <c r="BY85" s="265"/>
       <c r="BZ85" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -17617,7 +17617,7 @@
       <c r="CB85" s="107"/>
     </row>
     <row r="86" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="268"/>
+      <c r="A86" s="308"/>
       <c r="B86" s="120">
         <v>68</v>
       </c>
@@ -17704,7 +17704,7 @@
       <c r="BV86" s="4"/>
       <c r="BW86" s="4"/>
       <c r="BX86" s="4"/>
-      <c r="BY86" s="296"/>
+      <c r="BY86" s="265"/>
       <c r="BZ86" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -17713,7 +17713,7 @@
       <c r="CB86" s="107"/>
     </row>
     <row r="87" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="268"/>
+      <c r="A87" s="308"/>
       <c r="B87" s="120">
         <v>69</v>
       </c>
@@ -17800,7 +17800,7 @@
       <c r="BV87" s="4"/>
       <c r="BW87" s="4"/>
       <c r="BX87" s="4"/>
-      <c r="BY87" s="296"/>
+      <c r="BY87" s="265"/>
       <c r="BZ87" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -17809,7 +17809,7 @@
       <c r="CB87" s="107"/>
     </row>
     <row r="88" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="268"/>
+      <c r="A88" s="308"/>
       <c r="B88" s="120">
         <v>70</v>
       </c>
@@ -17896,7 +17896,7 @@
       <c r="BV88" s="4"/>
       <c r="BW88" s="4"/>
       <c r="BX88" s="4"/>
-      <c r="BY88" s="296"/>
+      <c r="BY88" s="265"/>
       <c r="BZ88" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -17905,7 +17905,7 @@
       <c r="CB88" s="117"/>
     </row>
     <row r="89" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="268"/>
+      <c r="A89" s="308"/>
       <c r="B89" s="120">
         <v>71</v>
       </c>
@@ -17992,7 +17992,7 @@
       <c r="BV89" s="4"/>
       <c r="BW89" s="4"/>
       <c r="BX89" s="4"/>
-      <c r="BY89" s="296"/>
+      <c r="BY89" s="265"/>
       <c r="BZ89" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -18001,7 +18001,7 @@
       <c r="CB89" s="117"/>
     </row>
     <row r="90" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="268"/>
+      <c r="A90" s="308"/>
       <c r="B90" s="120">
         <v>72</v>
       </c>
@@ -18088,7 +18088,7 @@
       <c r="BV90" s="4"/>
       <c r="BW90" s="4"/>
       <c r="BX90" s="4"/>
-      <c r="BY90" s="296"/>
+      <c r="BY90" s="265"/>
       <c r="BZ90" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -18097,7 +18097,7 @@
       <c r="CB90" s="117"/>
     </row>
     <row r="91" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="268"/>
+      <c r="A91" s="308"/>
       <c r="B91" s="120">
         <v>73</v>
       </c>
@@ -18184,7 +18184,7 @@
       <c r="BV91" s="4"/>
       <c r="BW91" s="4"/>
       <c r="BX91" s="4"/>
-      <c r="BY91" s="296"/>
+      <c r="BY91" s="265"/>
       <c r="BZ91" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -18193,7 +18193,7 @@
       <c r="CB91" s="117"/>
     </row>
     <row r="92" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="268"/>
+      <c r="A92" s="308"/>
       <c r="B92" s="120">
         <v>74</v>
       </c>
@@ -18280,7 +18280,7 @@
       <c r="BV92" s="4"/>
       <c r="BW92" s="4"/>
       <c r="BX92" s="4"/>
-      <c r="BY92" s="296"/>
+      <c r="BY92" s="265"/>
       <c r="BZ92" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -18289,7 +18289,7 @@
       <c r="CB92" s="117"/>
     </row>
     <row r="93" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="268"/>
+      <c r="A93" s="308"/>
       <c r="B93" s="120">
         <v>75</v>
       </c>
@@ -18376,7 +18376,7 @@
       <c r="BV93" s="4"/>
       <c r="BW93" s="4"/>
       <c r="BX93" s="4"/>
-      <c r="BY93" s="296"/>
+      <c r="BY93" s="265"/>
       <c r="BZ93" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -18385,7 +18385,7 @@
       <c r="CB93" s="117"/>
     </row>
     <row r="94" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="268"/>
+      <c r="A94" s="308"/>
       <c r="B94" s="120">
         <v>76</v>
       </c>
@@ -18472,7 +18472,7 @@
       <c r="BV94" s="4"/>
       <c r="BW94" s="4"/>
       <c r="BX94" s="4"/>
-      <c r="BY94" s="296"/>
+      <c r="BY94" s="265"/>
       <c r="BZ94" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -18481,7 +18481,7 @@
       <c r="CB94" s="117"/>
     </row>
     <row r="95" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="268"/>
+      <c r="A95" s="308"/>
       <c r="B95" s="120">
         <v>77</v>
       </c>
@@ -18568,7 +18568,7 @@
       <c r="BV95" s="4"/>
       <c r="BW95" s="4"/>
       <c r="BX95" s="4"/>
-      <c r="BY95" s="296"/>
+      <c r="BY95" s="265"/>
       <c r="BZ95" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -18577,7 +18577,7 @@
       <c r="CB95" s="117"/>
     </row>
     <row r="96" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="268"/>
+      <c r="A96" s="308"/>
       <c r="B96" s="120">
         <v>78</v>
       </c>
@@ -18664,7 +18664,7 @@
       <c r="BV96" s="4"/>
       <c r="BW96" s="4"/>
       <c r="BX96" s="4"/>
-      <c r="BY96" s="296"/>
+      <c r="BY96" s="265"/>
       <c r="BZ96" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -18673,7 +18673,7 @@
       <c r="CB96" s="117"/>
     </row>
     <row r="97" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="268"/>
+      <c r="A97" s="308"/>
       <c r="B97" s="120">
         <v>79</v>
       </c>
@@ -18760,7 +18760,7 @@
       <c r="BV97" s="4"/>
       <c r="BW97" s="4"/>
       <c r="BX97" s="4"/>
-      <c r="BY97" s="296"/>
+      <c r="BY97" s="265"/>
       <c r="BZ97" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -18769,7 +18769,7 @@
       <c r="CB97" s="117"/>
     </row>
     <row r="98" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="268"/>
+      <c r="A98" s="308"/>
       <c r="B98" s="120">
         <v>80</v>
       </c>
@@ -18856,7 +18856,7 @@
       <c r="BV98" s="4"/>
       <c r="BW98" s="4"/>
       <c r="BX98" s="4"/>
-      <c r="BY98" s="296"/>
+      <c r="BY98" s="265"/>
       <c r="BZ98" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -18865,7 +18865,7 @@
       <c r="CB98" s="117"/>
     </row>
     <row r="99" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="268"/>
+      <c r="A99" s="308"/>
       <c r="B99" s="120">
         <v>81</v>
       </c>
@@ -18952,7 +18952,7 @@
       <c r="BV99" s="4"/>
       <c r="BW99" s="4"/>
       <c r="BX99" s="4"/>
-      <c r="BY99" s="296"/>
+      <c r="BY99" s="265"/>
       <c r="BZ99" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -18961,7 +18961,7 @@
       <c r="CB99" s="117"/>
     </row>
     <row r="100" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="268"/>
+      <c r="A100" s="308"/>
       <c r="B100" s="120">
         <v>82</v>
       </c>
@@ -19048,7 +19048,7 @@
       <c r="BV100" s="4"/>
       <c r="BW100" s="4"/>
       <c r="BX100" s="4"/>
-      <c r="BY100" s="296"/>
+      <c r="BY100" s="265"/>
       <c r="BZ100" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -19057,7 +19057,7 @@
       <c r="CB100" s="117"/>
     </row>
     <row r="101" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="268"/>
+      <c r="A101" s="308"/>
       <c r="B101" s="120">
         <v>83</v>
       </c>
@@ -19144,7 +19144,7 @@
       <c r="BV101" s="4"/>
       <c r="BW101" s="4"/>
       <c r="BX101" s="4"/>
-      <c r="BY101" s="296"/>
+      <c r="BY101" s="265"/>
       <c r="BZ101" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -19153,7 +19153,7 @@
       <c r="CB101" s="117"/>
     </row>
     <row r="102" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="268"/>
+      <c r="A102" s="308"/>
       <c r="B102" s="120">
         <v>84</v>
       </c>
@@ -19240,7 +19240,7 @@
       <c r="BV102" s="4"/>
       <c r="BW102" s="4"/>
       <c r="BX102" s="4"/>
-      <c r="BY102" s="296"/>
+      <c r="BY102" s="265"/>
       <c r="BZ102" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -19249,7 +19249,7 @@
       <c r="CB102" s="117"/>
     </row>
     <row r="103" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="268"/>
+      <c r="A103" s="308"/>
       <c r="B103" s="120">
         <v>85</v>
       </c>
@@ -19336,7 +19336,7 @@
       <c r="BV103" s="4"/>
       <c r="BW103" s="4"/>
       <c r="BX103" s="4"/>
-      <c r="BY103" s="296"/>
+      <c r="BY103" s="265"/>
       <c r="BZ103" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -19345,7 +19345,7 @@
       <c r="CB103" s="117"/>
     </row>
     <row r="104" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="268"/>
+      <c r="A104" s="308"/>
       <c r="B104" s="120">
         <v>86</v>
       </c>
@@ -19432,7 +19432,7 @@
       <c r="BV104" s="4"/>
       <c r="BW104" s="4"/>
       <c r="BX104" s="4"/>
-      <c r="BY104" s="296"/>
+      <c r="BY104" s="265"/>
       <c r="BZ104" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -19441,7 +19441,7 @@
       <c r="CB104" s="117"/>
     </row>
     <row r="105" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="268"/>
+      <c r="A105" s="308"/>
       <c r="B105" s="120">
         <v>87</v>
       </c>
@@ -19528,7 +19528,7 @@
       <c r="BV105" s="4"/>
       <c r="BW105" s="4"/>
       <c r="BX105" s="4"/>
-      <c r="BY105" s="296"/>
+      <c r="BY105" s="265"/>
       <c r="BZ105" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -19537,7 +19537,7 @@
       <c r="CB105" s="117"/>
     </row>
     <row r="106" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="268"/>
+      <c r="A106" s="308"/>
       <c r="B106" s="121">
         <v>88</v>
       </c>
@@ -19624,7 +19624,7 @@
       <c r="BV106" s="4"/>
       <c r="BW106" s="4"/>
       <c r="BX106" s="4"/>
-      <c r="BY106" s="297"/>
+      <c r="BY106" s="283"/>
       <c r="BZ106" s="123">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -19633,19 +19633,19 @@
       <c r="CB106" s="117"/>
     </row>
     <row r="107" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="268"/>
-      <c r="B107" s="298" t="s">
+      <c r="A107" s="308"/>
+      <c r="B107" s="284" t="s">
         <v>537</v>
       </c>
-      <c r="C107" s="299"/>
-      <c r="D107" s="299"/>
-      <c r="E107" s="299"/>
-      <c r="F107" s="299"/>
-      <c r="G107" s="299"/>
-      <c r="H107" s="299"/>
-      <c r="I107" s="299"/>
-      <c r="J107" s="299"/>
-      <c r="K107" s="300"/>
+      <c r="C107" s="285"/>
+      <c r="D107" s="285"/>
+      <c r="E107" s="285"/>
+      <c r="F107" s="285"/>
+      <c r="G107" s="285"/>
+      <c r="H107" s="285"/>
+      <c r="I107" s="285"/>
+      <c r="J107" s="285"/>
+      <c r="K107" s="286"/>
       <c r="L107" s="76">
         <f>COUNTA(L13:L106)</f>
         <v>0</v>
@@ -19906,25 +19906,25 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="BY107" s="301"/>
-      <c r="BZ107" s="302"/>
-      <c r="CA107" s="305"/>
+      <c r="BY107" s="287"/>
+      <c r="BZ107" s="288"/>
+      <c r="CA107" s="291"/>
       <c r="CB107" s="117"/>
     </row>
     <row r="108" spans="1:80" ht="90" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="268"/>
-      <c r="B108" s="298" t="s">
+      <c r="A108" s="308"/>
+      <c r="B108" s="284" t="s">
         <v>24</v>
       </c>
-      <c r="C108" s="299"/>
-      <c r="D108" s="299"/>
-      <c r="E108" s="299"/>
-      <c r="F108" s="299"/>
-      <c r="G108" s="299"/>
-      <c r="H108" s="299"/>
-      <c r="I108" s="299"/>
-      <c r="J108" s="299"/>
-      <c r="K108" s="300"/>
+      <c r="C108" s="285"/>
+      <c r="D108" s="285"/>
+      <c r="E108" s="285"/>
+      <c r="F108" s="285"/>
+      <c r="G108" s="285"/>
+      <c r="H108" s="285"/>
+      <c r="I108" s="285"/>
+      <c r="J108" s="285"/>
+      <c r="K108" s="286"/>
       <c r="L108" s="77">
         <f>L10*L107</f>
         <v>0</v>
@@ -20185,278 +20185,286 @@
         <f t="shared" si="36"/>
         <v>0</v>
       </c>
-      <c r="BY108" s="303"/>
-      <c r="BZ108" s="304"/>
-      <c r="CA108" s="306"/>
+      <c r="BY108" s="289"/>
+      <c r="BZ108" s="290"/>
+      <c r="CA108" s="292"/>
       <c r="CB108" s="117"/>
     </row>
     <row r="109" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="268"/>
-      <c r="B109" s="298" t="s">
+      <c r="A109" s="308"/>
+      <c r="B109" s="284" t="s">
         <v>25</v>
       </c>
-      <c r="C109" s="299"/>
-      <c r="D109" s="299"/>
-      <c r="E109" s="299"/>
-      <c r="F109" s="299"/>
-      <c r="G109" s="299"/>
-      <c r="H109" s="299"/>
-      <c r="I109" s="299"/>
-      <c r="J109" s="299"/>
-      <c r="K109" s="300"/>
-      <c r="L109" s="308">
+      <c r="C109" s="285"/>
+      <c r="D109" s="285"/>
+      <c r="E109" s="285"/>
+      <c r="F109" s="285"/>
+      <c r="G109" s="285"/>
+      <c r="H109" s="285"/>
+      <c r="I109" s="285"/>
+      <c r="J109" s="285"/>
+      <c r="K109" s="286"/>
+      <c r="L109" s="294">
         <f>SUM(L108:BX108)</f>
         <v>7596.5</v>
       </c>
-      <c r="M109" s="309"/>
-      <c r="N109" s="309"/>
-      <c r="O109" s="309"/>
-      <c r="P109" s="310"/>
-      <c r="Q109" s="310"/>
-      <c r="R109" s="310"/>
-      <c r="S109" s="310"/>
-      <c r="T109" s="310"/>
-      <c r="U109" s="310"/>
-      <c r="V109" s="310"/>
-      <c r="W109" s="310"/>
-      <c r="X109" s="310"/>
-      <c r="Y109" s="310"/>
-      <c r="Z109" s="310"/>
-      <c r="AA109" s="310"/>
-      <c r="AB109" s="310"/>
-      <c r="AC109" s="310"/>
-      <c r="AD109" s="310"/>
-      <c r="AE109" s="310"/>
-      <c r="AF109" s="310"/>
-      <c r="AG109" s="310"/>
-      <c r="AH109" s="310"/>
-      <c r="AI109" s="310"/>
-      <c r="AJ109" s="310"/>
-      <c r="AK109" s="310"/>
-      <c r="AL109" s="310"/>
-      <c r="AM109" s="310"/>
-      <c r="AN109" s="310"/>
-      <c r="AO109" s="310"/>
-      <c r="AP109" s="310"/>
-      <c r="AQ109" s="310"/>
-      <c r="AR109" s="310"/>
-      <c r="AS109" s="310"/>
-      <c r="AT109" s="310"/>
-      <c r="AU109" s="310"/>
-      <c r="AV109" s="310"/>
-      <c r="AW109" s="310"/>
-      <c r="AX109" s="310"/>
-      <c r="AY109" s="310"/>
-      <c r="AZ109" s="310"/>
-      <c r="BA109" s="310"/>
-      <c r="BB109" s="310"/>
-      <c r="BC109" s="310"/>
-      <c r="BD109" s="310"/>
-      <c r="BE109" s="310"/>
-      <c r="BF109" s="310"/>
-      <c r="BG109" s="310"/>
-      <c r="BH109" s="310"/>
-      <c r="BI109" s="310"/>
-      <c r="BJ109" s="310"/>
-      <c r="BK109" s="310"/>
-      <c r="BL109" s="310"/>
-      <c r="BM109" s="310"/>
-      <c r="BN109" s="310"/>
-      <c r="BO109" s="310"/>
-      <c r="BP109" s="310"/>
-      <c r="BQ109" s="310"/>
-      <c r="BR109" s="310"/>
-      <c r="BS109" s="310"/>
-      <c r="BT109" s="310"/>
-      <c r="BU109" s="310"/>
-      <c r="BV109" s="310"/>
-      <c r="BW109" s="310"/>
-      <c r="BX109" s="310"/>
-      <c r="BY109" s="310"/>
-      <c r="BZ109" s="310"/>
-      <c r="CA109" s="306"/>
+      <c r="M109" s="295"/>
+      <c r="N109" s="295"/>
+      <c r="O109" s="295"/>
+      <c r="P109" s="296"/>
+      <c r="Q109" s="296"/>
+      <c r="R109" s="296"/>
+      <c r="S109" s="296"/>
+      <c r="T109" s="296"/>
+      <c r="U109" s="296"/>
+      <c r="V109" s="296"/>
+      <c r="W109" s="296"/>
+      <c r="X109" s="296"/>
+      <c r="Y109" s="296"/>
+      <c r="Z109" s="296"/>
+      <c r="AA109" s="296"/>
+      <c r="AB109" s="296"/>
+      <c r="AC109" s="296"/>
+      <c r="AD109" s="296"/>
+      <c r="AE109" s="296"/>
+      <c r="AF109" s="296"/>
+      <c r="AG109" s="296"/>
+      <c r="AH109" s="296"/>
+      <c r="AI109" s="296"/>
+      <c r="AJ109" s="296"/>
+      <c r="AK109" s="296"/>
+      <c r="AL109" s="296"/>
+      <c r="AM109" s="296"/>
+      <c r="AN109" s="296"/>
+      <c r="AO109" s="296"/>
+      <c r="AP109" s="296"/>
+      <c r="AQ109" s="296"/>
+      <c r="AR109" s="296"/>
+      <c r="AS109" s="296"/>
+      <c r="AT109" s="296"/>
+      <c r="AU109" s="296"/>
+      <c r="AV109" s="296"/>
+      <c r="AW109" s="296"/>
+      <c r="AX109" s="296"/>
+      <c r="AY109" s="296"/>
+      <c r="AZ109" s="296"/>
+      <c r="BA109" s="296"/>
+      <c r="BB109" s="296"/>
+      <c r="BC109" s="296"/>
+      <c r="BD109" s="296"/>
+      <c r="BE109" s="296"/>
+      <c r="BF109" s="296"/>
+      <c r="BG109" s="296"/>
+      <c r="BH109" s="296"/>
+      <c r="BI109" s="296"/>
+      <c r="BJ109" s="296"/>
+      <c r="BK109" s="296"/>
+      <c r="BL109" s="296"/>
+      <c r="BM109" s="296"/>
+      <c r="BN109" s="296"/>
+      <c r="BO109" s="296"/>
+      <c r="BP109" s="296"/>
+      <c r="BQ109" s="296"/>
+      <c r="BR109" s="296"/>
+      <c r="BS109" s="296"/>
+      <c r="BT109" s="296"/>
+      <c r="BU109" s="296"/>
+      <c r="BV109" s="296"/>
+      <c r="BW109" s="296"/>
+      <c r="BX109" s="296"/>
+      <c r="BY109" s="296"/>
+      <c r="BZ109" s="296"/>
+      <c r="CA109" s="292"/>
       <c r="CB109" s="117"/>
     </row>
     <row r="110" spans="1:80" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="268"/>
-      <c r="B110" s="298" t="s">
+      <c r="A110" s="308"/>
+      <c r="B110" s="284" t="s">
         <v>538</v>
       </c>
-      <c r="C110" s="299"/>
-      <c r="D110" s="299"/>
-      <c r="E110" s="299"/>
-      <c r="F110" s="299"/>
-      <c r="G110" s="299"/>
-      <c r="H110" s="299"/>
-      <c r="I110" s="299"/>
-      <c r="J110" s="299"/>
-      <c r="K110" s="300"/>
-      <c r="L110" s="311">
+      <c r="C110" s="285"/>
+      <c r="D110" s="285"/>
+      <c r="E110" s="285"/>
+      <c r="F110" s="285"/>
+      <c r="G110" s="285"/>
+      <c r="H110" s="285"/>
+      <c r="I110" s="285"/>
+      <c r="J110" s="285"/>
+      <c r="K110" s="286"/>
+      <c r="L110" s="297">
         <f>COUNTA(H12:H106)</f>
         <v>50</v>
       </c>
-      <c r="M110" s="312"/>
-      <c r="N110" s="312"/>
-      <c r="O110" s="312"/>
-      <c r="P110" s="313"/>
-      <c r="Q110" s="313"/>
-      <c r="R110" s="313"/>
-      <c r="S110" s="313"/>
-      <c r="T110" s="313"/>
-      <c r="U110" s="313"/>
-      <c r="V110" s="313"/>
-      <c r="W110" s="313"/>
-      <c r="X110" s="313"/>
-      <c r="Y110" s="313"/>
-      <c r="Z110" s="313"/>
-      <c r="AA110" s="313"/>
-      <c r="AB110" s="313"/>
-      <c r="AC110" s="313"/>
-      <c r="AD110" s="313"/>
-      <c r="AE110" s="313"/>
-      <c r="AF110" s="313"/>
-      <c r="AG110" s="313"/>
-      <c r="AH110" s="313"/>
-      <c r="AI110" s="313"/>
-      <c r="AJ110" s="313"/>
-      <c r="AK110" s="313"/>
-      <c r="AL110" s="313"/>
-      <c r="AM110" s="313"/>
-      <c r="AN110" s="313"/>
-      <c r="AO110" s="313"/>
-      <c r="AP110" s="313"/>
-      <c r="AQ110" s="313"/>
-      <c r="AR110" s="313"/>
-      <c r="AS110" s="313"/>
-      <c r="AT110" s="313"/>
-      <c r="AU110" s="313"/>
-      <c r="AV110" s="313"/>
-      <c r="AW110" s="313"/>
-      <c r="AX110" s="313"/>
-      <c r="AY110" s="313"/>
-      <c r="AZ110" s="313"/>
-      <c r="BA110" s="313"/>
-      <c r="BB110" s="313"/>
-      <c r="BC110" s="313"/>
-      <c r="BD110" s="313"/>
-      <c r="BE110" s="313"/>
-      <c r="BF110" s="313"/>
-      <c r="BG110" s="313"/>
-      <c r="BH110" s="313"/>
-      <c r="BI110" s="313"/>
-      <c r="BJ110" s="313"/>
-      <c r="BK110" s="313"/>
-      <c r="BL110" s="313"/>
-      <c r="BM110" s="313"/>
-      <c r="BN110" s="313"/>
-      <c r="BO110" s="313"/>
-      <c r="BP110" s="313"/>
-      <c r="BQ110" s="313"/>
-      <c r="BR110" s="313"/>
-      <c r="BS110" s="313"/>
-      <c r="BT110" s="313"/>
-      <c r="BU110" s="313"/>
-      <c r="BV110" s="313"/>
-      <c r="BW110" s="313"/>
-      <c r="BX110" s="313"/>
-      <c r="BY110" s="313"/>
-      <c r="BZ110" s="313"/>
-      <c r="CA110" s="307"/>
+      <c r="M110" s="298"/>
+      <c r="N110" s="298"/>
+      <c r="O110" s="298"/>
+      <c r="P110" s="299"/>
+      <c r="Q110" s="299"/>
+      <c r="R110" s="299"/>
+      <c r="S110" s="299"/>
+      <c r="T110" s="299"/>
+      <c r="U110" s="299"/>
+      <c r="V110" s="299"/>
+      <c r="W110" s="299"/>
+      <c r="X110" s="299"/>
+      <c r="Y110" s="299"/>
+      <c r="Z110" s="299"/>
+      <c r="AA110" s="299"/>
+      <c r="AB110" s="299"/>
+      <c r="AC110" s="299"/>
+      <c r="AD110" s="299"/>
+      <c r="AE110" s="299"/>
+      <c r="AF110" s="299"/>
+      <c r="AG110" s="299"/>
+      <c r="AH110" s="299"/>
+      <c r="AI110" s="299"/>
+      <c r="AJ110" s="299"/>
+      <c r="AK110" s="299"/>
+      <c r="AL110" s="299"/>
+      <c r="AM110" s="299"/>
+      <c r="AN110" s="299"/>
+      <c r="AO110" s="299"/>
+      <c r="AP110" s="299"/>
+      <c r="AQ110" s="299"/>
+      <c r="AR110" s="299"/>
+      <c r="AS110" s="299"/>
+      <c r="AT110" s="299"/>
+      <c r="AU110" s="299"/>
+      <c r="AV110" s="299"/>
+      <c r="AW110" s="299"/>
+      <c r="AX110" s="299"/>
+      <c r="AY110" s="299"/>
+      <c r="AZ110" s="299"/>
+      <c r="BA110" s="299"/>
+      <c r="BB110" s="299"/>
+      <c r="BC110" s="299"/>
+      <c r="BD110" s="299"/>
+      <c r="BE110" s="299"/>
+      <c r="BF110" s="299"/>
+      <c r="BG110" s="299"/>
+      <c r="BH110" s="299"/>
+      <c r="BI110" s="299"/>
+      <c r="BJ110" s="299"/>
+      <c r="BK110" s="299"/>
+      <c r="BL110" s="299"/>
+      <c r="BM110" s="299"/>
+      <c r="BN110" s="299"/>
+      <c r="BO110" s="299"/>
+      <c r="BP110" s="299"/>
+      <c r="BQ110" s="299"/>
+      <c r="BR110" s="299"/>
+      <c r="BS110" s="299"/>
+      <c r="BT110" s="299"/>
+      <c r="BU110" s="299"/>
+      <c r="BV110" s="299"/>
+      <c r="BW110" s="299"/>
+      <c r="BX110" s="299"/>
+      <c r="BY110" s="299"/>
+      <c r="BZ110" s="299"/>
+      <c r="CA110" s="293"/>
       <c r="CB110" s="117"/>
     </row>
     <row r="111" spans="1:80" x14ac:dyDescent="0.25">
-      <c r="A111" s="267"/>
-      <c r="B111" s="267"/>
-      <c r="C111" s="267"/>
-      <c r="D111" s="267"/>
-      <c r="E111" s="267"/>
-      <c r="F111" s="267"/>
-      <c r="G111" s="267"/>
-      <c r="H111" s="267"/>
-      <c r="I111" s="267"/>
-      <c r="J111" s="267"/>
-      <c r="K111" s="267"/>
-      <c r="L111" s="267"/>
-      <c r="M111" s="267"/>
-      <c r="N111" s="267"/>
-      <c r="O111" s="267"/>
-      <c r="P111" s="267"/>
-      <c r="Q111" s="267"/>
-      <c r="R111" s="267"/>
-      <c r="S111" s="267"/>
-      <c r="T111" s="267"/>
-      <c r="U111" s="267"/>
-      <c r="V111" s="267"/>
-      <c r="W111" s="267"/>
-      <c r="X111" s="267"/>
-      <c r="Y111" s="267"/>
-      <c r="Z111" s="267"/>
-      <c r="AA111" s="267"/>
-      <c r="AB111" s="267"/>
-      <c r="AC111" s="267"/>
-      <c r="AD111" s="267"/>
-      <c r="AE111" s="267"/>
-      <c r="AF111" s="267"/>
-      <c r="AG111" s="267"/>
-      <c r="AH111" s="267"/>
-      <c r="AI111" s="267"/>
-      <c r="AJ111" s="267"/>
-      <c r="AK111" s="267"/>
-      <c r="AL111" s="267"/>
-      <c r="AM111" s="267"/>
-      <c r="AN111" s="267"/>
-      <c r="AO111" s="267"/>
-      <c r="AP111" s="267"/>
-      <c r="AQ111" s="267"/>
-      <c r="AR111" s="267"/>
-      <c r="AS111" s="267"/>
-      <c r="AT111" s="267"/>
-      <c r="AU111" s="267"/>
-      <c r="AV111" s="267"/>
-      <c r="AW111" s="267"/>
-      <c r="AX111" s="267"/>
-      <c r="AY111" s="267"/>
-      <c r="AZ111" s="267"/>
-      <c r="BA111" s="267"/>
-      <c r="BB111" s="267"/>
-      <c r="BC111" s="267"/>
-      <c r="BD111" s="267"/>
-      <c r="BE111" s="267"/>
-      <c r="BF111" s="267"/>
-      <c r="BG111" s="267"/>
-      <c r="BH111" s="267"/>
-      <c r="BI111" s="267"/>
-      <c r="BJ111" s="267"/>
-      <c r="BK111" s="267"/>
-      <c r="BL111" s="267"/>
-      <c r="BM111" s="267"/>
-      <c r="BN111" s="267"/>
-      <c r="BO111" s="267"/>
-      <c r="BP111" s="267"/>
-      <c r="BQ111" s="267"/>
-      <c r="BR111" s="267"/>
-      <c r="BS111" s="267"/>
-      <c r="BT111" s="267"/>
-      <c r="BU111" s="267"/>
-      <c r="BV111" s="267"/>
-      <c r="BW111" s="267"/>
-      <c r="BX111" s="267"/>
-      <c r="BY111" s="267"/>
-      <c r="BZ111" s="267"/>
-      <c r="CA111" s="267"/>
+      <c r="A111" s="281"/>
+      <c r="B111" s="281"/>
+      <c r="C111" s="281"/>
+      <c r="D111" s="281"/>
+      <c r="E111" s="281"/>
+      <c r="F111" s="281"/>
+      <c r="G111" s="281"/>
+      <c r="H111" s="281"/>
+      <c r="I111" s="281"/>
+      <c r="J111" s="281"/>
+      <c r="K111" s="281"/>
+      <c r="L111" s="281"/>
+      <c r="M111" s="281"/>
+      <c r="N111" s="281"/>
+      <c r="O111" s="281"/>
+      <c r="P111" s="281"/>
+      <c r="Q111" s="281"/>
+      <c r="R111" s="281"/>
+      <c r="S111" s="281"/>
+      <c r="T111" s="281"/>
+      <c r="U111" s="281"/>
+      <c r="V111" s="281"/>
+      <c r="W111" s="281"/>
+      <c r="X111" s="281"/>
+      <c r="Y111" s="281"/>
+      <c r="Z111" s="281"/>
+      <c r="AA111" s="281"/>
+      <c r="AB111" s="281"/>
+      <c r="AC111" s="281"/>
+      <c r="AD111" s="281"/>
+      <c r="AE111" s="281"/>
+      <c r="AF111" s="281"/>
+      <c r="AG111" s="281"/>
+      <c r="AH111" s="281"/>
+      <c r="AI111" s="281"/>
+      <c r="AJ111" s="281"/>
+      <c r="AK111" s="281"/>
+      <c r="AL111" s="281"/>
+      <c r="AM111" s="281"/>
+      <c r="AN111" s="281"/>
+      <c r="AO111" s="281"/>
+      <c r="AP111" s="281"/>
+      <c r="AQ111" s="281"/>
+      <c r="AR111" s="281"/>
+      <c r="AS111" s="281"/>
+      <c r="AT111" s="281"/>
+      <c r="AU111" s="281"/>
+      <c r="AV111" s="281"/>
+      <c r="AW111" s="281"/>
+      <c r="AX111" s="281"/>
+      <c r="AY111" s="281"/>
+      <c r="AZ111" s="281"/>
+      <c r="BA111" s="281"/>
+      <c r="BB111" s="281"/>
+      <c r="BC111" s="281"/>
+      <c r="BD111" s="281"/>
+      <c r="BE111" s="281"/>
+      <c r="BF111" s="281"/>
+      <c r="BG111" s="281"/>
+      <c r="BH111" s="281"/>
+      <c r="BI111" s="281"/>
+      <c r="BJ111" s="281"/>
+      <c r="BK111" s="281"/>
+      <c r="BL111" s="281"/>
+      <c r="BM111" s="281"/>
+      <c r="BN111" s="281"/>
+      <c r="BO111" s="281"/>
+      <c r="BP111" s="281"/>
+      <c r="BQ111" s="281"/>
+      <c r="BR111" s="281"/>
+      <c r="BS111" s="281"/>
+      <c r="BT111" s="281"/>
+      <c r="BU111" s="281"/>
+      <c r="BV111" s="281"/>
+      <c r="BW111" s="281"/>
+      <c r="BX111" s="281"/>
+      <c r="BY111" s="281"/>
+      <c r="BZ111" s="281"/>
+      <c r="CA111" s="281"/>
       <c r="CB111" s="117"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="+OUfHYu+qKpL/hYAEW8zftCIaMG0eMIQFnZdtlgQ4yNYZM3cuILpw9wysi8dFDcSITbhuuFLn+MFBHdTQJ9vog==" saltValue="Pcu5PMyqtObvR1iMPrcpsg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="40">
-    <mergeCell ref="BY13:BY56"/>
-    <mergeCell ref="J58:AZ58"/>
-    <mergeCell ref="J59:AZ59"/>
-    <mergeCell ref="J60:AZ60"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="K8:K12"/>
-    <mergeCell ref="L8:V8"/>
-    <mergeCell ref="W8:BX8"/>
+    <mergeCell ref="CA8:CA11"/>
+    <mergeCell ref="A1:CB1"/>
+    <mergeCell ref="A2:A110"/>
+    <mergeCell ref="B2:F6"/>
+    <mergeCell ref="J2:AZ2"/>
+    <mergeCell ref="J3:AZ3"/>
+    <mergeCell ref="J4:AZ4"/>
+    <mergeCell ref="J5:AZ5"/>
+    <mergeCell ref="J6:AZ6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="C7:CA7"/>
+    <mergeCell ref="C8:D10"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="H8:H11"/>
     <mergeCell ref="BZ8:BZ11"/>
     <mergeCell ref="A111:CA111"/>
     <mergeCell ref="J62:AZ62"/>
@@ -20473,22 +20481,14 @@
     <mergeCell ref="J61:AZ61"/>
     <mergeCell ref="I8:I11"/>
     <mergeCell ref="BY8:BY11"/>
-    <mergeCell ref="CA8:CA11"/>
-    <mergeCell ref="A1:CB1"/>
-    <mergeCell ref="A2:A110"/>
-    <mergeCell ref="B2:F6"/>
-    <mergeCell ref="J2:AZ2"/>
-    <mergeCell ref="J3:AZ3"/>
-    <mergeCell ref="J4:AZ4"/>
-    <mergeCell ref="J5:AZ5"/>
-    <mergeCell ref="J6:AZ6"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="C7:CA7"/>
-    <mergeCell ref="C8:D10"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="BY13:BY56"/>
+    <mergeCell ref="J58:AZ58"/>
+    <mergeCell ref="J59:AZ59"/>
+    <mergeCell ref="J60:AZ60"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="K8:K12"/>
+    <mergeCell ref="L8:V8"/>
+    <mergeCell ref="W8:BX8"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:C56">
     <cfRule type="cellIs" dxfId="54" priority="8" stopIfTrue="1" operator="greaterThan">
